--- a/input/mapping/063. OCB_GOLD_TCKH_CB_OFCR_DIM_HOP.xlsx
+++ b/input/mapping/063. OCB_GOLD_TCKH_CB_OFCR_DIM_HOP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1713" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75B8A510-B1C7-41A2-9DEE-DEA43B124E87}"/>
+  <xr:revisionPtr revIDLastSave="1761" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3593D400-E7EE-4688-AA51-2B48CEB6036B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" firstSheet="9" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -22,14 +22,14 @@
     <sheet name="BRANCH_LIST" sheetId="20" state="hidden" r:id="rId7"/>
     <sheet name="V_BRANCH_LIST" sheetId="19" state="hidden" r:id="rId8"/>
     <sheet name="CB_OFCR_DIM" sheetId="32" r:id="rId9"/>
-    <sheet name="CB_OU_DIM" sheetId="31" r:id="rId10"/>
-    <sheet name="V_FTP_RATE" sheetId="14" state="hidden" r:id="rId11"/>
-    <sheet name="LD_FTP_RATE" sheetId="16" state="hidden" r:id="rId12"/>
-    <sheet name="V_LD_FTP_RATE" sheetId="25" state="hidden" r:id="rId13"/>
-    <sheet name="FTP_CONTRACT_HIST" sheetId="18" state="hidden" r:id="rId14"/>
-    <sheet name="FTP_CONTRACT" sheetId="30" state="hidden" r:id="rId15"/>
-    <sheet name="V_FTP_INTEREST_RATE_NIM_ON" sheetId="15" state="hidden" r:id="rId16"/>
-    <sheet name="FTP_RATE_LIST_HIST" sheetId="17" state="hidden" r:id="rId17"/>
+    <sheet name="V_FTP_RATE" sheetId="14" state="hidden" r:id="rId10"/>
+    <sheet name="LD_FTP_RATE" sheetId="16" state="hidden" r:id="rId11"/>
+    <sheet name="V_LD_FTP_RATE" sheetId="25" state="hidden" r:id="rId12"/>
+    <sheet name="FTP_CONTRACT_HIST" sheetId="18" state="hidden" r:id="rId13"/>
+    <sheet name="FTP_CONTRACT" sheetId="30" state="hidden" r:id="rId14"/>
+    <sheet name="V_FTP_INTEREST_RATE_NIM_ON" sheetId="15" state="hidden" r:id="rId15"/>
+    <sheet name="FTP_RATE_LIST_HIST" sheetId="17" state="hidden" r:id="rId16"/>
+    <sheet name="CB_OU_DIM (2)" sheetId="33" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -339,8 +339,8 @@
     <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
 CREATE TABLE IF NOT EXISTS CB_OU_DIM (
-    OU_DIM_ID       BIGINT,     -- MAX(OU_DIM_ID) + ROW_NUMBER()
-    OU_ID           STRING,     -- branch_hashkey (SHA256)
+    OU_DIM_ID       BIGINT,
+    OU_ID           STRING,
     OU_NM           STRING,
     OU_CODE         STRING,
     PRN_OU_ID       STRING,
@@ -367,15 +367,15 @@
         GROUP BY branch_hashkey
         HAVING MAX_BY(cdc_status, source_event_date) = 'D'
     ),
-    -- Hub đang có hiệu lực = Hub LEFT JOIN loại các khóa deleted
+    -- Hub đang có hiệu lực (CACHE: dùng lại 2 lần trong source_data)
     hub_active AS (
         SELECT h.branch_hashkey, h.business_key, h.source_event_date
         FROM IDENTIFIER(:cleaned || '.raw_vault.hub_branch') h
-        LEFT JOIN sts_deleted d
-            ON h.branch_hashkey = d.branch_hashkey
+        LEFT JOIN sts_deleted d ON h.branch_hashkey = d.branch_hashkey
         WHERE d.branch_hashkey IS NULL
     ),
-    -- Satellite (single-active): làm giàu thuộc tính, bản mới nhất đến :etl_date
+    -- Satellite branch_information: bản mới nhất &lt;= :etl_date
+    -- (CACHE: dùng lại 2 lần trong source_data cho branch và parent branch)
     sat_latest AS (
         SELECT
             branch_hashkey,
@@ -384,7 +384,7 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY branch_hashkey
     ),
-    -- Satellite branch_mapping (single-active)
+    -- Satellite branch_mapping: bản mới nhất &lt;= :etl_date
     bm_latest AS (
         SELECT
             branch_hashkey,
@@ -395,18 +395,25 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY branch_hashkey
     ),
+    -- ou_area_mapping filter trước join (WARN 3.3)
+    area_map AS (
+        SELECT OU_ID, CB_AREA_ID, CB_AREA_NM
+        FROM ou_area_mapping
+        WHERE CB_AREA_ID IS NOT NULL
+    ),
+    -- Source data tổng hợp (CACHE: dùng lại 3 lần trong changed, new_records, close_records)
     source_data AS (
         SELECT
-            h.branch_hashkey                                    AS OU_ID,
-            h.business_key                                      AS OU_CODE,
-            SUBSTRING_INDEX(si.t_company_name, '::', 1)         AS OU_NM,
-            prn_hub.branch_hashkey                              AS PRN_OU_ID,
-            SUBSTRING_INDEX(prn_si.t_company_name, '::', 1)     AS PRN_OU_NM,
-            bm.parent_branch_code                               AS PRN_OU_CODE,
+            h.branch_hashkey                                AS OU_ID,
+            h.business_key                                  AS OU_CODE,
+            SUBSTRING_INDEX(si.t_company_name, '::', 1)     AS OU_NM,
+            prn_hub.branch_hashkey                          AS PRN_OU_ID,
+            SUBSTRING_INDEX(prn_si.t_company_name, '::', 1) AS PRN_OU_NM,
+            bm.parent_branch_code                           AS PRN_OU_CODE,
             am.CB_AREA_ID,
             am.CB_AREA_NM,
-            bm.address                                          AS OU_ADR,
-            bm.phone_number                                     AS OU_PH,
+            bm.address                                      AS OU_ADR,
+            bm.phone_number                                 AS OU_PH,
             h.source_event_date
         FROM hub_active h
         LEFT JOIN sat_latest si
@@ -417,16 +424,13 @@
             ON prn_hub.business_key = bm.parent_branch_code
         LEFT JOIN sat_latest prn_si
             ON prn_hub.branch_hashkey = prn_si.branch_hashkey
-        LEFT JOIN ou_area_mapping am
+        LEFT JOIN area_map am
             ON am.OU_ID = h.business_key
         WHERE UPPER(COALESCE(si.t_company_name, '')) &lt;&gt; 'NOT USED'
           AND h.business_key &lt;&gt; 'VN0010001'
     ),
-    -- Max OU_DIM_ID hiện tại
-    max_id AS (
-        SELECT COALESCE(MAX(OU_DIM_ID), 0) AS max_val
-        FROM CB_OU_DIM
-    ),
+    -- Tập OU_ID có thay đổi thuộc tính so với bản đang active
+    -- (CACHE: dùng lại 2 lần trong new_records và close_records)
     changed AS (
         SELECT src.OU_ID
         FROM source_data src
@@ -440,6 +444,8 @@
            OR COALESCE(src.OU_ADR,      '') &lt;&gt; COALESCE(tgt.OU_ADR,      '')
            OR COALESCE(src.OU_PH,       '') &lt;&gt; COALESCE(tgt.OU_PH,       '')
     ),
+    -- Bản ghi NEW: insert mới hoặc insert version mới khi thay đổi
+    -- uuid() thay MAX+ROW_NUMBER() (fix 2.5/2.6): idempotent, không trùng khi parallel
     new_records AS (
         SELECT
             'NEW'                                               AS rec_type,
@@ -455,19 +461,19 @@
             src.source_event_date,
             src.OU_ADR,
             src.OU_PH,
-            m.max_val + ROW_NUMBER() OVER (ORDER BY src.OU_ID)  AS NEW_OU_DIM_ID
+            uuid()                                              AS NEW_OU_DIM_ID
         FROM source_data src
-        CROSS JOIN max_id m
         LEFT JOIN CB_OU_DIM tgt_chk
             ON  src.OU_ID        = tgt_chk.OU_ID
             AND tgt_chk.EFF_TO_DT IS NULL
         WHERE tgt_chk.OU_ID IS NULL
            OR src.OU_ID IN (SELECT OU_ID FROM changed)
     ),
+    -- Bản ghi CLOSE: đóng version hiện tại khi có thay đổi hoặc bị xóa
     close_records AS (
         SELECT
-            'CLOSE'                                             AS rec_type,
-            'D'                                                 AS CDC_FLAG,
+            'CLOSE'                AS rec_type,
+            'D'                    AS CDC_FLAG,
             tgt.OU_ID,
             tgt.OU_NM,
             tgt.OU_CODE,
@@ -476,10 +482,10 @@
             tgt.PRN_OU_CODE,
             tgt.CB_AREA_ID,
             tgt.CB_AREA_NM,
-            tgt.START_WK_DT                                     AS source_event_date,
+            tgt.START_WK_DT        AS source_event_date,
             tgt.OU_ADR,
             tgt.OU_PH,
-            tgt.OU_DIM_ID                                       AS NEW_OU_DIM_ID
+            tgt.OU_DIM_ID          AS NEW_OU_DIM_ID  -- giữ nguyên ID cũ khi close
         FROM CB_OU_DIM tgt
         LEFT JOIN source_data src ON src.OU_ID = tgt.OU_ID
         WHERE tgt.EFF_TO_DT IS NULL
@@ -488,9 +494,26 @@
                 OR src.OU_ID IS NULL
               )
     )
-    SELECT * FROM new_records
+    -- Liệt kê tường minh (fix 3.1: bỏ SELECT *)
+    SELECT
+        rec_type, CDC_FLAG,
+        OU_ID, OU_NM, OU_CODE,
+        PRN_OU_ID, PRN_OU_NM, PRN_OU_CODE,
+        CB_AREA_ID, CB_AREA_NM,
+        source_event_date,
+        OU_ADR, OU_PH,
+        NEW_OU_DIM_ID
+    FROM new_records
     UNION ALL
-    SELECT * FROM close_records
+    SELECT
+        rec_type, CDC_FLAG,
+        OU_ID, OU_NM, OU_CODE,
+        PRN_OU_ID, PRN_OU_NM, PRN_OU_CODE,
+        CB_AREA_ID, CB_AREA_NM,
+        source_event_date,
+        OU_ADR, OU_PH,
+        NEW_OU_DIM_ID
+    FROM close_records
 ) src
 ON  tgt.OU_ID     = src.OU_ID
 AND tgt.EFF_TO_DT IS NULL
@@ -530,15 +553,6 @@
   <si>
     <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
--- =============================================================================
--- CB_OFCR_DIM  (SCD Type 1, MERGE -&gt; chạy bằng SQL job NGOÀI LDP)
--- Nguồn: Silver (hub_acct_officer, sts_hub_acct_officer,
---        sat_acct_officer_information, link_acct_officer_branch,
---        sat_branch_mapping) + CB_OU_DIM, ou_area_mapping (Gold)
--- Params: :cleaned, :curated, :etl_date (yyyyMMdd)
--- Default NULL: OU_ID/PRN_OU_ID = '999999999', tên = 'Khong xac dinh'
--- Nguồn Silver ở catalog :cleaned (khác default) -&gt; giữ IDENTIFIER
--- =============================================================================
 MERGE INTO CB_OFCR_DIM tgt
 USING (
     WITH
@@ -550,7 +564,7 @@
         GROUP BY dept_acct_officer_hashkey
         HAVING MAX_BY(cdc_status, source_event_date) = 'D'
     ),
-    -- Satellite officer: bản thuộc tính mới nhất đến :etl_date (single-active)
+    -- Satellite officer: bản thuộc tính mới nhất đến :etl_date (fix X.6: LEFT JOIN)
     sat_ofcr AS (
         SELECT
             dept_acct_officer_hashkey,
@@ -560,7 +574,7 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY dept_acct_officer_hashkey
     ),
-    -- Hub officer active = Hub JOIN sat, loại khóa deleted
+    -- Hub officer active = Hub LEFT JOIN sat, loại khóa deleted (fix X.6)
     officer_active AS (
         SELECT
             h.dept_acct_officer_hashkey,
@@ -568,7 +582,7 @@
             s.t_name            AS OFCR_NM,
             s.source_event_date AS SRC_DT
         FROM IDENTIFIER(:cleaned || '.raw_vault.hub_acct_officer') h
-        JOIN sat_ofcr s
+        LEFT JOIN sat_ofcr s
             ON h.dept_acct_officer_hashkey = s.dept_acct_officer_hashkey
         LEFT JOIN sts_deleted d
             ON h.dept_acct_officer_hashkey = d.dept_acct_officer_hashkey
@@ -592,10 +606,11 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY branch_hashkey
     ),
-    -- MAX OU_OFCR_DIM_ID hiện tại
-    max_id AS (
-        SELECT COALESCE(MAX(OU_OFCR_DIM_ID), 0) AS max_val
-        FROM CB_OFCR_DIM
+    -- ou_area_mapping filter trước join (fix WARN 3.3)
+    area_mapping AS (
+        SELECT OU_ID, CB_AREA_ID, CB_AREA_NM
+        FROM ou_area_mapping
+        WHERE CB_AREA_ID IS NOT NULL
     ),
     -- Build source data với default '999999999' / 'Khong xac dinh'
     src_data AS (
@@ -604,38 +619,44 @@
             o.OFCR_T24_CODE,
             o.OFCR_NM,
             o.SRC_DT,
-            COALESCE(ou.OU_ID,   '999999999')          AS OU_ID,
-            COALESCE(ou.OU_NM,   'Khong xac dinh')     AS OU_NM,
-            ou.OU_CODE                                 AS OU_CODE,
-            COALESCE(prn.OU_ID,  '999999999')          AS PRN_OU_ID,
-            COALESCE(prn.OU_NM,  'Khong xac dinh')     AS PRN_OU_NM,
-            bm.parent_branch_code                      AS PRN_OU_CODE,
-            COALESCE(am.CB_AREA_ID, 999999999)         AS CB_AREA_ID,
-            COALESCE(am.CB_AREA_NM, 'Khong xac dinh')  AS CB_AREA_NM
+            COALESCE(ou.OU_ID,   '999999999')         AS OU_ID,
+            COALESCE(ou.OU_NM,   'Khong xac dinh')    AS OU_NM,
+            ou.OU_CODE                                AS OU_CODE,
+            COALESCE(prn.OU_ID,  '999999999')         AS PRN_OU_ID,
+            COALESCE(prn.OU_NM,  'Khong xac dinh')    AS PRN_OU_NM,
+            bm.parent_branch_code                     AS PRN_OU_CODE,
+            COALESCE(am.CB_AREA_ID, 999999999)        AS CB_AREA_ID,
+            COALESCE(am.CB_AREA_NM, 'Khong xac dinh') AS CB_AREA_NM
         FROM officer_active o
-        -- chi nhánh của officer
         LEFT JOIN ofcr_branch ob
             ON ob.dept_acct_officer_hashkey = o.dept_acct_officer_hashkey
-        -- dim chi nhánh (CB_OU_DIM.OU_ID = branch_hashkey)
         LEFT JOIN CB_OU_DIM ou
             ON  ou.OU_ID     = ob.branch_hashkey
             AND ou.EFF_TO_DT IS NULL
-        -- parent branch: silver sat_branch_mapping theo branch_hashkey của officer
         LEFT JOIN bm_latest bm
             ON bm.branch_hashkey = ob.branch_hashkey
         LEFT JOIN CB_OU_DIM prn
             ON  prn.OU_CODE   = bm.parent_branch_code
             AND prn.EFF_TO_DT IS NULL
-        -- vùng (area)
-        LEFT JOIN ou_area_mapping am
-            ON am.OU_ID       = ou.OU_CODE
+        LEFT JOIN area_mapping am
+            ON am.OU_ID = ou.OU_CODE
     )
-    -- Sinh OU_OFCR_DIM_ID mới cho record chưa tồn tại
+    -- Liệt kê tường minh (fix 3.1: bỏ s.*), surrogate key dùng uuid() (fix 2.5/2.6)
     SELECT
-        m.max_val + ROW_NUMBER() OVER (ORDER BY s.dept_acct_officer_hashkey) AS NEW_OU_OFCR_DIM_ID,
-        s.*
+        uuid()                        AS NEW_OU_OFCR_DIM_ID,
+        s.dept_acct_officer_hashkey,
+        s.OFCR_T24_CODE,
+        s.OFCR_NM,
+        s.SRC_DT,
+        s.OU_ID,
+        s.OU_NM,
+        s.OU_CODE,
+        s.PRN_OU_ID,
+        s.PRN_OU_NM,
+        s.PRN_OU_CODE,
+        s.CB_AREA_ID,
+        s.CB_AREA_NM
     FROM src_data s
-    CROSS JOIN max_id m
 ) src
 ON tgt.OU_OFCR_ID = src.dept_acct_officer_hashkey
 -- CASE INSERT: Officer mới
@@ -656,8 +677,7 @@
         CRT_TM,
         EFF_FM_DT,
         EFF_TO_DT,
-        START_WK_DT,
-        PPN_TM
+        START_WK_DT
     )
     VALUES (
         src.NEW_OU_OFCR_DIM_ID,
@@ -675,8 +695,7 @@
         CURRENT_TIMESTAMP(),
         NULL,
         NULL,
-        src.SRC_DT,
-        CURRENT_TIMESTAMP()
+        src.SRC_DT
     )
 -- CASE UPDATE: Officer đã có (SCD Type 1 — overwrite)
 WHEN MATCHED THEN
@@ -690,8 +709,7 @@
         tgt.PRN_OU_NM        = src.PRN_OU_NM,
         tgt.PRN_OU_CODE      = src.PRN_OU_CODE,
         tgt.CB_AREA_ID       = src.CB_AREA_ID,
-        tgt.CB_AREA_NM       = src.CB_AREA_NM,
-        tgt.PPN_TM           = CURRENT_TIMESTAMP()
+        tgt.CB_AREA_NM       = src.CB_AREA_NM
 ;</t>
   </si>
   <si>
@@ -1589,7 +1607,7 @@
         s.t_name                        AS OFCR_NM,
         s.source_event_date             AS SRC_DT
     FROM ocb_datavault_dev_cleaned.raw_vault.hub_acct_officer h
-    JOIN (
+    LEFT JOIN (
         SELECT dept_acct_officer_hashkey, t_name, source_event_date
         FROM (
             SELECT dept_acct_officer_hashkey, t_name, source_event_date,
@@ -1617,7 +1635,7 @@
     <t>CTE</t>
   </si>
   <si>
-    <t>Officer active (silver): hub_acct_officer JOIN sat_acct_officer_information (RN=1 latest per dept_acct_officer_hashkey). LOAI officer bi xoa (NOT EXISTS sts_hub_acct_officer cdc_status='D', RN=1). source_event_date &lt;= {target_date}. Fields: business_key-&gt;OFCR_T24_CODE, t_name-&gt;OFCR_NM, source_event_date-&gt;SRC_DT</t>
+    <t>Officer active (silver): hub_acct_officer LEFT JOIN sat_acct_officer_information (fix X.6: LEFT thay INNER, RN=1 latest per dept_acct_officer_hashkey). LOAI officer bi xoa (NOT EXISTS sts_hub_acct_officer cdc_status='D', RN=1). source_event_date &lt;= {target_date}. Fields: business_key-&gt;OFCR_T24_CODE, t_name-&gt;OFCR_NM, source_event_date-&gt;SRC_DT</t>
   </si>
   <si>
     <t>ofcr_branch AS (
@@ -1654,16 +1672,17 @@
     <t>Parent branch: silver sat_branch_mapping (RN=1 latest per branch_hashkey) -&gt; parent_branch_code</t>
   </si>
   <si>
-    <t>max_id AS (
-    SELECT COALESCE(MAX(OU_OFCR_DIM_ID), 0) AS max_val
-    FROM ocb_datavault_dev_curated.tckh.CB_OFCR_DIM
+    <t>area_mapping AS (
+    SELECT OU_ID, CB_AREA_ID, CB_AREA_NM
+    FROM ocb_datavault_dev_curated.tckh.ou_area_mapping
+    WHERE CB_AREA_ID IS NOT NULL
 )</t>
   </si>
   <si>
-    <t>max_id</t>
-  </si>
-  <si>
-    <t>MAX(OU_OFCR_DIM_ID) hien tai -&gt; sinh surrogate key moi (max_val + ROW_NUMBER)</t>
+    <t>area_mapping</t>
+  </si>
+  <si>
+    <t>Loc truoc ou_area_mapping (fix WARN 3.3): chi lay dong co CB_AREA_ID IS NOT NULL, tranh join nhan ban truoc khi LEFT JOIN vao src_data</t>
   </si>
   <si>
     <t>src_data AS (
@@ -1682,9 +1701,9 @@
     LEFT JOIN CB_OU_DIM ou          ON ou.OU_ID = ob.branch_hashkey AND ou.EFF_TO_DT IS NULL
     LEFT JOIN bm_latest bm          ON bm.branch_hashkey = ob.branch_hashkey
     LEFT JOIN CB_OU_DIM prn         ON prn.OU_CODE = bm.parent_branch_code AND prn.EFF_TO_DT IS NULL
-    LEFT JOIN ou_area_mapping am    ON am.OU_ID = ou.OU_CODE
+    LEFT JOIN area_mapping am       ON am.OU_ID = ou.OU_CODE
 )
--- FINAL: SELECT m.max_val + ROW_NUMBER() OVER (ORDER BY s.dept_acct_officer_hashkey) AS NEW_OU_OFCR_DIM_ID, s.* FROM src_data s CROSS JOIN max_id m</t>
+-- FINAL (fix 2.5/2.6/3.1): SELECT uuid() AS NEW_OU_OFCR_DIM_ID, s.dept_acct_officer_hashkey, s.OFCR_T24_CODE, s.OFCR_NM, s.SRC_DT, s.OU_ID, s.OU_NM, s.OU_CODE, s.PRN_OU_ID, s.PRN_OU_NM, s.PRN_OU_CODE, s.CB_AREA_ID, s.CB_AREA_NM FROM src_data s  (liet ke tuong minh, khong con s.*)</t>
   </si>
   <si>
     <t>src_data / src</t>
@@ -1698,11 +1717,11 @@
 LEFT JOIN CB_OU_DIM ou ON ou.OU_ID = ob.branch_hashkey AND ou.EFF_TO_DT IS NULL
 LEFT JOIN bm_latest bm ON bm.branch_hashkey = ob.branch_hashkey
 LEFT JOIN CB_OU_DIM prn ON prn.OU_CODE = bm.parent_branch_code AND prn.EFF_TO_DT IS NULL
-LEFT JOIN ou_area_mapping am ON am.OU_ID = ou.OU_CODE
-FINAL: NEW_OU_OFCR_DIM_ID = max_val + ROW_NUMBER() OVER (ORDER BY dept_acct_officer_hashkey); MERGE ON tgt.OU_OFCR_ID = src.dept_acct_officer_hashkey</t>
-  </si>
-  <si>
-    <t>[ MERGE —  INSERT branch ]  Data Vault raw_vault (hub_acct_officer + sat_acct_officer_information + link_acct_officer_branch)  →   tckh.CB_OFCR_DIM  (SQL mới, xem SCRIPT!B5)  |  WHEN NOT MATCHED (OU_OFCR_ID = dept_acct_officer_hashkey chưa tồn tại) THEN INSERT</t>
+LEFT JOIN area_mapping am ON am.OU_ID = ou.OU_CODE (fix WARN 3.3: join CTE da loc thay vi ou_area_mapping truc tiep)
+FINAL: NEW_OU_OFCR_DIM_ID = uuid() (fix 2.5/2.6: khong con dung max_id+ROW_NUMBER); MERGE ON tgt.OU_OFCR_ID = src.dept_acct_officer_hashkey</t>
+  </si>
+  <si>
+    <t>[ MERGE —  INSERT branch ]  Data Vault raw_vault (hub_acct_officer + sat_acct_officer_information + link_acct_officer_branch)  →   tckh.CB_OFCR_DIM  (SQL mới, xem SCRIPT!D5)  |  WHEN NOT MATCHED (OU_OFCR_ID = dept_acct_officer_hashkey chưa tồn tại) THEN INSERT</t>
   </si>
   <si>
     <t xml:space="preserve"> tckh.CB_OFCR_DIM (self)</t>
@@ -1714,8 +1733,8 @@
     <t>BIGINT</t>
   </si>
   <si>
-    <t>max_id.max_val + ROW_NUMBER() OVER (ORDER BY dept_acct_officer_hashkey)
-→ key tự sinh (MAX(OU_OFCR_DIM_ID) + row_number)</t>
+    <t>uuid()
+→ surrogate key idempotent (fix 2.5/2.6, không còn dùng max_id + ROW_NUMBER)</t>
   </si>
   <si>
     <t>OU_OFCR_ID</t>
@@ -1775,7 +1794,7 @@
     <t>INTEGER</t>
   </si>
   <si>
-    <t>COALESCE(am.CB_AREA_ID, 999999999)</t>
+    <t>COALESCE(am.CB_AREA_ID, 999999999)  (am = area_mapping CTE, đã lọc CB_AREA_ID IS NOT NULL)</t>
   </si>
   <si>
     <t>CB_AREA_NM</t>
@@ -1808,13 +1827,363 @@
     <t>START_WK_DT</t>
   </si>
   <si>
-    <t>TO_DATE(CAST(src.SRC_DT AS STRING), 'yyyyMMdd')</t>
-  </si>
-  <si>
-    <t>[ MERGE — UPDATE branch ]  Data Vault raw_vault (hub_acct_officer + sat_acct_officer_information + link_acct_officer_branch)  →   tckh.CB_OFCR_DIM  (SQL mới, xem SCRIPT!B5)  |  WHEN MATCHED (OU_OFCR_ID = dept_acct_officer_hashkey đã tồn tại) THEN UPDATE SET  (overwrite SCD1) + PPN_TM = CURRENT_TIMESTAMP()</t>
+    <t>src.SRC_DT</t>
+  </si>
+  <si>
+    <t>[ MERGE — UPDATE branch ]  Data Vault raw_vault (hub_acct_officer + sat_acct_officer_information + link_acct_officer_branch)  →   tckh.CB_OFCR_DIM  (SQL mới, xem SCRIPT!D5)  |  WHEN MATCHED (OU_OFCR_ID = dept_acct_officer_hashkey đã tồn tại) THEN UPDATE SET  (overwrite SCD1, không còn PPN_TM — fix 1.1: cột không tồn tại trong thiết kế)</t>
   </si>
   <si>
     <t>src.dept_acct_officer_hashkey  (không UPDATE — là khóa MERGE ON tgt.OU_OFCR_ID = src.dept_acct_officer_hashkey)</t>
+  </si>
+  <si>
+    <t>V_FTP_RATE — VIEW</t>
+  </si>
+  <si>
+    <t>JOIN SCHEMA — V_FTP_RATE</t>
+  </si>
+  <si>
+    <t>LD_FTP_RATE</t>
+  </si>
+  <si>
+    <t>FROM LD_FTP_RATE</t>
+  </si>
+  <si>
+    <t>FIELD MAPPING — V_FTP_RATE</t>
+  </si>
+  <si>
+    <t>V_FTP_RATE</t>
+  </si>
+  <si>
+    <t>AR_NO</t>
+  </si>
+  <si>
+    <t>PD_FTP_RATE</t>
+  </si>
+  <si>
+    <t>SYSTEM_ID</t>
+  </si>
+  <si>
+    <t>PTPT</t>
+  </si>
+  <si>
+    <t>(CASE WHEN SYSTEM_ID Like '%PHAITHU%' THEN 1
+			WHEN SYSTEM_ID Like '%PHAITRA%' THEN 1
+			WHEN SYSTEM_ID Like '%TSCOKHAC%' THEN 1
+			else 0 end) as PTPT</t>
+  </si>
+  <si>
+    <t>LD_FTP_RATE — VIEW</t>
+  </si>
+  <si>
+    <t>JOIN SCHEMA — LD_FTP_RATE</t>
+  </si>
+  <si>
+    <t>V_LD_FTP_RATE</t>
+  </si>
+  <si>
+    <t>FIELD MAPPING — LD_FTP_RATE</t>
+  </si>
+  <si>
+    <t>GL_ACCOUNT</t>
+  </si>
+  <si>
+    <t>V_LD_FTP_RATE — VIEW
+JOIN SCHEMA — V_LD_FTP_RATE</t>
+  </si>
+  <si>
+    <t>FTP_CONTRACT_HIST</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>FIELD MAPPING — V_LD_FTP_RATE</t>
+  </si>
+  <si>
+    <t>h.SYSTEM_ID</t>
+  </si>
+  <si>
+    <t>h.DATA_DATE</t>
+  </si>
+  <si>
+    <t>h.AR_NO</t>
+  </si>
+  <si>
+    <t>CAST(SUM(CASE WHEN SUBSTR(h.REF_NO, 1, 2) = 'PD' THEN 0
+                  ELSE h.TOTAL_INT_RATE END) AS DECIMAL(20,4))  AS FTP_RATE</t>
+  </si>
+  <si>
+    <t>CAST(SUM(CASE WHEN SUBSTR(h.REF_NO, 1, 2) &lt;&gt; 'PD'
+                   AND h.SYSTEM_ID = 'CHOVAYKH'               THEN 0
+                  ELSE h.TOTAL_INT_RATE END) AS DECIMAL(20,4)) AS PD_FTP_RATE</t>
+  </si>
+  <si>
+    <t>h.GL_ACCOUNT</t>
+  </si>
+  <si>
+    <t>FTP_CONTRACT_HIST
+JOIN SCHEMA — FTP_CONTRACT_HIST</t>
+  </si>
+  <si>
+    <t>FTP_CONTRACT</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> where status=1</t>
+  </si>
+  <si>
+    <t>FIELD MAPPING — FTP_CONTRACT_HIST</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>SMALLINT</t>
+  </si>
+  <si>
+    <t>DATE_UPDATE</t>
+  </si>
+  <si>
+    <t>CHANGE_CODE</t>
+  </si>
+  <si>
+    <t>TINYINT</t>
+  </si>
+  <si>
+    <t>TOTAL_INT_RATE</t>
+  </si>
+  <si>
+    <t>DECIMAL(20,4)</t>
+  </si>
+  <si>
+    <t>LIQ_RATE</t>
+  </si>
+  <si>
+    <t>EX_TERM_RATE</t>
+  </si>
+  <si>
+    <t>EX_LAST_CHANGE_DATE</t>
+  </si>
+  <si>
+    <t>EX_NEW_DATE_NEXT_RATE_CHANGE</t>
+  </si>
+  <si>
+    <t>CONTRACT_DATE</t>
+  </si>
+  <si>
+    <t>PASTDUE_DAYS</t>
+  </si>
+  <si>
+    <t>DATE_NEXT_RATE_CHANGE</t>
+  </si>
+  <si>
+    <t>VALUE_DATE</t>
+  </si>
+  <si>
+    <t>MATURE_DATE</t>
+  </si>
+  <si>
+    <t>DATE_BEGIN_RATE_CHANGE</t>
+  </si>
+  <si>
+    <t>BALANCE_LCY</t>
+  </si>
+  <si>
+    <t>TERM_RATE_FTP</t>
+  </si>
+  <si>
+    <t>DAYS_OF_TERM_FTP</t>
+  </si>
+  <si>
+    <t>DAYS_OF_TERM_AR</t>
+  </si>
+  <si>
+    <t>DAYS_OF_TERM_REMAIN</t>
+  </si>
+  <si>
+    <t>LN_EARLY_MATURE_FEE_RATE</t>
+  </si>
+  <si>
+    <t>DECIMAL(10,4)</t>
+  </si>
+  <si>
+    <t>LN_EARLY_MATURE_TERM_COND</t>
+  </si>
+  <si>
+    <t>TERM_REMAIN</t>
+  </si>
+  <si>
+    <t>TERM_RATE</t>
+  </si>
+  <si>
+    <t>TERM_AR</t>
+  </si>
+  <si>
+    <t>FTP_GROUP</t>
+  </si>
+  <si>
+    <t>CONTRACT_TYPE</t>
+  </si>
+  <si>
+    <t>BUSSINESS_UNIT_ID</t>
+  </si>
+  <si>
+    <t>REF_NO</t>
+  </si>
+  <si>
+    <t>PRODUCT</t>
+  </si>
+  <si>
+    <t>BALANCE</t>
+  </si>
+  <si>
+    <t>CATEGORY</t>
+  </si>
+  <si>
+    <t>DECIMAL(10,0)</t>
+  </si>
+  <si>
+    <t>IS_PD</t>
+  </si>
+  <si>
+    <t>PAST_DUE_INT_RATE</t>
+  </si>
+  <si>
+    <t>DATE_CREATED</t>
+  </si>
+  <si>
+    <t>AREA_ID</t>
+  </si>
+  <si>
+    <t>LIQ_FEE_RATE_BY_TERM_REMAIN</t>
+  </si>
+  <si>
+    <t>DECIMAL(13,4)</t>
+  </si>
+  <si>
+    <t>LIQ_FEE_RATE_BY_TERM_RATE</t>
+  </si>
+  <si>
+    <t>INTEREST_TYPE</t>
+  </si>
+  <si>
+    <t>INTEREST_KEY_ID</t>
+  </si>
+  <si>
+    <t>LAST_DATE_INT_CHANGE</t>
+  </si>
+  <si>
+    <t>CLOSE_DATE</t>
+  </si>
+  <si>
+    <t>EX_INTEREST_RATE</t>
+  </si>
+  <si>
+    <t>DECIMAL(12,6)</t>
+  </si>
+  <si>
+    <t>IS_EARLY_MATURE_CHARGE</t>
+  </si>
+  <si>
+    <t>INTEREST_RATE_BY_KEY</t>
+  </si>
+  <si>
+    <t>AMOUNT_AH_INTEREST_RATE</t>
+  </si>
+  <si>
+    <t>CURRENCY_RATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAST(:DATADT AS INT) </t>
+  </si>
+  <si>
+    <t>INT_RT</t>
+  </si>
+  <si>
+    <t>DECIMAL(15,4)</t>
+  </si>
+  <si>
+    <t>TERM_RATE_CHANGE</t>
+  </si>
+  <si>
+    <t>MATURE_FEE_TYPE</t>
+  </si>
+  <si>
+    <t>LN_CL_BY_GL_ID</t>
+  </si>
+  <si>
+    <t>IS_OVERDUE</t>
+  </si>
+  <si>
+    <t>FTP_BEFORE_RECAL_RATE</t>
+  </si>
+  <si>
+    <t>DATE_END_RECAL</t>
+  </si>
+  <si>
+    <t>BUSINESS_UNIT_TYPE</t>
+  </si>
+  <si>
+    <t>MARGIN_RATE</t>
+  </si>
+  <si>
+    <t>FTP_CONTRACT
+JOIN SCHEMA — FTP_CONTRACT</t>
+  </si>
+  <si>
+    <t>FIELD MAPPING — FTP_CONTRACT</t>
+  </si>
+  <si>
+    <t>IS_NEW_PD</t>
+  </si>
+  <si>
+    <t>V_FTP_INTEREST_RATE_NIM_ON
+JOIN SCHEMA — V_FTP_INTEREST_RATE_NIM_ON</t>
+  </si>
+  <si>
+    <t>FTP_RATE_LIST_HIST</t>
+  </si>
+  <si>
+    <t>Where TERM = 'ON' and INTEREST_KEY_ID = 1 and INT_RATE_TYPE = 'BUY'</t>
+  </si>
+  <si>
+    <t>FIELD MAPPING — V_FTP_INTEREST_RATE_NIM_ON</t>
+  </si>
+  <si>
+    <t>V_FTP_INTEREST_RATE_NIM_ON</t>
+  </si>
+  <si>
+    <t>FROM_DATE</t>
+  </si>
+  <si>
+    <t>RATE</t>
+  </si>
+  <si>
+    <t>FTP_RATE_LIST_HIST
+JOIN SCHEMA — FTP_RATE_LIST_HIST</t>
+  </si>
+  <si>
+    <t>FIELD MAPPING — FTP_RATE_LIST_HIST</t>
+  </si>
+  <si>
+    <t>Transform Type</t>
+  </si>
+  <si>
+    <t>LAST_UPDATED</t>
+  </si>
+  <si>
+    <t>USER_APPROVED</t>
+  </si>
+  <si>
+    <t>USER_CREATED</t>
+  </si>
+  <si>
+    <t>DAYS_TO</t>
+  </si>
+  <si>
+    <t>DAYS_FROM</t>
+  </si>
+  <si>
+    <t>LAST_DATE_CHANGE</t>
   </si>
   <si>
     <t>sts_deleted AS (
@@ -1895,7 +2264,7 @@
     LEFT JOIN bm_latest bm       ON bm.branch_hashkey = h.branch_hashkey
     LEFT JOIN hub_active prn_hub ON prn_hub.business_key = bm.parent_branch_code
     LEFT JOIN sat_latest prn_si  ON prn_hub.branch_hashkey = prn_si.branch_hashkey
-    LEFT JOIN ou_area_mapping am ON am.OU_ID = h.business_key
+    LEFT JOIN area_map am        ON am.OU_ID = h.business_key
     WHERE UPPER(COALESCE(si.t_company_name, '')) &lt;&gt; 'NOT USED'
       AND h.business_key &lt;&gt; 'VN0010001'
 )</t>
@@ -1904,16 +2273,20 @@
     <t>source_data</t>
   </si>
   <si>
-    <t>Build source. Self-join hub_active/sat_latest cho parent (prn_hub, prn_si) qua bm.parent_branch_code. am = ou_area_mapping. Loc 'NOT USED' &amp; VN0010001</t>
-  </si>
-  <si>
-    <t>max_id AS (
-    SELECT COALESCE(MAX(OU_DIM_ID), 0) AS max_val
-    FROM CB_OU_DIM
+    <t>Build source. Self-join hub_active/sat_latest cho parent (prn_hub, prn_si) qua bm.parent_branch_code. am = area_map CTE (fix WARN 3.3: join qua CTE da loc thay ou_area_mapping truc tiep). Loc 'NOT USED' &amp; VN0010001</t>
+  </si>
+  <si>
+    <t>area_map AS (
+    SELECT OU_ID, CB_AREA_ID, CB_AREA_NM
+    FROM ou_area_mapping
+    WHERE CB_AREA_ID IS NOT NULL
 )</t>
   </si>
   <si>
-    <t>MAX(OU_DIM_ID) hien tai -&gt; sinh surrogate key moi (max_val + ROW_NUMBER)</t>
+    <t>area_map</t>
+  </si>
+  <si>
+    <t>Loc truoc ou_area_mapping (fix WARN 3.3): chi lay dong co CB_AREA_ID IS NOT NULL, tranh join nhan ban truoc khi LEFT JOIN vao source_data</t>
   </si>
   <si>
     <t>changed AS (
@@ -1939,14 +2312,13 @@
   <si>
     <t>new_records AS (
     SELECT 'NEW' AS rec_type,
+        CASE WHEN tgt_chk.OU_ID IS NULL THEN 'I' ELSE 'U' END AS CDC_FLAG,
         src.OU_ID, src.OU_NM, src.OU_CODE,
         src.PRN_OU_ID, src.PRN_OU_NM, src.PRN_OU_CODE,
         src.CB_AREA_ID, src.CB_AREA_NM,
         src.source_event_date, src.OU_ADR, src.OU_PH,
-        CASE WHEN tgt_chk.OU_ID IS NULL THEN 'I' ELSE 'U' END AS CDC_FLAG,
-        m.max_val + ROW_NUMBER() OVER (ORDER BY src.OU_ID) AS NEW_OU_DIM_ID
+        uuid() AS NEW_OU_DIM_ID
     FROM source_data src
-    CROSS JOIN max_id m
     LEFT JOIN CB_OU_DIM tgt_chk
         ON  src.OU_ID = tgt_chk.OU_ID
         AND tgt_chk.EFF_TO_DT IS NULL
@@ -1958,7 +2330,7 @@
     <t>new_records</t>
   </si>
   <si>
-    <t>Ban ghi moi (I) hoac thay doi (U): sinh OU_DIM_ID = max_val + ROW_NUMBER. EFF_FM_DT = target_date, EFF_TO_DT = NULL</t>
+    <t>Ban ghi moi (I) hoac thay doi (U): NEW_OU_DIM_ID = uuid() (fix 2.5/2.6, khong con dung max_id+ROW_NUMBER, idempotent). EFF_FM_DT = target_date, EFF_TO_DT = NULL</t>
   </si>
   <si>
     <t>close_records AS (
@@ -1984,10 +2356,12 @@
     <t>Ban ghi can dong (D): branch thay doi (co trong changed) hoac khong con trong source. EFF_TO_DT = target_date - 1, CDC_FLAG='D'</t>
   </si>
   <si>
-    <t>-- FINAL SELECT (USING src)
-SELECT * FROM new_records
+    <t>-- FINAL SELECT (fix 3.1: liet ke tuong minh, bo SELECT *)
+SELECT rec_type, CDC_FLAG, OU_ID, OU_NM, OU_CODE, PRN_OU_ID, PRN_OU_NM, PRN_OU_CODE, CB_AREA_ID, CB_AREA_NM, source_event_date, OU_ADR, OU_PH, NEW_OU_DIM_ID
+FROM new_records
 UNION ALL
-SELECT * FROM close_records</t>
+SELECT rec_type, CDC_FLAG, OU_ID, OU_NM, OU_CODE, PRN_OU_ID, PRN_OU_NM, PRN_OU_CODE, CB_AREA_ID, CB_AREA_NM, source_event_date, OU_ADR, OU_PH, NEW_OU_DIM_ID
+FROM close_records</t>
   </si>
   <si>
     <t>src</t>
@@ -2007,19 +2381,16 @@
     <t>OU_DIM_ID</t>
   </si>
   <si>
-    <t>COALESCE(MAX(OU_DIM_ID),0) + ROW_NUMBER() OVER (ORDER BY src.OU_ID)</t>
-  </si>
-  <si>
     <t>map</t>
   </si>
   <si>
-    <t>hub.branch_hashkey</t>
+    <t>h.branch_hashkey</t>
   </si>
   <si>
     <t>SUBSTRING_INDEX(si.t_company_name, '::', 1)</t>
   </si>
   <si>
-    <t>hub.business_key</t>
+    <t>h.business_key</t>
   </si>
   <si>
     <t>prn_hub.branch_hashkey</t>
@@ -2028,10 +2399,10 @@
     <t>SUBSTRING_INDEX(prn_si.t_company_name, '::', 1)</t>
   </si>
   <si>
-    <t>am.CB_AREA_ID</t>
-  </si>
-  <si>
-    <t>am.CB_AREA_NM</t>
+    <t>am.CB_AREA_ID  (am = area_map CTE, đã lọc CB_AREA_ID IS NOT NULL)</t>
+  </si>
+  <si>
+    <t>am.CB_AREA_NM  (am = area_map CTE, đã lọc CB_AREA_ID IS NOT NULL)</t>
   </si>
   <si>
     <t>CURRENT_TIMESTAMP()</t>
@@ -2040,7 +2411,7 @@
     <t>TO_DATE(:etl_date, 'yyyyMMdd')</t>
   </si>
   <si>
-    <t>hub.source_event_date</t>
+    <t>h.source_event_date</t>
   </si>
   <si>
     <t>OU_ADR</t>
@@ -2053,356 +2424,6 @@
   </si>
   <si>
     <t>bm.phone_number</t>
-  </si>
-  <si>
-    <t>V_FTP_RATE — VIEW</t>
-  </si>
-  <si>
-    <t>JOIN SCHEMA — V_FTP_RATE</t>
-  </si>
-  <si>
-    <t>LD_FTP_RATE</t>
-  </si>
-  <si>
-    <t>FROM LD_FTP_RATE</t>
-  </si>
-  <si>
-    <t>FIELD MAPPING — V_FTP_RATE</t>
-  </si>
-  <si>
-    <t>V_FTP_RATE</t>
-  </si>
-  <si>
-    <t>AR_NO</t>
-  </si>
-  <si>
-    <t>PD_FTP_RATE</t>
-  </si>
-  <si>
-    <t>SYSTEM_ID</t>
-  </si>
-  <si>
-    <t>PTPT</t>
-  </si>
-  <si>
-    <t>(CASE WHEN SYSTEM_ID Like '%PHAITHU%' THEN 1
-			WHEN SYSTEM_ID Like '%PHAITRA%' THEN 1
-			WHEN SYSTEM_ID Like '%TSCOKHAC%' THEN 1
-			else 0 end) as PTPT</t>
-  </si>
-  <si>
-    <t>LD_FTP_RATE — VIEW</t>
-  </si>
-  <si>
-    <t>JOIN SCHEMA — LD_FTP_RATE</t>
-  </si>
-  <si>
-    <t>V_LD_FTP_RATE</t>
-  </si>
-  <si>
-    <t>FIELD MAPPING — LD_FTP_RATE</t>
-  </si>
-  <si>
-    <t>GL_ACCOUNT</t>
-  </si>
-  <si>
-    <t>V_LD_FTP_RATE — VIEW
-JOIN SCHEMA — V_LD_FTP_RATE</t>
-  </si>
-  <si>
-    <t>FTP_CONTRACT_HIST</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
-    <t>FIELD MAPPING — V_LD_FTP_RATE</t>
-  </si>
-  <si>
-    <t>h.SYSTEM_ID</t>
-  </si>
-  <si>
-    <t>h.DATA_DATE</t>
-  </si>
-  <si>
-    <t>h.AR_NO</t>
-  </si>
-  <si>
-    <t>CAST(SUM(CASE WHEN SUBSTR(h.REF_NO, 1, 2) = 'PD' THEN 0
-                  ELSE h.TOTAL_INT_RATE END) AS DECIMAL(20,4))  AS FTP_RATE</t>
-  </si>
-  <si>
-    <t>CAST(SUM(CASE WHEN SUBSTR(h.REF_NO, 1, 2) &lt;&gt; 'PD'
-                   AND h.SYSTEM_ID = 'CHOVAYKH'               THEN 0
-                  ELSE h.TOTAL_INT_RATE END) AS DECIMAL(20,4)) AS PD_FTP_RATE</t>
-  </si>
-  <si>
-    <t>h.GL_ACCOUNT</t>
-  </si>
-  <si>
-    <t>FTP_CONTRACT_HIST
-JOIN SCHEMA — FTP_CONTRACT_HIST</t>
-  </si>
-  <si>
-    <t>FTP_CONTRACT</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> where status=1</t>
-  </si>
-  <si>
-    <t>FIELD MAPPING — FTP_CONTRACT_HIST</t>
-  </si>
-  <si>
-    <t>STATUS</t>
-  </si>
-  <si>
-    <t>SMALLINT</t>
-  </si>
-  <si>
-    <t>DATE_UPDATE</t>
-  </si>
-  <si>
-    <t>CHANGE_CODE</t>
-  </si>
-  <si>
-    <t>TINYINT</t>
-  </si>
-  <si>
-    <t>TOTAL_INT_RATE</t>
-  </si>
-  <si>
-    <t>DECIMAL(20,4)</t>
-  </si>
-  <si>
-    <t>LIQ_RATE</t>
-  </si>
-  <si>
-    <t>EX_TERM_RATE</t>
-  </si>
-  <si>
-    <t>EX_LAST_CHANGE_DATE</t>
-  </si>
-  <si>
-    <t>EX_NEW_DATE_NEXT_RATE_CHANGE</t>
-  </si>
-  <si>
-    <t>CONTRACT_DATE</t>
-  </si>
-  <si>
-    <t>PASTDUE_DAYS</t>
-  </si>
-  <si>
-    <t>DATE_NEXT_RATE_CHANGE</t>
-  </si>
-  <si>
-    <t>VALUE_DATE</t>
-  </si>
-  <si>
-    <t>MATURE_DATE</t>
-  </si>
-  <si>
-    <t>DATE_BEGIN_RATE_CHANGE</t>
-  </si>
-  <si>
-    <t>BALANCE_LCY</t>
-  </si>
-  <si>
-    <t>TERM_RATE_FTP</t>
-  </si>
-  <si>
-    <t>DAYS_OF_TERM_FTP</t>
-  </si>
-  <si>
-    <t>DAYS_OF_TERM_AR</t>
-  </si>
-  <si>
-    <t>DAYS_OF_TERM_REMAIN</t>
-  </si>
-  <si>
-    <t>LN_EARLY_MATURE_FEE_RATE</t>
-  </si>
-  <si>
-    <t>DECIMAL(10,4)</t>
-  </si>
-  <si>
-    <t>LN_EARLY_MATURE_TERM_COND</t>
-  </si>
-  <si>
-    <t>TERM_REMAIN</t>
-  </si>
-  <si>
-    <t>TERM_RATE</t>
-  </si>
-  <si>
-    <t>TERM_AR</t>
-  </si>
-  <si>
-    <t>FTP_GROUP</t>
-  </si>
-  <si>
-    <t>CONTRACT_TYPE</t>
-  </si>
-  <si>
-    <t>BUSSINESS_UNIT_ID</t>
-  </si>
-  <si>
-    <t>REF_NO</t>
-  </si>
-  <si>
-    <t>PRODUCT</t>
-  </si>
-  <si>
-    <t>BALANCE</t>
-  </si>
-  <si>
-    <t>CATEGORY</t>
-  </si>
-  <si>
-    <t>DECIMAL(10,0)</t>
-  </si>
-  <si>
-    <t>IS_PD</t>
-  </si>
-  <si>
-    <t>PAST_DUE_INT_RATE</t>
-  </si>
-  <si>
-    <t>DATE_CREATED</t>
-  </si>
-  <si>
-    <t>AREA_ID</t>
-  </si>
-  <si>
-    <t>LIQ_FEE_RATE_BY_TERM_REMAIN</t>
-  </si>
-  <si>
-    <t>DECIMAL(13,4)</t>
-  </si>
-  <si>
-    <t>LIQ_FEE_RATE_BY_TERM_RATE</t>
-  </si>
-  <si>
-    <t>INTEREST_TYPE</t>
-  </si>
-  <si>
-    <t>INTEREST_KEY_ID</t>
-  </si>
-  <si>
-    <t>LAST_DATE_INT_CHANGE</t>
-  </si>
-  <si>
-    <t>CLOSE_DATE</t>
-  </si>
-  <si>
-    <t>EX_INTEREST_RATE</t>
-  </si>
-  <si>
-    <t>DECIMAL(12,6)</t>
-  </si>
-  <si>
-    <t>IS_EARLY_MATURE_CHARGE</t>
-  </si>
-  <si>
-    <t>INTEREST_RATE_BY_KEY</t>
-  </si>
-  <si>
-    <t>AMOUNT_AH_INTEREST_RATE</t>
-  </si>
-  <si>
-    <t>CURRENCY_RATE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAST(:DATADT AS INT) </t>
-  </si>
-  <si>
-    <t>INT_RT</t>
-  </si>
-  <si>
-    <t>DECIMAL(15,4)</t>
-  </si>
-  <si>
-    <t>TERM_RATE_CHANGE</t>
-  </si>
-  <si>
-    <t>MATURE_FEE_TYPE</t>
-  </si>
-  <si>
-    <t>LN_CL_BY_GL_ID</t>
-  </si>
-  <si>
-    <t>IS_OVERDUE</t>
-  </si>
-  <si>
-    <t>FTP_BEFORE_RECAL_RATE</t>
-  </si>
-  <si>
-    <t>DATE_END_RECAL</t>
-  </si>
-  <si>
-    <t>BUSINESS_UNIT_TYPE</t>
-  </si>
-  <si>
-    <t>MARGIN_RATE</t>
-  </si>
-  <si>
-    <t>FTP_CONTRACT
-JOIN SCHEMA — FTP_CONTRACT</t>
-  </si>
-  <si>
-    <t>FIELD MAPPING — FTP_CONTRACT</t>
-  </si>
-  <si>
-    <t>IS_NEW_PD</t>
-  </si>
-  <si>
-    <t>V_FTP_INTEREST_RATE_NIM_ON
-JOIN SCHEMA — V_FTP_INTEREST_RATE_NIM_ON</t>
-  </si>
-  <si>
-    <t>FTP_RATE_LIST_HIST</t>
-  </si>
-  <si>
-    <t>Where TERM = 'ON' and INTEREST_KEY_ID = 1 and INT_RATE_TYPE = 'BUY'</t>
-  </si>
-  <si>
-    <t>FIELD MAPPING — V_FTP_INTEREST_RATE_NIM_ON</t>
-  </si>
-  <si>
-    <t>V_FTP_INTEREST_RATE_NIM_ON</t>
-  </si>
-  <si>
-    <t>FROM_DATE</t>
-  </si>
-  <si>
-    <t>RATE</t>
-  </si>
-  <si>
-    <t>FTP_RATE_LIST_HIST
-JOIN SCHEMA — FTP_RATE_LIST_HIST</t>
-  </si>
-  <si>
-    <t>FIELD MAPPING — FTP_RATE_LIST_HIST</t>
-  </si>
-  <si>
-    <t>Transform Type</t>
-  </si>
-  <si>
-    <t>LAST_UPDATED</t>
-  </si>
-  <si>
-    <t>USER_APPROVED</t>
-  </si>
-  <si>
-    <t>USER_CREATED</t>
-  </si>
-  <si>
-    <t>DAYS_TO</t>
-  </si>
-  <si>
-    <t>DAYS_FROM</t>
-  </si>
-  <si>
-    <t>LAST_DATE_CHANGE</t>
   </si>
 </sst>
 </file>
@@ -3734,9 +3755,6 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -3746,7 +3764,6 @@
     <xf numFmtId="0" fontId="38" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -3835,7 +3852,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3890,260 +3906,267 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4162,7 +4185,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -4529,17 +4552,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="30" customHeight="1">
-      <c r="A1" s="191" t="s">
+      <c r="A1" s="197" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="192"/>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="192"/>
-      <c r="F1" s="192"/>
-      <c r="G1" s="192"/>
-      <c r="H1" s="192"/>
-      <c r="I1" s="143"/>
+      <c r="B1" s="198"/>
+      <c r="C1" s="198"/>
+      <c r="D1" s="198"/>
+      <c r="E1" s="198"/>
+      <c r="F1" s="198"/>
+      <c r="G1" s="198"/>
+      <c r="H1" s="198"/>
+      <c r="I1" s="141"/>
       <c r="J1" s="39"/>
       <c r="K1" s="39"/>
       <c r="L1" s="39"/>
@@ -4581,44 +4604,44 @@
       <c r="AV1" s="39"/>
     </row>
     <row r="2" spans="1:48">
-      <c r="A2" s="203" t="s">
+      <c r="A2" s="191" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="203"/>
-      <c r="C2" s="206" t="s">
+      <c r="B2" s="191"/>
+      <c r="C2" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="193" t="s">
+      <c r="D2" s="199" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="193"/>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
-      <c r="H2" s="170"/>
+      <c r="E2" s="199"/>
+      <c r="F2" s="167"/>
+      <c r="G2" s="167"/>
+      <c r="H2" s="167"/>
     </row>
     <row r="3" spans="1:48">
-      <c r="A3" s="204"/>
-      <c r="B3" s="204"/>
-      <c r="C3" s="207"/>
-      <c r="D3" s="194"/>
-      <c r="E3" s="194"/>
-      <c r="F3" s="170"/>
-      <c r="G3" s="170"/>
-      <c r="H3" s="170"/>
+      <c r="A3" s="192"/>
+      <c r="B3" s="192"/>
+      <c r="C3" s="195"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="200"/>
+      <c r="F3" s="167"/>
+      <c r="G3" s="167"/>
+      <c r="H3" s="167"/>
     </row>
     <row r="4" spans="1:48">
-      <c r="A4" s="204"/>
-      <c r="B4" s="204"/>
-      <c r="C4" s="207"/>
-      <c r="D4" s="194"/>
-      <c r="E4" s="194"/>
-      <c r="F4" s="170"/>
-      <c r="G4" s="170"/>
-      <c r="H4" s="170"/>
+      <c r="A4" s="192"/>
+      <c r="B4" s="192"/>
+      <c r="C4" s="195"/>
+      <c r="D4" s="200"/>
+      <c r="E4" s="200"/>
+      <c r="F4" s="167"/>
+      <c r="G4" s="167"/>
+      <c r="H4" s="167"/>
     </row>
     <row r="5" spans="1:48" ht="18.75" customHeight="1">
-      <c r="A5" s="204"/>
-      <c r="B5" s="204"/>
+      <c r="A5" s="192"/>
+      <c r="B5" s="192"/>
       <c r="C5" s="33"/>
       <c r="D5" s="33"/>
       <c r="E5" s="33"/>
@@ -4627,60 +4650,60 @@
       <c r="H5" s="33"/>
     </row>
     <row r="6" spans="1:48">
-      <c r="A6" s="204"/>
-      <c r="B6" s="204"/>
-      <c r="C6" s="207" t="s">
+      <c r="A6" s="192"/>
+      <c r="B6" s="192"/>
+      <c r="C6" s="195" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="195" t="s">
+      <c r="D6" s="201" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="195"/>
-      <c r="F6" s="198" t="s">
+      <c r="E6" s="201"/>
+      <c r="F6" s="204" t="s">
         <v>2</v>
       </c>
-      <c r="G6" s="199" t="s">
+      <c r="G6" s="205" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="199"/>
+      <c r="H6" s="205"/>
     </row>
     <row r="7" spans="1:48" ht="30.75" customHeight="1">
-      <c r="A7" s="204"/>
-      <c r="B7" s="204"/>
-      <c r="C7" s="207"/>
-      <c r="D7" s="195"/>
-      <c r="E7" s="195"/>
-      <c r="F7" s="198"/>
-      <c r="G7" s="199"/>
-      <c r="H7" s="199"/>
+      <c r="A7" s="192"/>
+      <c r="B7" s="192"/>
+      <c r="C7" s="195"/>
+      <c r="D7" s="201"/>
+      <c r="E7" s="201"/>
+      <c r="F7" s="204"/>
+      <c r="G7" s="205"/>
+      <c r="H7" s="205"/>
     </row>
     <row r="8" spans="1:48" ht="25.5" customHeight="1">
-      <c r="A8" s="204"/>
-      <c r="B8" s="204"/>
-      <c r="C8" s="207"/>
-      <c r="D8" s="195"/>
-      <c r="E8" s="195"/>
+      <c r="A8" s="192"/>
+      <c r="B8" s="192"/>
+      <c r="C8" s="195"/>
+      <c r="D8" s="201"/>
+      <c r="E8" s="201"/>
       <c r="F8"/>
       <c r="G8"/>
       <c r="H8"/>
     </row>
     <row r="9" spans="1:48" ht="71.25" customHeight="1">
-      <c r="A9" s="204"/>
-      <c r="B9" s="204"/>
-      <c r="C9" s="207"/>
-      <c r="D9" s="195"/>
-      <c r="E9" s="195"/>
-      <c r="F9" s="169" t="s">
+      <c r="A9" s="192"/>
+      <c r="B9" s="192"/>
+      <c r="C9" s="195"/>
+      <c r="D9" s="201"/>
+      <c r="E9" s="201"/>
+      <c r="F9" s="166" t="s">
         <v>2</v>
       </c>
-      <c r="G9" s="200" t="s">
+      <c r="G9" s="206" t="s">
         <v>6</v>
       </c>
-      <c r="H9" s="200"/>
+      <c r="H9" s="206"/>
     </row>
     <row r="10" spans="1:48" ht="18.75" customHeight="1">
-      <c r="A10" s="204"/>
-      <c r="B10" s="204"/>
+      <c r="A10" s="192"/>
+      <c r="B10" s="192"/>
       <c r="C10" s="33"/>
       <c r="D10" s="33"/>
       <c r="E10" s="33"/>
@@ -4689,44 +4712,44 @@
       <c r="H10" s="33"/>
     </row>
     <row r="11" spans="1:48">
-      <c r="A11" s="204"/>
-      <c r="B11" s="204"/>
-      <c r="C11" s="207" t="s">
+      <c r="A11" s="192"/>
+      <c r="B11" s="192"/>
+      <c r="C11" s="195" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="196" t="s">
+      <c r="D11" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="196"/>
-      <c r="F11" s="170"/>
-      <c r="G11" s="170"/>
-      <c r="H11" s="170"/>
+      <c r="E11" s="202"/>
+      <c r="F11" s="167"/>
+      <c r="G11" s="167"/>
+      <c r="H11" s="167"/>
     </row>
     <row r="12" spans="1:48">
-      <c r="A12" s="204"/>
-      <c r="B12" s="204"/>
-      <c r="C12" s="207"/>
-      <c r="D12" s="196"/>
-      <c r="E12" s="196"/>
-      <c r="F12" s="170"/>
-      <c r="G12" s="170"/>
-      <c r="H12" s="170"/>
+      <c r="A12" s="192"/>
+      <c r="B12" s="192"/>
+      <c r="C12" s="195"/>
+      <c r="D12" s="202"/>
+      <c r="E12" s="202"/>
+      <c r="F12" s="167"/>
+      <c r="G12" s="167"/>
+      <c r="H12" s="167"/>
     </row>
     <row r="13" spans="1:48">
-      <c r="A13" s="205"/>
-      <c r="B13" s="205"/>
-      <c r="C13" s="208"/>
-      <c r="D13" s="197"/>
-      <c r="E13" s="197"/>
-      <c r="F13" s="170"/>
-      <c r="G13" s="170"/>
-      <c r="H13" s="170"/>
+      <c r="A13" s="193"/>
+      <c r="B13" s="193"/>
+      <c r="C13" s="196"/>
+      <c r="D13" s="203"/>
+      <c r="E13" s="203"/>
+      <c r="F13" s="167"/>
+      <c r="G13" s="167"/>
+      <c r="H13" s="167"/>
     </row>
     <row r="14" spans="1:48">
-      <c r="A14" s="201" t="s">
+      <c r="A14" s="189" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="202"/>
+      <c r="B14" s="190"/>
       <c r="C14" s="272"/>
       <c r="D14" s="272"/>
       <c r="E14" s="272"/>
@@ -4781,20 +4804,15 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="171" t="s">
+      <c r="A23" s="168" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="171" t="s">
+      <c r="B23" s="168" t="s">
         <v>16</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A2:B13"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="C6:C9"/>
-    <mergeCell ref="C11:C13"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="D6:E9"/>
@@ -4802,601 +4820,17 @@
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="G6:H7"/>
     <mergeCell ref="G9:H9"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A2:B13"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="C6:C9"/>
+    <mergeCell ref="C11:C13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F30B291-4DB7-4B60-9AA4-2E6486676981}">
-  <dimension ref="A1:H29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="44.42578125" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" customWidth="1"/>
-    <col min="5" max="5" width="21.42578125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="74.28515625" customWidth="1"/>
-    <col min="7" max="7" width="69.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="153" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="153"/>
-      <c r="C1" s="153"/>
-      <c r="D1" s="153"/>
-      <c r="E1" s="153"/>
-      <c r="F1" s="134"/>
-      <c r="G1" s="102"/>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="154" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="153" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="153" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="153" t="s">
-        <v>34</v>
-      </c>
-      <c r="E2" s="155" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" s="103"/>
-      <c r="G2" s="102"/>
-    </row>
-    <row r="3" spans="1:8" ht="152.25">
-      <c r="A3" s="156">
-        <v>1</v>
-      </c>
-      <c r="B3" s="157" t="s">
-        <v>356</v>
-      </c>
-      <c r="C3" s="156" t="s">
-        <v>357</v>
-      </c>
-      <c r="D3" s="158" t="s">
-        <v>303</v>
-      </c>
-      <c r="E3" s="167" t="s">
-        <v>358</v>
-      </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="102"/>
-    </row>
-    <row r="4" spans="1:8" ht="137.25">
-      <c r="A4" s="159">
-        <v>2</v>
-      </c>
-      <c r="B4" s="160" t="s">
-        <v>359</v>
-      </c>
-      <c r="C4" s="161" t="s">
-        <v>360</v>
-      </c>
-      <c r="D4" s="161" t="s">
-        <v>303</v>
-      </c>
-      <c r="E4" s="162" t="s">
-        <v>361</v>
-      </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="104"/>
-    </row>
-    <row r="5" spans="1:8" ht="167.25">
-      <c r="A5" s="159">
-        <v>3</v>
-      </c>
-      <c r="B5" s="160" t="s">
-        <v>362</v>
-      </c>
-      <c r="C5" s="161" t="s">
-        <v>363</v>
-      </c>
-      <c r="D5" s="161" t="s">
-        <v>303</v>
-      </c>
-      <c r="E5" s="162" t="s">
-        <v>364</v>
-      </c>
-      <c r="F5" s="103"/>
-      <c r="G5" s="104"/>
-    </row>
-    <row r="6" spans="1:8" ht="229.5">
-      <c r="A6" s="159">
-        <v>4</v>
-      </c>
-      <c r="B6" s="160" t="s">
-        <v>365</v>
-      </c>
-      <c r="C6" s="161" t="s">
-        <v>309</v>
-      </c>
-      <c r="D6" s="161" t="s">
-        <v>303</v>
-      </c>
-      <c r="E6" s="162" t="s">
-        <v>366</v>
-      </c>
-      <c r="F6" s="103"/>
-      <c r="G6" s="104"/>
-    </row>
-    <row r="7" spans="1:8" ht="409.6">
-      <c r="A7" s="163">
-        <v>5</v>
-      </c>
-      <c r="B7" s="160" t="s">
-        <v>367</v>
-      </c>
-      <c r="C7" s="164" t="s">
-        <v>368</v>
-      </c>
-      <c r="D7" s="164" t="s">
-        <v>303</v>
-      </c>
-      <c r="E7" s="165" t="s">
-        <v>369</v>
-      </c>
-      <c r="F7" s="103"/>
-      <c r="G7" s="104"/>
-    </row>
-    <row r="8" spans="1:8" ht="76.5">
-      <c r="A8" s="163">
-        <v>6</v>
-      </c>
-      <c r="B8" s="160" t="s">
-        <v>370</v>
-      </c>
-      <c r="C8" s="164" t="s">
-        <v>312</v>
-      </c>
-      <c r="D8" s="164" t="s">
-        <v>303</v>
-      </c>
-      <c r="E8" s="165" t="s">
-        <v>371</v>
-      </c>
-      <c r="F8" s="103"/>
-      <c r="G8" s="104"/>
-    </row>
-    <row r="9" spans="1:8" ht="290.25">
-      <c r="A9" s="163">
-        <v>7</v>
-      </c>
-      <c r="B9" s="160" t="s">
-        <v>372</v>
-      </c>
-      <c r="C9" s="164" t="s">
-        <v>373</v>
-      </c>
-      <c r="D9" s="164" t="s">
-        <v>303</v>
-      </c>
-      <c r="E9" s="165" t="s">
-        <v>374</v>
-      </c>
-      <c r="F9" s="103"/>
-      <c r="G9" s="104"/>
-    </row>
-    <row r="10" spans="1:8" ht="321">
-      <c r="A10" s="163">
-        <v>8</v>
-      </c>
-      <c r="B10" s="160" t="s">
-        <v>375</v>
-      </c>
-      <c r="C10" s="164" t="s">
-        <v>376</v>
-      </c>
-      <c r="D10" s="164" t="s">
-        <v>303</v>
-      </c>
-      <c r="E10" s="165" t="s">
-        <v>377</v>
-      </c>
-      <c r="F10" s="103"/>
-      <c r="G10" s="104"/>
-    </row>
-    <row r="11" spans="1:8" ht="275.25">
-      <c r="A11" s="163">
-        <v>9</v>
-      </c>
-      <c r="B11" s="160" t="s">
-        <v>378</v>
-      </c>
-      <c r="C11" s="164" t="s">
-        <v>379</v>
-      </c>
-      <c r="D11" s="164" t="s">
-        <v>303</v>
-      </c>
-      <c r="E11" s="165" t="s">
-        <v>380</v>
-      </c>
-      <c r="F11" s="137"/>
-      <c r="G11" s="105"/>
-    </row>
-    <row r="12" spans="1:8" ht="148.5">
-      <c r="A12" s="163">
-        <v>10</v>
-      </c>
-      <c r="B12" s="166" t="s">
-        <v>381</v>
-      </c>
-      <c r="C12" s="164" t="s">
-        <v>382</v>
-      </c>
-      <c r="D12" s="164" t="s">
-        <v>383</v>
-      </c>
-      <c r="E12" s="165" t="s">
-        <v>384</v>
-      </c>
-      <c r="F12" s="137"/>
-      <c r="G12" s="105"/>
-    </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1">
-      <c r="A13" s="189" t="s">
-        <v>229</v>
-      </c>
-      <c r="B13" s="189"/>
-      <c r="C13" s="189"/>
-      <c r="D13" s="189"/>
-      <c r="E13" s="189"/>
-      <c r="F13" s="190"/>
-      <c r="G13" s="142"/>
-    </row>
-    <row r="14" spans="1:8" ht="27">
-      <c r="A14" s="135" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="136" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="136" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" s="136" t="s">
-        <v>385</v>
-      </c>
-      <c r="E14" s="136" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="141" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14" s="140"/>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="138">
-        <v>1</v>
-      </c>
-      <c r="B15" s="139" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="139" t="s">
-        <v>386</v>
-      </c>
-      <c r="D15" s="144" t="s">
-        <v>321</v>
-      </c>
-      <c r="E15" s="145" t="s">
-        <v>235</v>
-      </c>
-      <c r="F15" s="139" t="s">
-        <v>387</v>
-      </c>
-      <c r="G15" s="105"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="129">
-        <v>2</v>
-      </c>
-      <c r="B16" s="130" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="130" t="s">
-        <v>290</v>
-      </c>
-      <c r="D16" s="146" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" s="147" t="s">
-        <v>388</v>
-      </c>
-      <c r="F16" s="130" t="s">
-        <v>389</v>
-      </c>
-      <c r="G16" s="105"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="129">
-        <v>3</v>
-      </c>
-      <c r="B17" s="130" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="130" t="s">
-        <v>330</v>
-      </c>
-      <c r="D17" s="148" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17" s="147" t="s">
-        <v>235</v>
-      </c>
-      <c r="F17" s="130" t="s">
-        <v>390</v>
-      </c>
-      <c r="G17" s="105"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="129">
-        <v>4</v>
-      </c>
-      <c r="B18" s="130" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="130" t="s">
-        <v>332</v>
-      </c>
-      <c r="D18" s="148" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="147" t="s">
-        <v>388</v>
-      </c>
-      <c r="F18" s="130" t="s">
-        <v>391</v>
-      </c>
-      <c r="G18" s="105"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="131">
-        <v>5</v>
-      </c>
-      <c r="B19" s="130" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="132" t="s">
-        <v>334</v>
-      </c>
-      <c r="D19" s="149" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="150" t="s">
-        <v>388</v>
-      </c>
-      <c r="F19" s="132" t="s">
-        <v>392</v>
-      </c>
-      <c r="G19" s="106"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="129">
-        <v>6</v>
-      </c>
-      <c r="B20" s="130" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="130" t="s">
-        <v>336</v>
-      </c>
-      <c r="D20" s="148" t="s">
-        <v>52</v>
-      </c>
-      <c r="E20" s="147" t="s">
-        <v>235</v>
-      </c>
-      <c r="F20" s="130" t="s">
-        <v>393</v>
-      </c>
-      <c r="G20" s="104"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="129">
-        <v>7</v>
-      </c>
-      <c r="B21" s="130" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="130" t="s">
-        <v>340</v>
-      </c>
-      <c r="D21" s="148" t="s">
-        <v>341</v>
-      </c>
-      <c r="E21" s="147" t="s">
-        <v>388</v>
-      </c>
-      <c r="F21" s="130" t="s">
-        <v>394</v>
-      </c>
-      <c r="G21" s="105"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="129">
-        <v>8</v>
-      </c>
-      <c r="B22" s="130" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="130" t="s">
-        <v>343</v>
-      </c>
-      <c r="D22" s="148" t="s">
-        <v>52</v>
-      </c>
-      <c r="E22" s="147" t="s">
-        <v>388</v>
-      </c>
-      <c r="F22" s="130" t="s">
-        <v>395</v>
-      </c>
-      <c r="G22" s="105"/>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="129">
-        <v>9</v>
-      </c>
-      <c r="B23" s="130" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" s="130" t="s">
-        <v>345</v>
-      </c>
-      <c r="D23" s="148" t="s">
-        <v>346</v>
-      </c>
-      <c r="E23" s="147" t="s">
-        <v>235</v>
-      </c>
-      <c r="F23" s="130" t="s">
-        <v>396</v>
-      </c>
-      <c r="G23" s="105"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="129">
-        <v>10</v>
-      </c>
-      <c r="B24" s="130" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="130" t="s">
-        <v>349</v>
-      </c>
-      <c r="D24" s="148" t="s">
-        <v>67</v>
-      </c>
-      <c r="E24" s="147" t="s">
-        <v>347</v>
-      </c>
-      <c r="F24" s="130" t="s">
-        <v>397</v>
-      </c>
-      <c r="G24" s="105"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="129">
-        <v>11</v>
-      </c>
-      <c r="B25" s="130" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="130" t="s">
-        <v>351</v>
-      </c>
-      <c r="D25" s="148" t="s">
-        <v>67</v>
-      </c>
-      <c r="E25" s="147" t="s">
-        <v>347</v>
-      </c>
-      <c r="F25" s="130" t="s">
-        <v>350</v>
-      </c>
-      <c r="G25" s="105"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="129">
-        <v>12</v>
-      </c>
-      <c r="B26" s="130" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" s="130" t="s">
-        <v>338</v>
-      </c>
-      <c r="D26" s="148" t="s">
-        <v>52</v>
-      </c>
-      <c r="E26" s="147" t="s">
-        <v>388</v>
-      </c>
-      <c r="F26" s="130" t="s">
-        <v>339</v>
-      </c>
-      <c r="G26" s="105"/>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="129">
-        <v>13</v>
-      </c>
-      <c r="B27" s="130" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="130" t="s">
-        <v>352</v>
-      </c>
-      <c r="D27" s="148" t="s">
-        <v>67</v>
-      </c>
-      <c r="E27" s="147" t="s">
-        <v>388</v>
-      </c>
-      <c r="F27" s="130" t="s">
-        <v>398</v>
-      </c>
-      <c r="G27" s="105"/>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="129">
-        <v>14</v>
-      </c>
-      <c r="B28" s="130" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" s="129" t="s">
-        <v>399</v>
-      </c>
-      <c r="D28" s="151" t="s">
-        <v>52</v>
-      </c>
-      <c r="E28" s="152" t="s">
-        <v>388</v>
-      </c>
-      <c r="F28" s="129" t="s">
-        <v>400</v>
-      </c>
-      <c r="G28" s="133"/>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="129">
-        <v>15</v>
-      </c>
-      <c r="B29" s="130" t="s">
-        <v>17</v>
-      </c>
-      <c r="C29" s="129" t="s">
-        <v>401</v>
-      </c>
-      <c r="D29" s="151" t="s">
-        <v>52</v>
-      </c>
-      <c r="E29" s="152" t="s">
-        <v>388</v>
-      </c>
-      <c r="F29" s="129" t="s">
-        <v>402</v>
-      </c>
-      <c r="G29" s="133"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A13:F13"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E46C9CDD-1BE9-4BD4-96A5-21EA191027EB}">
   <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5412,7 +4846,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.6" customHeight="1">
       <c r="A1" s="58" t="s">
-        <v>403</v>
+        <v>356</v>
       </c>
       <c r="B1" s="58"/>
       <c r="C1" s="58"/>
@@ -5421,7 +4855,7 @@
     </row>
     <row r="2" spans="1:7" ht="14.45" customHeight="1">
       <c r="A2" s="58" t="s">
-        <v>404</v>
+        <v>357</v>
       </c>
       <c r="B2" s="58"/>
       <c r="C2" s="58"/>
@@ -5452,14 +4886,14 @@
         <v>1</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>405</v>
+        <v>358</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8" t="s">
         <v>38</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>406</v>
+        <v>359</v>
       </c>
       <c r="G4" s="11"/>
     </row>
@@ -5468,12 +4902,12 @@
     </row>
     <row r="6" spans="1:7" ht="21" customHeight="1">
       <c r="A6" s="58" t="s">
-        <v>407</v>
+        <v>360</v>
       </c>
       <c r="B6" s="58"/>
       <c r="C6" s="58"/>
-      <c r="D6" s="252"/>
-      <c r="E6" s="252"/>
+      <c r="D6" s="251"/>
+      <c r="E6" s="251"/>
       <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7" ht="21" customHeight="1">
@@ -5486,31 +4920,31 @@
       <c r="C7" s="59" t="s">
         <v>182</v>
       </c>
-      <c r="D7" s="253" t="s">
+      <c r="D7" s="252" t="s">
         <v>183</v>
       </c>
-      <c r="E7" s="254"/>
+      <c r="E7" s="253"/>
       <c r="G7" s="11"/>
     </row>
     <row r="8" spans="1:7" ht="21" customHeight="1">
       <c r="A8" s="8" t="s">
-        <v>408</v>
+        <v>361</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>409</v>
+        <v>362</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="250" t="s">
-        <v>409</v>
-      </c>
-      <c r="E8" s="251"/>
+      <c r="D8" s="249" t="s">
+        <v>362</v>
+      </c>
+      <c r="E8" s="250"/>
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" ht="21" customHeight="1">
       <c r="A9" s="8" t="s">
-        <v>408</v>
+        <v>361</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>119</v>
@@ -5518,15 +4952,15 @@
       <c r="C9" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="250" t="s">
+      <c r="D9" s="249" t="s">
         <v>119</v>
       </c>
-      <c r="E9" s="251"/>
+      <c r="E9" s="250"/>
       <c r="G9" s="11"/>
     </row>
     <row r="10" spans="1:7" ht="14.45" customHeight="1">
       <c r="A10" s="8" t="s">
-        <v>408</v>
+        <v>361</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>105</v>
@@ -5534,44 +4968,44 @@
       <c r="C10" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="250" t="s">
+      <c r="D10" s="249" t="s">
         <v>105</v>
       </c>
-      <c r="E10" s="251"/>
+      <c r="E10" s="250"/>
     </row>
     <row r="11" spans="1:7" ht="14.45" customHeight="1">
       <c r="A11" s="8" t="s">
-        <v>408</v>
+        <v>361</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>410</v>
+        <v>363</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="250" t="s">
+      <c r="D11" s="249" t="s">
         <v>107</v>
       </c>
-      <c r="E11" s="251"/>
+      <c r="E11" s="250"/>
     </row>
     <row r="12" spans="1:7" ht="14.45" customHeight="1">
       <c r="A12" s="8" t="s">
-        <v>408</v>
+        <v>361</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>411</v>
+        <v>364</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="250" t="s">
-        <v>411</v>
-      </c>
-      <c r="E12" s="251"/>
+      <c r="D12" s="249" t="s">
+        <v>364</v>
+      </c>
+      <c r="E12" s="250"/>
     </row>
     <row r="13" spans="1:7" ht="14.45" customHeight="1">
       <c r="A13" s="8" t="s">
-        <v>408</v>
+        <v>361</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>66</v>
@@ -5579,25 +5013,25 @@
       <c r="C13" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="250" t="s">
+      <c r="D13" s="249" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="251"/>
+      <c r="E13" s="250"/>
     </row>
     <row r="14" spans="1:7" ht="70.5" customHeight="1">
       <c r="A14" s="8" t="s">
-        <v>408</v>
+        <v>361</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>412</v>
+        <v>365</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="250" t="s">
-        <v>413</v>
-      </c>
-      <c r="E14" s="251"/>
+      <c r="D14" s="249" t="s">
+        <v>366</v>
+      </c>
+      <c r="E14" s="250"/>
     </row>
     <row r="15" spans="1:7" ht="14.45" customHeight="1"/>
   </sheetData>
@@ -5616,7 +5050,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65888E63-9065-4321-B61B-16EA00135A99}">
   <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5632,7 +5066,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.6" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>414</v>
+        <v>367</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -5643,7 +5077,7 @@
     </row>
     <row r="2" spans="1:7" ht="14.45" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>415</v>
+        <v>368</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -5676,7 +5110,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>416</v>
+        <v>369</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8" t="s">
@@ -5694,7 +5128,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="6" t="s">
-        <v>417</v>
+        <v>370</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -5724,26 +5158,26 @@
     </row>
     <row r="8" spans="1:7" ht="14.45" customHeight="1">
       <c r="A8" s="8" t="s">
-        <v>405</v>
+        <v>358</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>410</v>
+        <v>363</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>53</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>410</v>
+        <v>363</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>416</v>
+        <v>369</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" ht="14.45" customHeight="1">
       <c r="A9" s="8" t="s">
-        <v>405</v>
+        <v>358</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>105</v>
@@ -5755,29 +5189,29 @@
         <v>105</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>416</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="14.45" customHeight="1">
       <c r="A10" s="8" t="s">
-        <v>405</v>
+        <v>358</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>409</v>
+        <v>362</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>53</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>409</v>
+        <v>362</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>416</v>
+        <v>369</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="14.45" customHeight="1">
       <c r="A11" s="8" t="s">
-        <v>405</v>
+        <v>358</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>66</v>
@@ -5789,29 +5223,29 @@
         <v>66</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>416</v>
+        <v>369</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.45" customHeight="1">
       <c r="A12" s="8" t="s">
-        <v>405</v>
+        <v>358</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>411</v>
+        <v>364</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>53</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>411</v>
+        <v>364</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>416</v>
+        <v>369</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="14.45" customHeight="1">
       <c r="A13" s="8" t="s">
-        <v>405</v>
+        <v>358</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>119</v>
@@ -5820,10 +5254,10 @@
         <v>53</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>418</v>
+        <v>371</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>416</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -5831,7 +5265,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A17B6E20-B240-45DE-813B-0BB8459EA705}">
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5847,13 +5281,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="41.25" customHeight="1">
-      <c r="A1" s="255" t="s">
-        <v>419</v>
-      </c>
-      <c r="B1" s="256"/>
-      <c r="C1" s="256"/>
-      <c r="D1" s="256"/>
-      <c r="E1" s="256"/>
+      <c r="A1" s="254" t="s">
+        <v>372</v>
+      </c>
+      <c r="B1" s="255"/>
+      <c r="C1" s="255"/>
+      <c r="D1" s="255"/>
+      <c r="E1" s="255"/>
     </row>
     <row r="2" spans="1:5" ht="18.75">
       <c r="A2" s="61" t="s">
@@ -5877,10 +5311,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="62" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="C3" s="62" t="s">
-        <v>421</v>
+        <v>374</v>
       </c>
       <c r="D3" s="62" t="s">
         <v>38</v>
@@ -5895,13 +5329,13 @@
       <c r="E4" s="63"/>
     </row>
     <row r="5" spans="1:5" ht="18.75">
-      <c r="A5" s="256" t="s">
-        <v>422</v>
-      </c>
-      <c r="B5" s="256"/>
-      <c r="C5" s="256"/>
-      <c r="D5" s="256"/>
-      <c r="E5" s="256"/>
+      <c r="A5" s="255" t="s">
+        <v>375</v>
+      </c>
+      <c r="B5" s="255"/>
+      <c r="C5" s="255"/>
+      <c r="D5" s="255"/>
+      <c r="E5" s="255"/>
     </row>
     <row r="6" spans="1:5" ht="18.75">
       <c r="A6" s="61" t="s">
@@ -5922,22 +5356,22 @@
     </row>
     <row r="7" spans="1:5" ht="18.75">
       <c r="A7" s="62" t="s">
-        <v>416</v>
+        <v>369</v>
       </c>
       <c r="B7" s="62" t="s">
-        <v>411</v>
+        <v>364</v>
       </c>
       <c r="C7" s="64" t="s">
         <v>53</v>
       </c>
       <c r="D7" s="62" t="s">
-        <v>423</v>
+        <v>376</v>
       </c>
       <c r="E7" s="62"/>
     </row>
     <row r="8" spans="1:5" ht="18.75">
       <c r="A8" s="62" t="s">
-        <v>416</v>
+        <v>369</v>
       </c>
       <c r="B8" s="62" t="s">
         <v>66</v>
@@ -5946,28 +5380,28 @@
         <v>53</v>
       </c>
       <c r="D8" s="62" t="s">
-        <v>424</v>
+        <v>377</v>
       </c>
       <c r="E8" s="62"/>
     </row>
     <row r="9" spans="1:5" ht="18.75">
       <c r="A9" s="62" t="s">
-        <v>416</v>
+        <v>369</v>
       </c>
       <c r="B9" s="62" t="s">
-        <v>409</v>
+        <v>362</v>
       </c>
       <c r="C9" s="64" t="s">
         <v>53</v>
       </c>
       <c r="D9" s="62" t="s">
-        <v>425</v>
+        <v>378</v>
       </c>
       <c r="E9" s="62"/>
     </row>
     <row r="10" spans="1:5" ht="75.75">
       <c r="A10" s="62" t="s">
-        <v>416</v>
+        <v>369</v>
       </c>
       <c r="B10" s="62" t="s">
         <v>105</v>
@@ -5976,37 +5410,37 @@
         <v>68</v>
       </c>
       <c r="D10" s="62" t="s">
-        <v>426</v>
+        <v>379</v>
       </c>
       <c r="E10" s="62"/>
     </row>
     <row r="11" spans="1:5" ht="113.25">
       <c r="A11" s="62" t="s">
-        <v>416</v>
+        <v>369</v>
       </c>
       <c r="B11" s="62" t="s">
-        <v>410</v>
+        <v>363</v>
       </c>
       <c r="C11" s="64" t="s">
         <v>68</v>
       </c>
       <c r="D11" s="62" t="s">
-        <v>427</v>
+        <v>380</v>
       </c>
       <c r="E11" s="62"/>
     </row>
     <row r="12" spans="1:5" ht="18.75">
       <c r="A12" s="62" t="s">
-        <v>416</v>
+        <v>369</v>
       </c>
       <c r="B12" s="62" t="s">
-        <v>418</v>
+        <v>371</v>
       </c>
       <c r="C12" s="64" t="s">
         <v>53</v>
       </c>
       <c r="D12" s="62" t="s">
-        <v>428</v>
+        <v>381</v>
       </c>
       <c r="E12" s="62"/>
     </row>
@@ -6019,7 +5453,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C2B050D-BC7C-494A-847D-9B4C9751E8F0}">
   <dimension ref="A1:F74"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6034,14 +5468,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="46.5" customHeight="1">
-      <c r="A1" s="257" t="s">
-        <v>429</v>
-      </c>
-      <c r="B1" s="258"/>
-      <c r="C1" s="258"/>
-      <c r="D1" s="258"/>
-      <c r="E1" s="258"/>
-      <c r="F1" s="258"/>
+      <c r="A1" s="256" t="s">
+        <v>382</v>
+      </c>
+      <c r="B1" s="257"/>
+      <c r="C1" s="257"/>
+      <c r="D1" s="257"/>
+      <c r="E1" s="257"/>
+      <c r="F1" s="257"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="66" t="s">
@@ -6050,10 +5484,10 @@
       <c r="B2" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="259" t="s">
+      <c r="C2" s="258" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="260"/>
+      <c r="D2" s="259"/>
       <c r="E2" s="66" t="s">
         <v>34</v>
       </c>
@@ -6066,15 +5500,15 @@
         <v>1</v>
       </c>
       <c r="B3" s="68" t="s">
-        <v>430</v>
-      </c>
-      <c r="C3" s="261"/>
-      <c r="D3" s="262"/>
+        <v>383</v>
+      </c>
+      <c r="C3" s="260"/>
+      <c r="D3" s="261"/>
       <c r="E3" s="68" t="s">
         <v>38</v>
       </c>
       <c r="F3" s="68" t="s">
-        <v>431</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -6086,13 +5520,13 @@
       <c r="F4" s="69"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="258" t="s">
-        <v>432</v>
-      </c>
-      <c r="B5" s="258"/>
-      <c r="C5" s="258"/>
-      <c r="D5" s="258"/>
-      <c r="E5" s="258"/>
+      <c r="A5" s="257" t="s">
+        <v>385</v>
+      </c>
+      <c r="B5" s="257"/>
+      <c r="C5" s="257"/>
+      <c r="D5" s="257"/>
+      <c r="E5" s="257"/>
       <c r="F5" s="70"/>
     </row>
     <row r="6" spans="1:6">
@@ -6115,28 +5549,28 @@
     </row>
     <row r="7" spans="1:6" ht="29.25">
       <c r="A7" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B7" s="68" t="s">
-        <v>433</v>
+        <v>386</v>
       </c>
       <c r="C7" s="68" t="s">
-        <v>434</v>
+        <v>387</v>
       </c>
       <c r="D7" s="72" t="s">
         <v>53</v>
       </c>
       <c r="E7" s="73" t="s">
-        <v>433</v>
+        <v>386</v>
       </c>
       <c r="F7" s="74"/>
     </row>
     <row r="8" spans="1:6" ht="29.25">
       <c r="A8" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B8" s="68" t="s">
-        <v>435</v>
+        <v>388</v>
       </c>
       <c r="C8" s="68" t="s">
         <v>346</v>
@@ -6145,70 +5579,70 @@
         <v>53</v>
       </c>
       <c r="E8" s="73" t="s">
-        <v>435</v>
+        <v>388</v>
       </c>
       <c r="F8" s="74"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B9" s="68" t="s">
-        <v>436</v>
+        <v>389</v>
       </c>
       <c r="C9" s="68" t="s">
-        <v>437</v>
+        <v>390</v>
       </c>
       <c r="D9" s="72" t="s">
         <v>53</v>
       </c>
       <c r="E9" s="73" t="s">
-        <v>436</v>
+        <v>389</v>
       </c>
       <c r="F9" s="74"/>
     </row>
     <row r="10" spans="1:6" ht="29.25">
       <c r="A10" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B10" s="68" t="s">
-        <v>438</v>
+        <v>391</v>
       </c>
       <c r="C10" s="68" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="D10" s="72" t="s">
         <v>53</v>
       </c>
       <c r="E10" s="73" t="s">
-        <v>438</v>
+        <v>391</v>
       </c>
       <c r="F10" s="74"/>
     </row>
     <row r="11" spans="1:6" ht="29.25">
       <c r="A11" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B11" s="68" t="s">
-        <v>440</v>
+        <v>393</v>
       </c>
       <c r="C11" s="68" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="D11" s="72" t="s">
         <v>53</v>
       </c>
       <c r="E11" s="73" t="s">
-        <v>440</v>
+        <v>393</v>
       </c>
       <c r="F11" s="74"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B12" s="68" t="s">
-        <v>441</v>
+        <v>394</v>
       </c>
       <c r="C12" s="68" t="s">
         <v>52</v>
@@ -6217,16 +5651,16 @@
         <v>53</v>
       </c>
       <c r="E12" s="73" t="s">
-        <v>441</v>
+        <v>394</v>
       </c>
       <c r="F12" s="74"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B13" s="68" t="s">
-        <v>442</v>
+        <v>395</v>
       </c>
       <c r="C13" s="68" t="s">
         <v>72</v>
@@ -6235,16 +5669,16 @@
         <v>53</v>
       </c>
       <c r="E13" s="73" t="s">
-        <v>442</v>
+        <v>395</v>
       </c>
       <c r="F13" s="74"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B14" s="68" t="s">
-        <v>443</v>
+        <v>396</v>
       </c>
       <c r="C14" s="68" t="s">
         <v>72</v>
@@ -6253,13 +5687,13 @@
         <v>53</v>
       </c>
       <c r="E14" s="73" t="s">
-        <v>443</v>
+        <v>396</v>
       </c>
       <c r="F14" s="74"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B15" s="68" t="s">
         <v>58</v>
@@ -6277,10 +5711,10 @@
     </row>
     <row r="16" spans="1:6" ht="29.25">
       <c r="A16" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B16" s="68" t="s">
-        <v>444</v>
+        <v>397</v>
       </c>
       <c r="C16" s="68" t="s">
         <v>346</v>
@@ -6289,16 +5723,16 @@
         <v>53</v>
       </c>
       <c r="E16" s="73" t="s">
-        <v>444</v>
+        <v>397</v>
       </c>
       <c r="F16" s="74"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B17" s="68" t="s">
-        <v>445</v>
+        <v>398</v>
       </c>
       <c r="C17" s="68" t="s">
         <v>72</v>
@@ -6307,16 +5741,16 @@
         <v>53</v>
       </c>
       <c r="E17" s="73" t="s">
-        <v>445</v>
+        <v>398</v>
       </c>
       <c r="F17" s="74"/>
     </row>
     <row r="18" spans="1:6" ht="29.25">
       <c r="A18" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B18" s="68" t="s">
-        <v>446</v>
+        <v>399</v>
       </c>
       <c r="C18" s="68" t="s">
         <v>346</v>
@@ -6325,16 +5759,16 @@
         <v>53</v>
       </c>
       <c r="E18" s="73" t="s">
-        <v>446</v>
+        <v>399</v>
       </c>
       <c r="F18" s="74"/>
     </row>
     <row r="19" spans="1:6" ht="29.25">
       <c r="A19" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B19" s="68" t="s">
-        <v>447</v>
+        <v>400</v>
       </c>
       <c r="C19" s="68" t="s">
         <v>346</v>
@@ -6343,13 +5777,13 @@
         <v>53</v>
       </c>
       <c r="E19" s="73" t="s">
-        <v>447</v>
+        <v>400</v>
       </c>
       <c r="F19" s="74"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B20" s="68" t="s">
         <v>127</v>
@@ -6367,10 +5801,10 @@
     </row>
     <row r="21" spans="1:6" ht="29.25">
       <c r="A21" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B21" s="68" t="s">
-        <v>448</v>
+        <v>401</v>
       </c>
       <c r="C21" s="68" t="s">
         <v>346</v>
@@ -6379,16 +5813,16 @@
         <v>53</v>
       </c>
       <c r="E21" s="73" t="s">
-        <v>448</v>
+        <v>401</v>
       </c>
       <c r="F21" s="74"/>
     </row>
     <row r="22" spans="1:6" ht="29.25">
       <c r="A22" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B22" s="68" t="s">
-        <v>449</v>
+        <v>402</v>
       </c>
       <c r="C22" s="68" t="s">
         <v>346</v>
@@ -6397,13 +5831,13 @@
         <v>53</v>
       </c>
       <c r="E22" s="73" t="s">
-        <v>449</v>
+        <v>402</v>
       </c>
       <c r="F22" s="74"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B23" s="68" t="s">
         <v>153</v>
@@ -6421,7 +5855,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B24" s="68" t="s">
         <v>71</v>
@@ -6439,28 +5873,28 @@
     </row>
     <row r="25" spans="1:6" ht="29.25">
       <c r="A25" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B25" s="68" t="s">
-        <v>450</v>
+        <v>403</v>
       </c>
       <c r="C25" s="68" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="D25" s="72" t="s">
         <v>53</v>
       </c>
       <c r="E25" s="73" t="s">
-        <v>450</v>
+        <v>403</v>
       </c>
       <c r="F25" s="74"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B26" s="68" t="s">
-        <v>451</v>
+        <v>404</v>
       </c>
       <c r="C26" s="68" t="s">
         <v>52</v>
@@ -6469,16 +5903,16 @@
         <v>53</v>
       </c>
       <c r="E26" s="73" t="s">
-        <v>451</v>
+        <v>404</v>
       </c>
       <c r="F26" s="74"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B27" s="68" t="s">
-        <v>452</v>
+        <v>405</v>
       </c>
       <c r="C27" s="68" t="s">
         <v>72</v>
@@ -6487,16 +5921,16 @@
         <v>53</v>
       </c>
       <c r="E27" s="73" t="s">
-        <v>452</v>
+        <v>405</v>
       </c>
       <c r="F27" s="74"/>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B28" s="68" t="s">
-        <v>453</v>
+        <v>406</v>
       </c>
       <c r="C28" s="68" t="s">
         <v>72</v>
@@ -6505,16 +5939,16 @@
         <v>53</v>
       </c>
       <c r="E28" s="73" t="s">
-        <v>453</v>
+        <v>406</v>
       </c>
       <c r="F28" s="74"/>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B29" s="68" t="s">
-        <v>454</v>
+        <v>407</v>
       </c>
       <c r="C29" s="68" t="s">
         <v>72</v>
@@ -6523,52 +5957,52 @@
         <v>53</v>
       </c>
       <c r="E29" s="73" t="s">
-        <v>454</v>
+        <v>407</v>
       </c>
       <c r="F29" s="74"/>
     </row>
     <row r="30" spans="1:6" ht="29.25">
       <c r="A30" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B30" s="68" t="s">
-        <v>455</v>
+        <v>408</v>
       </c>
       <c r="C30" s="68" t="s">
-        <v>456</v>
+        <v>409</v>
       </c>
       <c r="D30" s="72" t="s">
         <v>53</v>
       </c>
       <c r="E30" s="73" t="s">
-        <v>455</v>
+        <v>408</v>
       </c>
       <c r="F30" s="74"/>
     </row>
     <row r="31" spans="1:6" ht="29.25">
       <c r="A31" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B31" s="68" t="s">
-        <v>457</v>
+        <v>410</v>
       </c>
       <c r="C31" s="68" t="s">
-        <v>456</v>
+        <v>409</v>
       </c>
       <c r="D31" s="72" t="s">
         <v>53</v>
       </c>
       <c r="E31" s="73" t="s">
-        <v>457</v>
+        <v>410</v>
       </c>
       <c r="F31" s="74"/>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B32" s="68" t="s">
-        <v>458</v>
+        <v>411</v>
       </c>
       <c r="C32" s="68" t="s">
         <v>52</v>
@@ -6577,16 +6011,16 @@
         <v>53</v>
       </c>
       <c r="E32" s="73" t="s">
-        <v>458</v>
+        <v>411</v>
       </c>
       <c r="F32" s="74"/>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B33" s="68" t="s">
-        <v>459</v>
+        <v>412</v>
       </c>
       <c r="C33" s="68" t="s">
         <v>52</v>
@@ -6595,16 +6029,16 @@
         <v>53</v>
       </c>
       <c r="E33" s="73" t="s">
-        <v>459</v>
+        <v>412</v>
       </c>
       <c r="F33" s="74"/>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B34" s="68" t="s">
-        <v>460</v>
+        <v>413</v>
       </c>
       <c r="C34" s="68" t="s">
         <v>52</v>
@@ -6613,19 +6047,19 @@
         <v>53</v>
       </c>
       <c r="E34" s="73" t="s">
-        <v>460</v>
+        <v>413</v>
       </c>
       <c r="F34" s="74"/>
     </row>
     <row r="35" spans="1:6" ht="29.25">
       <c r="A35" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B35" s="68" t="s">
         <v>163</v>
       </c>
       <c r="C35" s="68" t="s">
-        <v>434</v>
+        <v>387</v>
       </c>
       <c r="D35" s="72" t="s">
         <v>53</v>
@@ -6637,10 +6071,10 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B36" s="68" t="s">
-        <v>461</v>
+        <v>414</v>
       </c>
       <c r="C36" s="68" t="s">
         <v>52</v>
@@ -6649,13 +6083,13 @@
         <v>53</v>
       </c>
       <c r="E36" s="73" t="s">
-        <v>461</v>
+        <v>414</v>
       </c>
       <c r="F36" s="74"/>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B37" s="68" t="s">
         <v>113</v>
@@ -6673,10 +6107,10 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B38" s="68" t="s">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="C38" s="68" t="s">
         <v>52</v>
@@ -6685,16 +6119,16 @@
         <v>53</v>
       </c>
       <c r="E38" s="73" t="s">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="F38" s="74"/>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B39" s="68" t="s">
-        <v>463</v>
+        <v>416</v>
       </c>
       <c r="C39" s="68" t="s">
         <v>52</v>
@@ -6703,16 +6137,16 @@
         <v>53</v>
       </c>
       <c r="E39" s="73" t="s">
-        <v>463</v>
+        <v>416</v>
       </c>
       <c r="F39" s="74"/>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B40" s="68" t="s">
-        <v>411</v>
+        <v>364</v>
       </c>
       <c r="C40" s="68" t="s">
         <v>52</v>
@@ -6721,13 +6155,13 @@
         <v>53</v>
       </c>
       <c r="E40" s="73" t="s">
-        <v>411</v>
+        <v>364</v>
       </c>
       <c r="F40" s="74"/>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B41" s="68" t="s">
         <v>141</v>
@@ -6745,10 +6179,10 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B42" s="68" t="s">
-        <v>409</v>
+        <v>362</v>
       </c>
       <c r="C42" s="68" t="s">
         <v>52</v>
@@ -6757,16 +6191,16 @@
         <v>53</v>
       </c>
       <c r="E42" s="73" t="s">
-        <v>409</v>
+        <v>362</v>
       </c>
       <c r="F42" s="74"/>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B43" s="68" t="s">
-        <v>464</v>
+        <v>417</v>
       </c>
       <c r="C43" s="68" t="s">
         <v>52</v>
@@ -6775,16 +6209,16 @@
         <v>53</v>
       </c>
       <c r="E43" s="73" t="s">
-        <v>464</v>
+        <v>417</v>
       </c>
       <c r="F43" s="74"/>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B44" s="68" t="s">
-        <v>465</v>
+        <v>418</v>
       </c>
       <c r="C44" s="68" t="s">
         <v>52</v>
@@ -6793,88 +6227,88 @@
         <v>53</v>
       </c>
       <c r="E44" s="73" t="s">
-        <v>465</v>
+        <v>418</v>
       </c>
       <c r="F44" s="74"/>
     </row>
     <row r="45" spans="1:6" ht="29.25">
       <c r="A45" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B45" s="68" t="s">
-        <v>466</v>
+        <v>419</v>
       </c>
       <c r="C45" s="68" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="D45" s="72" t="s">
         <v>53</v>
       </c>
       <c r="E45" s="73" t="s">
-        <v>466</v>
+        <v>419</v>
       </c>
       <c r="F45" s="74"/>
     </row>
     <row r="46" spans="1:6" ht="29.25">
       <c r="A46" s="68" t="s">
+        <v>373</v>
+      </c>
+      <c r="B46" s="68" t="s">
         <v>420</v>
       </c>
-      <c r="B46" s="68" t="s">
-        <v>467</v>
-      </c>
       <c r="C46" s="68" t="s">
-        <v>468</v>
+        <v>421</v>
       </c>
       <c r="D46" s="72" t="s">
         <v>53</v>
       </c>
       <c r="E46" s="73" t="s">
-        <v>467</v>
+        <v>420</v>
       </c>
       <c r="F46" s="74"/>
     </row>
     <row r="47" spans="1:6" ht="29.25">
       <c r="A47" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B47" s="68" t="s">
-        <v>469</v>
+        <v>422</v>
       </c>
       <c r="C47" s="68" t="s">
-        <v>434</v>
+        <v>387</v>
       </c>
       <c r="D47" s="72" t="s">
         <v>53</v>
       </c>
       <c r="E47" s="73" t="s">
-        <v>469</v>
+        <v>422</v>
       </c>
       <c r="F47" s="74"/>
     </row>
     <row r="48" spans="1:6" ht="29.25">
       <c r="A48" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B48" s="68" t="s">
-        <v>470</v>
+        <v>423</v>
       </c>
       <c r="C48" s="68" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="D48" s="72" t="s">
         <v>53</v>
       </c>
       <c r="E48" s="73" t="s">
-        <v>470</v>
+        <v>423</v>
       </c>
       <c r="F48" s="74"/>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B49" s="68" t="s">
-        <v>418</v>
+        <v>371</v>
       </c>
       <c r="C49" s="68" t="s">
         <v>52</v>
@@ -6883,16 +6317,16 @@
         <v>53</v>
       </c>
       <c r="E49" s="73" t="s">
-        <v>418</v>
+        <v>371</v>
       </c>
       <c r="F49" s="74"/>
     </row>
     <row r="50" spans="1:6" ht="29.25">
       <c r="A50" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B50" s="68" t="s">
-        <v>471</v>
+        <v>424</v>
       </c>
       <c r="C50" s="68" t="s">
         <v>346</v>
@@ -6901,70 +6335,70 @@
         <v>53</v>
       </c>
       <c r="E50" s="73" t="s">
-        <v>471</v>
+        <v>424</v>
       </c>
       <c r="F50" s="74"/>
     </row>
     <row r="51" spans="1:6" ht="29.25">
       <c r="A51" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B51" s="68" t="s">
-        <v>472</v>
+        <v>425</v>
       </c>
       <c r="C51" s="68" t="s">
-        <v>434</v>
+        <v>387</v>
       </c>
       <c r="D51" s="72" t="s">
         <v>53</v>
       </c>
       <c r="E51" s="73" t="s">
-        <v>472</v>
+        <v>425</v>
       </c>
       <c r="F51" s="74"/>
     </row>
     <row r="52" spans="1:6" ht="29.25">
       <c r="A52" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B52" s="68" t="s">
-        <v>473</v>
+        <v>426</v>
       </c>
       <c r="C52" s="68" t="s">
-        <v>474</v>
+        <v>427</v>
       </c>
       <c r="D52" s="72" t="s">
         <v>53</v>
       </c>
       <c r="E52" s="73" t="s">
-        <v>473</v>
+        <v>426</v>
       </c>
       <c r="F52" s="74"/>
     </row>
     <row r="53" spans="1:6" ht="29.25">
       <c r="A53" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B53" s="68" t="s">
-        <v>475</v>
+        <v>428</v>
       </c>
       <c r="C53" s="68" t="s">
-        <v>474</v>
+        <v>427</v>
       </c>
       <c r="D53" s="72" t="s">
         <v>53</v>
       </c>
       <c r="E53" s="73" t="s">
-        <v>475</v>
+        <v>428</v>
       </c>
       <c r="F53" s="74"/>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B54" s="68" t="s">
-        <v>476</v>
+        <v>429</v>
       </c>
       <c r="C54" s="68" t="s">
         <v>52</v>
@@ -6973,16 +6407,16 @@
         <v>53</v>
       </c>
       <c r="E54" s="73" t="s">
-        <v>476</v>
+        <v>429</v>
       </c>
       <c r="F54" s="74"/>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B55" s="68" t="s">
-        <v>477</v>
+        <v>430</v>
       </c>
       <c r="C55" s="68" t="s">
         <v>72</v>
@@ -6991,16 +6425,16 @@
         <v>53</v>
       </c>
       <c r="E55" s="73" t="s">
-        <v>477</v>
+        <v>430</v>
       </c>
       <c r="F55" s="74"/>
     </row>
     <row r="56" spans="1:6" ht="29.25">
       <c r="A56" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B56" s="68" t="s">
-        <v>478</v>
+        <v>431</v>
       </c>
       <c r="C56" s="68" t="s">
         <v>346</v>
@@ -7009,16 +6443,16 @@
         <v>53</v>
       </c>
       <c r="E56" s="73" t="s">
-        <v>478</v>
+        <v>431</v>
       </c>
       <c r="F56" s="74"/>
     </row>
     <row r="57" spans="1:6" ht="29.25">
       <c r="A57" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B57" s="68" t="s">
-        <v>479</v>
+        <v>432</v>
       </c>
       <c r="C57" s="68" t="s">
         <v>346</v>
@@ -7027,55 +6461,55 @@
         <v>53</v>
       </c>
       <c r="E57" s="73" t="s">
-        <v>479</v>
+        <v>432</v>
       </c>
       <c r="F57" s="74"/>
     </row>
     <row r="58" spans="1:6" ht="29.25">
       <c r="A58" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B58" s="68" t="s">
-        <v>480</v>
+        <v>433</v>
       </c>
       <c r="C58" s="68" t="s">
-        <v>481</v>
+        <v>434</v>
       </c>
       <c r="D58" s="72" t="s">
         <v>53</v>
       </c>
       <c r="E58" s="73" t="s">
-        <v>480</v>
+        <v>433</v>
       </c>
       <c r="F58" s="74"/>
     </row>
     <row r="59" spans="1:6" ht="29.25">
       <c r="A59" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B59" s="68" t="s">
-        <v>482</v>
+        <v>435</v>
       </c>
       <c r="C59" s="68" t="s">
-        <v>434</v>
+        <v>387</v>
       </c>
       <c r="D59" s="72" t="s">
         <v>53</v>
       </c>
       <c r="E59" s="73" t="s">
-        <v>482</v>
+        <v>435</v>
       </c>
       <c r="F59" s="74"/>
     </row>
     <row r="60" spans="1:6" ht="29.25">
       <c r="A60" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B60" s="68" t="s">
         <v>103</v>
       </c>
       <c r="C60" s="68" t="s">
-        <v>481</v>
+        <v>434</v>
       </c>
       <c r="D60" s="72" t="s">
         <v>53</v>
@@ -7087,46 +6521,46 @@
     </row>
     <row r="61" spans="1:6" ht="29.25">
       <c r="A61" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B61" s="68" t="s">
-        <v>483</v>
+        <v>436</v>
       </c>
       <c r="C61" s="68" t="s">
-        <v>481</v>
+        <v>434</v>
       </c>
       <c r="D61" s="72" t="s">
         <v>53</v>
       </c>
       <c r="E61" s="73" t="s">
-        <v>483</v>
+        <v>436</v>
       </c>
       <c r="F61" s="74"/>
     </row>
     <row r="62" spans="1:6" ht="29.25">
       <c r="A62" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B62" s="68" t="s">
-        <v>484</v>
+        <v>437</v>
       </c>
       <c r="C62" s="68" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="D62" s="72" t="s">
         <v>53</v>
       </c>
       <c r="E62" s="73" t="s">
-        <v>484</v>
+        <v>437</v>
       </c>
       <c r="F62" s="74"/>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B63" s="68" t="s">
-        <v>485</v>
+        <v>438</v>
       </c>
       <c r="C63" s="68" t="s">
         <v>52</v>
@@ -7135,13 +6569,13 @@
         <v>53</v>
       </c>
       <c r="E63" s="73" t="s">
-        <v>485</v>
+        <v>438</v>
       </c>
       <c r="F63" s="74"/>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B64" s="68" t="s">
         <v>66</v>
@@ -7153,34 +6587,34 @@
         <v>53</v>
       </c>
       <c r="E64" s="73" t="s">
-        <v>486</v>
+        <v>439</v>
       </c>
       <c r="F64" s="74"/>
     </row>
     <row r="65" spans="1:6" ht="29.25">
       <c r="A65" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B65" s="68" t="s">
-        <v>487</v>
+        <v>440</v>
       </c>
       <c r="C65" s="68" t="s">
-        <v>488</v>
+        <v>441</v>
       </c>
       <c r="D65" s="72" t="s">
         <v>53</v>
       </c>
       <c r="E65" s="73" t="s">
-        <v>487</v>
+        <v>440</v>
       </c>
       <c r="F65" s="74"/>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B66" s="68" t="s">
-        <v>489</v>
+        <v>442</v>
       </c>
       <c r="C66" s="68" t="s">
         <v>52</v>
@@ -7189,34 +6623,34 @@
         <v>53</v>
       </c>
       <c r="E66" s="73" t="s">
-        <v>489</v>
+        <v>442</v>
       </c>
       <c r="F66" s="74"/>
     </row>
     <row r="67" spans="1:6" ht="29.25">
       <c r="A67" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B67" s="68" t="s">
-        <v>490</v>
+        <v>443</v>
       </c>
       <c r="C67" s="68" t="s">
-        <v>434</v>
+        <v>387</v>
       </c>
       <c r="D67" s="72" t="s">
         <v>53</v>
       </c>
       <c r="E67" s="73" t="s">
-        <v>490</v>
+        <v>443</v>
       </c>
       <c r="F67" s="74"/>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B68" s="68" t="s">
-        <v>491</v>
+        <v>444</v>
       </c>
       <c r="C68" s="68" t="s">
         <v>72</v>
@@ -7225,16 +6659,16 @@
         <v>53</v>
       </c>
       <c r="E68" s="73" t="s">
-        <v>491</v>
+        <v>444</v>
       </c>
       <c r="F68" s="74"/>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B69" s="68" t="s">
-        <v>492</v>
+        <v>445</v>
       </c>
       <c r="C69" s="68" t="s">
         <v>72</v>
@@ -7243,34 +6677,34 @@
         <v>53</v>
       </c>
       <c r="E69" s="73" t="s">
-        <v>492</v>
+        <v>445</v>
       </c>
       <c r="F69" s="74"/>
     </row>
     <row r="70" spans="1:6" ht="29.25">
       <c r="A70" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B70" s="68" t="s">
-        <v>493</v>
+        <v>446</v>
       </c>
       <c r="C70" s="68" t="s">
-        <v>456</v>
+        <v>409</v>
       </c>
       <c r="D70" s="72" t="s">
         <v>53</v>
       </c>
       <c r="E70" s="73" t="s">
-        <v>493</v>
+        <v>446</v>
       </c>
       <c r="F70" s="74"/>
     </row>
     <row r="71" spans="1:6" ht="29.25">
       <c r="A71" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B71" s="68" t="s">
-        <v>494</v>
+        <v>447</v>
       </c>
       <c r="C71" s="68" t="s">
         <v>346</v>
@@ -7279,16 +6713,16 @@
         <v>53</v>
       </c>
       <c r="E71" s="73" t="s">
-        <v>494</v>
+        <v>447</v>
       </c>
       <c r="F71" s="74"/>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B72" s="68" t="s">
-        <v>495</v>
+        <v>448</v>
       </c>
       <c r="C72" s="68" t="s">
         <v>52</v>
@@ -7297,25 +6731,25 @@
         <v>53</v>
       </c>
       <c r="E72" s="73" t="s">
-        <v>495</v>
+        <v>448</v>
       </c>
       <c r="F72" s="74"/>
     </row>
     <row r="73" spans="1:6" ht="29.25">
       <c r="A73" s="68" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="B73" s="68" t="s">
-        <v>496</v>
+        <v>449</v>
       </c>
       <c r="C73" s="68" t="s">
-        <v>456</v>
+        <v>409</v>
       </c>
       <c r="D73" s="72" t="s">
         <v>53</v>
       </c>
       <c r="E73" s="73" t="s">
-        <v>496</v>
+        <v>449</v>
       </c>
       <c r="F73" s="74"/>
     </row>
@@ -7338,7 +6772,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A20A4369-5079-4D5C-A792-E08D91BCD820}">
   <dimension ref="A1:F72"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7352,14 +6786,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="46.5" customHeight="1">
-      <c r="A1" s="263" t="s">
-        <v>497</v>
-      </c>
-      <c r="B1" s="264"/>
-      <c r="C1" s="264"/>
-      <c r="D1" s="264"/>
-      <c r="E1" s="264"/>
-      <c r="F1" s="264"/>
+      <c r="A1" s="262" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1" s="263"/>
+      <c r="C1" s="263"/>
+      <c r="D1" s="263"/>
+      <c r="E1" s="263"/>
+      <c r="F1" s="263"/>
     </row>
     <row r="2" spans="1:6" ht="18.75">
       <c r="A2" s="60" t="s">
@@ -7368,10 +6802,10 @@
       <c r="B2" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="264" t="s">
+      <c r="C2" s="263" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="264"/>
+      <c r="D2" s="263"/>
       <c r="E2" s="60" t="s">
         <v>34</v>
       </c>
@@ -7388,13 +6822,13 @@
       <c r="F3" s="75"/>
     </row>
     <row r="4" spans="1:6" ht="18.75">
-      <c r="A4" s="264" t="s">
-        <v>498</v>
-      </c>
-      <c r="B4" s="264"/>
-      <c r="C4" s="264"/>
-      <c r="D4" s="264"/>
-      <c r="E4" s="264"/>
+      <c r="A4" s="263" t="s">
+        <v>451</v>
+      </c>
+      <c r="B4" s="263"/>
+      <c r="C4" s="263"/>
+      <c r="D4" s="263"/>
+      <c r="E4" s="263"/>
       <c r="F4" s="76"/>
     </row>
     <row r="5" spans="1:6" ht="18.75">
@@ -7417,64 +6851,64 @@
     </row>
     <row r="6" spans="1:6" ht="18.75">
       <c r="A6" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B6" s="78" t="s">
-        <v>440</v>
+        <v>393</v>
       </c>
       <c r="C6" s="78" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="D6" s="79" t="s">
         <v>53</v>
       </c>
       <c r="E6" s="78" t="s">
-        <v>440</v>
+        <v>393</v>
       </c>
       <c r="F6" s="80"/>
     </row>
     <row r="7" spans="1:6" ht="18.75">
       <c r="A7" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B7" s="78" t="s">
-        <v>438</v>
+        <v>391</v>
       </c>
       <c r="C7" s="78" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="D7" s="79" t="s">
         <v>53</v>
       </c>
       <c r="E7" s="78" t="s">
-        <v>438</v>
+        <v>391</v>
       </c>
       <c r="F7" s="80"/>
     </row>
     <row r="8" spans="1:6" ht="18.75">
       <c r="A8" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B8" s="78" t="s">
-        <v>436</v>
+        <v>389</v>
       </c>
       <c r="C8" s="78" t="s">
-        <v>434</v>
+        <v>387</v>
       </c>
       <c r="D8" s="79" t="s">
         <v>53</v>
       </c>
       <c r="E8" s="78" t="s">
-        <v>436</v>
+        <v>389</v>
       </c>
       <c r="F8" s="80"/>
     </row>
     <row r="9" spans="1:6" ht="18.75">
       <c r="A9" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B9" s="78" t="s">
-        <v>435</v>
+        <v>388</v>
       </c>
       <c r="C9" s="78" t="s">
         <v>346</v>
@@ -7483,34 +6917,34 @@
         <v>53</v>
       </c>
       <c r="E9" s="78" t="s">
-        <v>435</v>
+        <v>388</v>
       </c>
       <c r="F9" s="80"/>
     </row>
     <row r="10" spans="1:6" ht="18.75">
       <c r="A10" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B10" s="78" t="s">
-        <v>433</v>
+        <v>386</v>
       </c>
       <c r="C10" s="78" t="s">
-        <v>434</v>
+        <v>387</v>
       </c>
       <c r="D10" s="79" t="s">
         <v>53</v>
       </c>
       <c r="E10" s="78" t="s">
-        <v>433</v>
+        <v>386</v>
       </c>
       <c r="F10" s="80"/>
     </row>
     <row r="11" spans="1:6" ht="18.75">
       <c r="A11" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B11" s="78" t="s">
-        <v>479</v>
+        <v>432</v>
       </c>
       <c r="C11" s="78" t="s">
         <v>67</v>
@@ -7519,16 +6953,16 @@
         <v>53</v>
       </c>
       <c r="E11" s="78" t="s">
-        <v>479</v>
+        <v>432</v>
       </c>
       <c r="F11" s="80"/>
     </row>
     <row r="12" spans="1:6" ht="18.75">
       <c r="A12" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B12" s="78" t="s">
-        <v>478</v>
+        <v>431</v>
       </c>
       <c r="C12" s="78" t="s">
         <v>67</v>
@@ -7537,16 +6971,16 @@
         <v>53</v>
       </c>
       <c r="E12" s="78" t="s">
-        <v>478</v>
+        <v>431</v>
       </c>
       <c r="F12" s="80"/>
     </row>
     <row r="13" spans="1:6" ht="16.5" customHeight="1">
       <c r="A13" s="75" t="s">
+        <v>383</v>
+      </c>
+      <c r="B13" s="78" t="s">
         <v>430</v>
-      </c>
-      <c r="B13" s="78" t="s">
-        <v>477</v>
       </c>
       <c r="C13" s="78" t="s">
         <v>72</v>
@@ -7555,16 +6989,16 @@
         <v>53</v>
       </c>
       <c r="E13" s="78" t="s">
-        <v>477</v>
+        <v>430</v>
       </c>
       <c r="F13" s="80"/>
     </row>
     <row r="14" spans="1:6" ht="18.75">
       <c r="A14" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B14" s="78" t="s">
-        <v>476</v>
+        <v>429</v>
       </c>
       <c r="C14" s="78" t="s">
         <v>52</v>
@@ -7573,70 +7007,70 @@
         <v>53</v>
       </c>
       <c r="E14" s="78" t="s">
-        <v>476</v>
+        <v>429</v>
       </c>
       <c r="F14" s="80"/>
     </row>
     <row r="15" spans="1:6" ht="18.75">
       <c r="A15" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B15" s="78" t="s">
-        <v>475</v>
+        <v>428</v>
       </c>
       <c r="C15" s="78" t="s">
-        <v>474</v>
+        <v>427</v>
       </c>
       <c r="D15" s="79" t="s">
         <v>53</v>
       </c>
       <c r="E15" s="78" t="s">
-        <v>475</v>
+        <v>428</v>
       </c>
       <c r="F15" s="80"/>
     </row>
     <row r="16" spans="1:6" ht="18.75">
       <c r="A16" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B16" s="78" t="s">
-        <v>473</v>
+        <v>426</v>
       </c>
       <c r="C16" s="78" t="s">
-        <v>474</v>
+        <v>427</v>
       </c>
       <c r="D16" s="79" t="s">
         <v>53</v>
       </c>
       <c r="E16" s="78" t="s">
-        <v>473</v>
+        <v>426</v>
       </c>
       <c r="F16" s="80"/>
     </row>
     <row r="17" spans="1:6" ht="18.75">
       <c r="A17" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B17" s="78" t="s">
-        <v>472</v>
+        <v>425</v>
       </c>
       <c r="C17" s="78" t="s">
-        <v>434</v>
+        <v>387</v>
       </c>
       <c r="D17" s="79" t="s">
         <v>53</v>
       </c>
       <c r="E17" s="78" t="s">
-        <v>472</v>
+        <v>425</v>
       </c>
       <c r="F17" s="80"/>
     </row>
     <row r="18" spans="1:6" ht="18.75">
       <c r="A18" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B18" s="78" t="s">
-        <v>471</v>
+        <v>424</v>
       </c>
       <c r="C18" s="78" t="s">
         <v>67</v>
@@ -7645,16 +7079,16 @@
         <v>53</v>
       </c>
       <c r="E18" s="78" t="s">
-        <v>471</v>
+        <v>424</v>
       </c>
       <c r="F18" s="80"/>
     </row>
     <row r="19" spans="1:6" ht="18.75">
       <c r="A19" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B19" s="78" t="s">
-        <v>418</v>
+        <v>371</v>
       </c>
       <c r="C19" s="78" t="s">
         <v>52</v>
@@ -7663,88 +7097,88 @@
         <v>53</v>
       </c>
       <c r="E19" s="78" t="s">
-        <v>418</v>
+        <v>371</v>
       </c>
       <c r="F19" s="80"/>
     </row>
     <row r="20" spans="1:6" ht="18.75">
       <c r="A20" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B20" s="78" t="s">
-        <v>470</v>
+        <v>423</v>
       </c>
       <c r="C20" s="78" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="D20" s="79" t="s">
         <v>53</v>
       </c>
       <c r="E20" s="78" t="s">
-        <v>470</v>
+        <v>423</v>
       </c>
       <c r="F20" s="80"/>
     </row>
     <row r="21" spans="1:6" ht="18.75">
       <c r="A21" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B21" s="78" t="s">
-        <v>469</v>
+        <v>422</v>
       </c>
       <c r="C21" s="78" t="s">
-        <v>434</v>
+        <v>387</v>
       </c>
       <c r="D21" s="79" t="s">
         <v>53</v>
       </c>
       <c r="E21" s="78" t="s">
-        <v>469</v>
+        <v>422</v>
       </c>
       <c r="F21" s="80"/>
     </row>
     <row r="22" spans="1:6" ht="18.75">
       <c r="A22" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B22" s="78" t="s">
-        <v>467</v>
+        <v>420</v>
       </c>
       <c r="C22" s="78" t="s">
-        <v>468</v>
+        <v>421</v>
       </c>
       <c r="D22" s="79" t="s">
         <v>53</v>
       </c>
       <c r="E22" s="78" t="s">
-        <v>467</v>
+        <v>420</v>
       </c>
       <c r="F22" s="80"/>
     </row>
     <row r="23" spans="1:6" ht="18.75">
       <c r="A23" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B23" s="78" t="s">
-        <v>466</v>
+        <v>419</v>
       </c>
       <c r="C23" s="78" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="D23" s="79" t="s">
         <v>53</v>
       </c>
       <c r="E23" s="78" t="s">
-        <v>466</v>
+        <v>419</v>
       </c>
       <c r="F23" s="80"/>
     </row>
     <row r="24" spans="1:6" ht="18.75">
       <c r="A24" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B24" s="78" t="s">
-        <v>465</v>
+        <v>418</v>
       </c>
       <c r="C24" s="78" t="s">
         <v>52</v>
@@ -7753,16 +7187,16 @@
         <v>53</v>
       </c>
       <c r="E24" s="78" t="s">
-        <v>465</v>
+        <v>418</v>
       </c>
       <c r="F24" s="80"/>
     </row>
     <row r="25" spans="1:6" ht="18.75">
       <c r="A25" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B25" s="78" t="s">
-        <v>464</v>
+        <v>417</v>
       </c>
       <c r="C25" s="78" t="s">
         <v>52</v>
@@ -7771,16 +7205,16 @@
         <v>53</v>
       </c>
       <c r="E25" s="78" t="s">
-        <v>464</v>
+        <v>417</v>
       </c>
       <c r="F25" s="80"/>
     </row>
     <row r="26" spans="1:6" ht="18.75">
       <c r="A26" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B26" s="78" t="s">
-        <v>409</v>
+        <v>362</v>
       </c>
       <c r="C26" s="78" t="s">
         <v>52</v>
@@ -7789,13 +7223,13 @@
         <v>53</v>
       </c>
       <c r="E26" s="78" t="s">
-        <v>409</v>
+        <v>362</v>
       </c>
       <c r="F26" s="80"/>
     </row>
     <row r="27" spans="1:6" ht="18.75">
       <c r="A27" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B27" s="78" t="s">
         <v>141</v>
@@ -7813,10 +7247,10 @@
     </row>
     <row r="28" spans="1:6" ht="18.75">
       <c r="A28" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B28" s="78" t="s">
-        <v>411</v>
+        <v>364</v>
       </c>
       <c r="C28" s="78" t="s">
         <v>52</v>
@@ -7825,16 +7259,16 @@
         <v>53</v>
       </c>
       <c r="E28" s="78" t="s">
-        <v>411</v>
+        <v>364</v>
       </c>
       <c r="F28" s="80"/>
     </row>
     <row r="29" spans="1:6" ht="18.75">
       <c r="A29" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B29" s="78" t="s">
-        <v>463</v>
+        <v>416</v>
       </c>
       <c r="C29" s="78" t="s">
         <v>52</v>
@@ -7843,16 +7277,16 @@
         <v>53</v>
       </c>
       <c r="E29" s="78" t="s">
-        <v>463</v>
+        <v>416</v>
       </c>
       <c r="F29" s="80"/>
     </row>
     <row r="30" spans="1:6" ht="18.75">
       <c r="A30" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B30" s="78" t="s">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="C30" s="78" t="s">
         <v>52</v>
@@ -7861,13 +7295,13 @@
         <v>53</v>
       </c>
       <c r="E30" s="78" t="s">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="F30" s="80"/>
     </row>
     <row r="31" spans="1:6" ht="18.75">
       <c r="A31" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B31" s="78" t="s">
         <v>113</v>
@@ -7885,10 +7319,10 @@
     </row>
     <row r="32" spans="1:6" ht="18.75">
       <c r="A32" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B32" s="78" t="s">
-        <v>461</v>
+        <v>414</v>
       </c>
       <c r="C32" s="78" t="s">
         <v>52</v>
@@ -7897,19 +7331,19 @@
         <v>53</v>
       </c>
       <c r="E32" s="78" t="s">
-        <v>461</v>
+        <v>414</v>
       </c>
       <c r="F32" s="80"/>
     </row>
     <row r="33" spans="1:6" ht="18.75">
       <c r="A33" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B33" s="78" t="s">
         <v>163</v>
       </c>
       <c r="C33" s="78" t="s">
-        <v>434</v>
+        <v>387</v>
       </c>
       <c r="D33" s="79" t="s">
         <v>53</v>
@@ -7921,10 +7355,10 @@
     </row>
     <row r="34" spans="1:6" ht="18.75">
       <c r="A34" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B34" s="78" t="s">
-        <v>460</v>
+        <v>413</v>
       </c>
       <c r="C34" s="78" t="s">
         <v>52</v>
@@ -7933,16 +7367,16 @@
         <v>53</v>
       </c>
       <c r="E34" s="78" t="s">
-        <v>460</v>
+        <v>413</v>
       </c>
       <c r="F34" s="80"/>
     </row>
     <row r="35" spans="1:6" ht="18.75">
       <c r="A35" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B35" s="78" t="s">
-        <v>459</v>
+        <v>412</v>
       </c>
       <c r="C35" s="78" t="s">
         <v>52</v>
@@ -7951,16 +7385,16 @@
         <v>53</v>
       </c>
       <c r="E35" s="78" t="s">
-        <v>459</v>
+        <v>412</v>
       </c>
       <c r="F35" s="80"/>
     </row>
     <row r="36" spans="1:6" ht="18.75">
       <c r="A36" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B36" s="78" t="s">
-        <v>458</v>
+        <v>411</v>
       </c>
       <c r="C36" s="78" t="s">
         <v>52</v>
@@ -7969,52 +7403,52 @@
         <v>53</v>
       </c>
       <c r="E36" s="78" t="s">
-        <v>458</v>
+        <v>411</v>
       </c>
       <c r="F36" s="80"/>
     </row>
     <row r="37" spans="1:6" ht="18.75">
       <c r="A37" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B37" s="78" t="s">
-        <v>457</v>
+        <v>410</v>
       </c>
       <c r="C37" s="78" t="s">
-        <v>456</v>
+        <v>409</v>
       </c>
       <c r="D37" s="79" t="s">
         <v>53</v>
       </c>
       <c r="E37" s="78" t="s">
-        <v>457</v>
+        <v>410</v>
       </c>
       <c r="F37" s="80"/>
     </row>
     <row r="38" spans="1:6" ht="18.75">
       <c r="A38" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B38" s="78" t="s">
-        <v>455</v>
+        <v>408</v>
       </c>
       <c r="C38" s="78" t="s">
-        <v>456</v>
+        <v>409</v>
       </c>
       <c r="D38" s="79" t="s">
         <v>53</v>
       </c>
       <c r="E38" s="78" t="s">
-        <v>455</v>
+        <v>408</v>
       </c>
       <c r="F38" s="80"/>
     </row>
     <row r="39" spans="1:6" ht="18.75">
       <c r="A39" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B39" s="78" t="s">
-        <v>454</v>
+        <v>407</v>
       </c>
       <c r="C39" s="78" t="s">
         <v>72</v>
@@ -8023,16 +7457,16 @@
         <v>53</v>
       </c>
       <c r="E39" s="78" t="s">
-        <v>454</v>
+        <v>407</v>
       </c>
       <c r="F39" s="80"/>
     </row>
     <row r="40" spans="1:6" ht="18.75">
       <c r="A40" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B40" s="78" t="s">
-        <v>453</v>
+        <v>406</v>
       </c>
       <c r="C40" s="78" t="s">
         <v>72</v>
@@ -8041,16 +7475,16 @@
         <v>53</v>
       </c>
       <c r="E40" s="78" t="s">
-        <v>453</v>
+        <v>406</v>
       </c>
       <c r="F40" s="80"/>
     </row>
     <row r="41" spans="1:6" ht="18.75">
       <c r="A41" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B41" s="78" t="s">
-        <v>452</v>
+        <v>405</v>
       </c>
       <c r="C41" s="78" t="s">
         <v>72</v>
@@ -8059,16 +7493,16 @@
         <v>53</v>
       </c>
       <c r="E41" s="78" t="s">
-        <v>452</v>
+        <v>405</v>
       </c>
       <c r="F41" s="80"/>
     </row>
     <row r="42" spans="1:6" ht="18.75">
       <c r="A42" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B42" s="78" t="s">
-        <v>451</v>
+        <v>404</v>
       </c>
       <c r="C42" s="78" t="s">
         <v>52</v>
@@ -8077,31 +7511,31 @@
         <v>53</v>
       </c>
       <c r="E42" s="78" t="s">
-        <v>451</v>
+        <v>404</v>
       </c>
       <c r="F42" s="80"/>
     </row>
     <row r="43" spans="1:6" ht="18.75">
       <c r="A43" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B43" s="78" t="s">
-        <v>450</v>
+        <v>403</v>
       </c>
       <c r="C43" s="78" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="D43" s="79" t="s">
         <v>53</v>
       </c>
       <c r="E43" s="78" t="s">
-        <v>450</v>
+        <v>403</v>
       </c>
       <c r="F43" s="80"/>
     </row>
     <row r="44" spans="1:6" ht="18.75">
       <c r="A44" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B44" s="78" t="s">
         <v>71</v>
@@ -8119,7 +7553,7 @@
     </row>
     <row r="45" spans="1:6" ht="18.75">
       <c r="A45" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B45" s="78" t="s">
         <v>153</v>
@@ -8137,10 +7571,10 @@
     </row>
     <row r="46" spans="1:6" ht="18.75">
       <c r="A46" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B46" s="78" t="s">
-        <v>449</v>
+        <v>402</v>
       </c>
       <c r="C46" s="78" t="s">
         <v>67</v>
@@ -8149,16 +7583,16 @@
         <v>53</v>
       </c>
       <c r="E46" s="78" t="s">
-        <v>449</v>
+        <v>402</v>
       </c>
       <c r="F46" s="80"/>
     </row>
     <row r="47" spans="1:6" ht="18.75">
       <c r="A47" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B47" s="78" t="s">
-        <v>448</v>
+        <v>401</v>
       </c>
       <c r="C47" s="78" t="s">
         <v>67</v>
@@ -8167,13 +7601,13 @@
         <v>53</v>
       </c>
       <c r="E47" s="78" t="s">
-        <v>448</v>
+        <v>401</v>
       </c>
       <c r="F47" s="80"/>
     </row>
     <row r="48" spans="1:6" ht="18.75">
       <c r="A48" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B48" s="78" t="s">
         <v>127</v>
@@ -8191,10 +7625,10 @@
     </row>
     <row r="49" spans="1:6" ht="18.75">
       <c r="A49" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B49" s="78" t="s">
-        <v>447</v>
+        <v>400</v>
       </c>
       <c r="C49" s="78" t="s">
         <v>67</v>
@@ -8203,16 +7637,16 @@
         <v>53</v>
       </c>
       <c r="E49" s="78" t="s">
-        <v>447</v>
+        <v>400</v>
       </c>
       <c r="F49" s="80"/>
     </row>
     <row r="50" spans="1:6" ht="18.75">
       <c r="A50" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B50" s="78" t="s">
-        <v>446</v>
+        <v>399</v>
       </c>
       <c r="C50" s="78" t="s">
         <v>67</v>
@@ -8221,16 +7655,16 @@
         <v>53</v>
       </c>
       <c r="E50" s="78" t="s">
-        <v>446</v>
+        <v>399</v>
       </c>
       <c r="F50" s="80"/>
     </row>
     <row r="51" spans="1:6" ht="18.75">
       <c r="A51" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B51" s="78" t="s">
-        <v>445</v>
+        <v>398</v>
       </c>
       <c r="C51" s="78" t="s">
         <v>72</v>
@@ -8239,16 +7673,16 @@
         <v>53</v>
       </c>
       <c r="E51" s="78" t="s">
-        <v>445</v>
+        <v>398</v>
       </c>
       <c r="F51" s="80"/>
     </row>
     <row r="52" spans="1:6" ht="18.75">
       <c r="A52" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B52" s="78" t="s">
-        <v>444</v>
+        <v>397</v>
       </c>
       <c r="C52" s="78" t="s">
         <v>67</v>
@@ -8257,13 +7691,13 @@
         <v>53</v>
       </c>
       <c r="E52" s="78" t="s">
-        <v>444</v>
+        <v>397</v>
       </c>
       <c r="F52" s="80"/>
     </row>
     <row r="53" spans="1:6" ht="18.75">
       <c r="A53" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B53" s="78" t="s">
         <v>58</v>
@@ -8281,10 +7715,10 @@
     </row>
     <row r="54" spans="1:6" ht="36">
       <c r="A54" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B54" s="78" t="s">
-        <v>443</v>
+        <v>396</v>
       </c>
       <c r="C54" s="78" t="s">
         <v>72</v>
@@ -8293,16 +7727,16 @@
         <v>53</v>
       </c>
       <c r="E54" s="78" t="s">
-        <v>443</v>
+        <v>396</v>
       </c>
       <c r="F54" s="80"/>
     </row>
     <row r="55" spans="1:6" ht="18.75">
       <c r="A55" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B55" s="78" t="s">
-        <v>442</v>
+        <v>395</v>
       </c>
       <c r="C55" s="78" t="s">
         <v>72</v>
@@ -8311,16 +7745,16 @@
         <v>53</v>
       </c>
       <c r="E55" s="78" t="s">
-        <v>442</v>
+        <v>395</v>
       </c>
       <c r="F55" s="80"/>
     </row>
     <row r="56" spans="1:6" ht="18.75">
       <c r="A56" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B56" s="78" t="s">
-        <v>441</v>
+        <v>394</v>
       </c>
       <c r="C56" s="78" t="s">
         <v>52</v>
@@ -8329,16 +7763,16 @@
         <v>53</v>
       </c>
       <c r="E56" s="78" t="s">
-        <v>441</v>
+        <v>394</v>
       </c>
       <c r="F56" s="80"/>
     </row>
     <row r="57" spans="1:6" ht="18.75">
       <c r="A57" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B57" s="78" t="s">
-        <v>485</v>
+        <v>438</v>
       </c>
       <c r="C57" s="78" t="s">
         <v>52</v>
@@ -8347,55 +7781,55 @@
         <v>53</v>
       </c>
       <c r="E57" s="78" t="s">
-        <v>485</v>
+        <v>438</v>
       </c>
       <c r="F57" s="80"/>
     </row>
     <row r="58" spans="1:6" ht="18.75">
       <c r="A58" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B58" s="78" t="s">
-        <v>484</v>
+        <v>437</v>
       </c>
       <c r="C58" s="78" t="s">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="D58" s="79" t="s">
         <v>53</v>
       </c>
       <c r="E58" s="78" t="s">
-        <v>484</v>
+        <v>437</v>
       </c>
       <c r="F58" s="80"/>
     </row>
     <row r="59" spans="1:6" ht="18.75">
       <c r="A59" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B59" s="78" t="s">
-        <v>483</v>
+        <v>436</v>
       </c>
       <c r="C59" s="78" t="s">
-        <v>481</v>
+        <v>434</v>
       </c>
       <c r="D59" s="79" t="s">
         <v>53</v>
       </c>
       <c r="E59" s="78" t="s">
-        <v>483</v>
+        <v>436</v>
       </c>
       <c r="F59" s="80"/>
     </row>
     <row r="60" spans="1:6" ht="18.75">
       <c r="A60" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B60" s="78" t="s">
         <v>103</v>
       </c>
       <c r="C60" s="78" t="s">
-        <v>481</v>
+        <v>434</v>
       </c>
       <c r="D60" s="79" t="s">
         <v>53</v>
@@ -8407,64 +7841,64 @@
     </row>
     <row r="61" spans="1:6" ht="18.75">
       <c r="A61" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B61" s="78" t="s">
-        <v>482</v>
+        <v>435</v>
       </c>
       <c r="C61" s="78" t="s">
-        <v>434</v>
+        <v>387</v>
       </c>
       <c r="D61" s="79" t="s">
         <v>53</v>
       </c>
       <c r="E61" s="78" t="s">
-        <v>482</v>
+        <v>435</v>
       </c>
       <c r="F61" s="80"/>
     </row>
     <row r="62" spans="1:6" ht="18.75">
       <c r="A62" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B62" s="78" t="s">
-        <v>480</v>
+        <v>433</v>
       </c>
       <c r="C62" s="78" t="s">
-        <v>481</v>
+        <v>434</v>
       </c>
       <c r="D62" s="79" t="s">
         <v>53</v>
       </c>
       <c r="E62" s="78" t="s">
-        <v>480</v>
+        <v>433</v>
       </c>
       <c r="F62" s="80"/>
     </row>
     <row r="63" spans="1:6" ht="18.75">
       <c r="A63" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B63" s="78" t="s">
-        <v>487</v>
+        <v>440</v>
       </c>
       <c r="C63" s="78" t="s">
-        <v>488</v>
+        <v>441</v>
       </c>
       <c r="D63" s="79" t="s">
         <v>53</v>
       </c>
       <c r="E63" s="78" t="s">
-        <v>487</v>
+        <v>440</v>
       </c>
       <c r="F63" s="80"/>
     </row>
     <row r="64" spans="1:6" ht="18.75">
       <c r="A64" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B64" s="78" t="s">
-        <v>489</v>
+        <v>442</v>
       </c>
       <c r="C64" s="78" t="s">
         <v>52</v>
@@ -8473,52 +7907,52 @@
         <v>53</v>
       </c>
       <c r="E64" s="78" t="s">
-        <v>489</v>
+        <v>442</v>
       </c>
       <c r="F64" s="80"/>
     </row>
     <row r="65" spans="1:6" ht="18.75">
       <c r="A65" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B65" s="78" t="s">
-        <v>490</v>
+        <v>443</v>
       </c>
       <c r="C65" s="78" t="s">
-        <v>434</v>
+        <v>387</v>
       </c>
       <c r="D65" s="79" t="s">
         <v>53</v>
       </c>
       <c r="E65" s="78" t="s">
-        <v>490</v>
+        <v>443</v>
       </c>
       <c r="F65" s="80"/>
     </row>
     <row r="66" spans="1:6" ht="18.75">
       <c r="A66" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B66" s="78" t="s">
-        <v>499</v>
+        <v>452</v>
       </c>
       <c r="C66" s="78" t="s">
-        <v>434</v>
+        <v>387</v>
       </c>
       <c r="D66" s="79" t="s">
         <v>53</v>
       </c>
       <c r="E66" s="78" t="s">
-        <v>499</v>
+        <v>452</v>
       </c>
       <c r="F66" s="80"/>
     </row>
     <row r="67" spans="1:6" ht="18.75">
       <c r="A67" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B67" s="78" t="s">
-        <v>492</v>
+        <v>445</v>
       </c>
       <c r="C67" s="78" t="s">
         <v>72</v>
@@ -8527,16 +7961,16 @@
         <v>53</v>
       </c>
       <c r="E67" s="78" t="s">
-        <v>492</v>
+        <v>445</v>
       </c>
       <c r="F67" s="80"/>
     </row>
     <row r="68" spans="1:6" ht="18.75">
       <c r="A68" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B68" s="78" t="s">
-        <v>491</v>
+        <v>444</v>
       </c>
       <c r="C68" s="78" t="s">
         <v>72</v>
@@ -8545,34 +7979,34 @@
         <v>53</v>
       </c>
       <c r="E68" s="78" t="s">
-        <v>491</v>
+        <v>444</v>
       </c>
       <c r="F68" s="80"/>
     </row>
     <row r="69" spans="1:6" ht="18.75">
       <c r="A69" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B69" s="78" t="s">
-        <v>493</v>
+        <v>446</v>
       </c>
       <c r="C69" s="78" t="s">
-        <v>456</v>
+        <v>409</v>
       </c>
       <c r="D69" s="79" t="s">
         <v>53</v>
       </c>
       <c r="E69" s="78" t="s">
-        <v>493</v>
+        <v>446</v>
       </c>
       <c r="F69" s="80"/>
     </row>
     <row r="70" spans="1:6" ht="18.75">
       <c r="A70" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B70" s="78" t="s">
-        <v>494</v>
+        <v>447</v>
       </c>
       <c r="C70" s="78" t="s">
         <v>67</v>
@@ -8581,16 +8015,16 @@
         <v>53</v>
       </c>
       <c r="E70" s="78" t="s">
-        <v>494</v>
+        <v>447</v>
       </c>
       <c r="F70" s="80"/>
     </row>
     <row r="71" spans="1:6" ht="18.75">
       <c r="A71" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B71" s="78" t="s">
-        <v>495</v>
+        <v>448</v>
       </c>
       <c r="C71" s="78" t="s">
         <v>52</v>
@@ -8599,25 +8033,25 @@
         <v>53</v>
       </c>
       <c r="E71" s="78" t="s">
-        <v>495</v>
+        <v>448</v>
       </c>
       <c r="F71" s="80"/>
     </row>
     <row r="72" spans="1:6" ht="18.75">
       <c r="A72" s="75" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="B72" s="78" t="s">
-        <v>496</v>
+        <v>449</v>
       </c>
       <c r="C72" s="78" t="s">
-        <v>456</v>
+        <v>409</v>
       </c>
       <c r="D72" s="79" t="s">
         <v>53</v>
       </c>
       <c r="E72" s="78" t="s">
-        <v>496</v>
+        <v>449</v>
       </c>
       <c r="F72" s="80"/>
     </row>
@@ -8631,7 +8065,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89021E1C-CB51-4696-A042-61474206883C}">
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8645,13 +8079,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="37.5" customHeight="1">
-      <c r="A1" s="265" t="s">
-        <v>500</v>
-      </c>
-      <c r="B1" s="266"/>
-      <c r="C1" s="266"/>
-      <c r="D1" s="266"/>
-      <c r="E1" s="266"/>
+      <c r="A1" s="264" t="s">
+        <v>453</v>
+      </c>
+      <c r="B1" s="265"/>
+      <c r="C1" s="265"/>
+      <c r="D1" s="265"/>
+      <c r="E1" s="265"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="81" t="s">
@@ -8675,24 +8109,24 @@
         <v>1</v>
       </c>
       <c r="B3" s="82" t="s">
-        <v>501</v>
+        <v>454</v>
       </c>
       <c r="C3" s="82"/>
       <c r="D3" s="82" t="s">
         <v>38</v>
       </c>
       <c r="E3" s="82" t="s">
-        <v>502</v>
+        <v>455</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="267" t="s">
-        <v>503</v>
-      </c>
-      <c r="B4" s="268"/>
-      <c r="C4" s="268"/>
-      <c r="D4" s="268"/>
-      <c r="E4" s="269"/>
+      <c r="A4" s="266" t="s">
+        <v>456</v>
+      </c>
+      <c r="B4" s="267"/>
+      <c r="C4" s="267"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="268"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="81" t="s">
@@ -8713,22 +8147,22 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="82" t="s">
-        <v>504</v>
+        <v>457</v>
       </c>
       <c r="B6" s="82" t="s">
-        <v>505</v>
+        <v>458</v>
       </c>
       <c r="C6" s="83" t="s">
         <v>53</v>
       </c>
       <c r="D6" s="82" t="s">
-        <v>505</v>
+        <v>458</v>
       </c>
       <c r="E6" s="82"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="82" t="s">
-        <v>504</v>
+        <v>457</v>
       </c>
       <c r="B7" s="82" t="s">
         <v>123</v>
@@ -8743,7 +8177,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="82" t="s">
-        <v>504</v>
+        <v>457</v>
       </c>
       <c r="B8" s="82" t="s">
         <v>109</v>
@@ -8758,7 +8192,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="82" t="s">
-        <v>504</v>
+        <v>457</v>
       </c>
       <c r="B9" s="82" t="s">
         <v>127</v>
@@ -8773,16 +8207,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="82" t="s">
-        <v>504</v>
+        <v>457</v>
       </c>
       <c r="B10" s="82" t="s">
-        <v>506</v>
+        <v>459</v>
       </c>
       <c r="C10" s="83" t="s">
         <v>53</v>
       </c>
       <c r="D10" s="82" t="s">
-        <v>506</v>
+        <v>459</v>
       </c>
       <c r="E10" s="82"/>
     </row>
@@ -8795,7 +8229,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E0C52D2-84C9-4375-A6BC-B6321EA1C5A5}">
   <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8808,13 +8242,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="47.25" customHeight="1">
-      <c r="A1" s="270" t="s">
-        <v>507</v>
-      </c>
-      <c r="B1" s="271"/>
-      <c r="C1" s="271"/>
-      <c r="D1" s="271"/>
-      <c r="E1" s="271"/>
+      <c r="A1" s="269" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1" s="270"/>
+      <c r="C1" s="270"/>
+      <c r="D1" s="270"/>
+      <c r="E1" s="270"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="85" t="s">
@@ -8841,13 +8275,13 @@
       <c r="E3" s="86"/>
     </row>
     <row r="5" spans="1:5" ht="18.75">
-      <c r="A5" s="264" t="s">
-        <v>508</v>
-      </c>
-      <c r="B5" s="264"/>
-      <c r="C5" s="264"/>
-      <c r="D5" s="264"/>
-      <c r="E5" s="264"/>
+      <c r="A5" s="263" t="s">
+        <v>461</v>
+      </c>
+      <c r="B5" s="263"/>
+      <c r="C5" s="263"/>
+      <c r="D5" s="263"/>
+      <c r="E5" s="263"/>
     </row>
     <row r="6" spans="1:5" ht="18.75">
       <c r="A6" s="60" t="s">
@@ -8860,7 +8294,7 @@
         <v>47</v>
       </c>
       <c r="D6" s="60" t="s">
-        <v>509</v>
+        <v>462</v>
       </c>
       <c r="E6" s="60" t="s">
         <v>183</v>
@@ -8868,10 +8302,10 @@
     </row>
     <row r="7" spans="1:5" ht="18">
       <c r="A7" s="87" t="s">
-        <v>501</v>
+        <v>454</v>
       </c>
       <c r="B7" s="87" t="s">
-        <v>510</v>
+        <v>463</v>
       </c>
       <c r="C7" s="88" t="s">
         <v>67</v>
@@ -8880,15 +8314,15 @@
         <v>53</v>
       </c>
       <c r="E7" s="87" t="s">
-        <v>510</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18">
       <c r="A8" s="87" t="s">
-        <v>501</v>
+        <v>454</v>
       </c>
       <c r="B8" s="87" t="s">
-        <v>511</v>
+        <v>464</v>
       </c>
       <c r="C8" s="88" t="s">
         <v>52</v>
@@ -8897,15 +8331,15 @@
         <v>53</v>
       </c>
       <c r="E8" s="87" t="s">
-        <v>511</v>
+        <v>464</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18">
       <c r="A9" s="87" t="s">
-        <v>501</v>
+        <v>454</v>
       </c>
       <c r="B9" s="87" t="s">
-        <v>512</v>
+        <v>465</v>
       </c>
       <c r="C9" s="88" t="s">
         <v>52</v>
@@ -8914,15 +8348,15 @@
         <v>53</v>
       </c>
       <c r="E9" s="87" t="s">
-        <v>512</v>
+        <v>465</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18">
       <c r="A10" s="87" t="s">
-        <v>501</v>
+        <v>454</v>
       </c>
       <c r="B10" s="87" t="s">
-        <v>513</v>
+        <v>466</v>
       </c>
       <c r="C10" s="88" t="s">
         <v>321</v>
@@ -8931,15 +8365,15 @@
         <v>53</v>
       </c>
       <c r="E10" s="87" t="s">
-        <v>513</v>
+        <v>466</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18">
       <c r="A11" s="87" t="s">
-        <v>501</v>
+        <v>454</v>
       </c>
       <c r="B11" s="87" t="s">
-        <v>514</v>
+        <v>467</v>
       </c>
       <c r="C11" s="88" t="s">
         <v>321</v>
@@ -8948,12 +8382,12 @@
         <v>53</v>
       </c>
       <c r="E11" s="87" t="s">
-        <v>514</v>
+        <v>467</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18">
       <c r="A12" s="87" t="s">
-        <v>501</v>
+        <v>454</v>
       </c>
       <c r="B12" s="87" t="s">
         <v>109</v>
@@ -8970,7 +8404,7 @@
     </row>
     <row r="13" spans="1:5" ht="18">
       <c r="A13" s="87" t="s">
-        <v>501</v>
+        <v>454</v>
       </c>
       <c r="B13" s="87" t="s">
         <v>74</v>
@@ -8987,7 +8421,7 @@
     </row>
     <row r="14" spans="1:5" ht="18">
       <c r="A14" s="87" t="s">
-        <v>501</v>
+        <v>454</v>
       </c>
       <c r="B14" s="87" t="s">
         <v>123</v>
@@ -9004,10 +8438,10 @@
     </row>
     <row r="15" spans="1:5" ht="18">
       <c r="A15" s="87" t="s">
-        <v>501</v>
+        <v>454</v>
       </c>
       <c r="B15" s="87" t="s">
-        <v>505</v>
+        <v>458</v>
       </c>
       <c r="C15" s="88" t="s">
         <v>72</v>
@@ -9016,29 +8450,29 @@
         <v>53</v>
       </c>
       <c r="E15" s="87" t="s">
-        <v>505</v>
+        <v>458</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="36">
       <c r="A16" s="87" t="s">
-        <v>501</v>
+        <v>454</v>
       </c>
       <c r="B16" s="87" t="s">
-        <v>506</v>
+        <v>459</v>
       </c>
       <c r="C16" s="88" t="s">
-        <v>481</v>
+        <v>434</v>
       </c>
       <c r="D16" s="88" t="s">
         <v>53</v>
       </c>
       <c r="E16" s="87" t="s">
-        <v>506</v>
+        <v>459</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18">
       <c r="A17" s="87" t="s">
-        <v>501</v>
+        <v>454</v>
       </c>
       <c r="B17" s="87" t="s">
         <v>127</v>
@@ -9055,10 +8489,10 @@
     </row>
     <row r="18" spans="1:5" ht="18">
       <c r="A18" s="87" t="s">
-        <v>501</v>
+        <v>454</v>
       </c>
       <c r="B18" s="87" t="s">
-        <v>515</v>
+        <v>468</v>
       </c>
       <c r="C18" s="88" t="s">
         <v>67</v>
@@ -9067,15 +8501,15 @@
         <v>53</v>
       </c>
       <c r="E18" s="87" t="s">
-        <v>515</v>
+        <v>468</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18">
       <c r="A19" s="87" t="s">
-        <v>501</v>
+        <v>454</v>
       </c>
       <c r="B19" s="87" t="s">
-        <v>477</v>
+        <v>430</v>
       </c>
       <c r="C19" s="88" t="s">
         <v>72</v>
@@ -9084,13 +8518,599 @@
         <v>53</v>
       </c>
       <c r="E19" s="87" t="s">
-        <v>477</v>
+        <v>430</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A5:E5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0AAAEE-6532-4107-BFC0-FBA58A0A23E4}">
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="44.42578125" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="74.28515625" customWidth="1"/>
+    <col min="7" max="7" width="69.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="151" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="151"/>
+      <c r="C1" s="151"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="151"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="102"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="152" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="151" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="151" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="151" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="153" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="103"/>
+      <c r="G2" s="102"/>
+    </row>
+    <row r="3" spans="1:7" ht="152.25">
+      <c r="A3" s="154">
+        <v>1</v>
+      </c>
+      <c r="B3" s="155" t="s">
+        <v>469</v>
+      </c>
+      <c r="C3" s="154" t="s">
+        <v>470</v>
+      </c>
+      <c r="D3" s="156" t="s">
+        <v>303</v>
+      </c>
+      <c r="E3" s="165" t="s">
+        <v>471</v>
+      </c>
+      <c r="G3" s="102"/>
+    </row>
+    <row r="4" spans="1:7" ht="137.25">
+      <c r="A4" s="157">
+        <v>2</v>
+      </c>
+      <c r="B4" s="158" t="s">
+        <v>472</v>
+      </c>
+      <c r="C4" s="159" t="s">
+        <v>473</v>
+      </c>
+      <c r="D4" s="159" t="s">
+        <v>303</v>
+      </c>
+      <c r="E4" s="160" t="s">
+        <v>474</v>
+      </c>
+      <c r="G4" s="104"/>
+    </row>
+    <row r="5" spans="1:7" ht="167.25">
+      <c r="A5" s="157">
+        <v>3</v>
+      </c>
+      <c r="B5" s="158" t="s">
+        <v>475</v>
+      </c>
+      <c r="C5" s="159" t="s">
+        <v>476</v>
+      </c>
+      <c r="D5" s="159" t="s">
+        <v>303</v>
+      </c>
+      <c r="E5" s="160" t="s">
+        <v>477</v>
+      </c>
+      <c r="F5" s="103"/>
+      <c r="G5" s="104"/>
+    </row>
+    <row r="6" spans="1:7" ht="229.5">
+      <c r="A6" s="157">
+        <v>4</v>
+      </c>
+      <c r="B6" s="158" t="s">
+        <v>478</v>
+      </c>
+      <c r="C6" s="159" t="s">
+        <v>309</v>
+      </c>
+      <c r="D6" s="159" t="s">
+        <v>303</v>
+      </c>
+      <c r="E6" s="160" t="s">
+        <v>479</v>
+      </c>
+      <c r="F6" s="103"/>
+      <c r="G6" s="104"/>
+    </row>
+    <row r="7" spans="1:7" ht="409.6">
+      <c r="A7" s="161">
+        <v>5</v>
+      </c>
+      <c r="B7" s="158" t="s">
+        <v>480</v>
+      </c>
+      <c r="C7" s="162" t="s">
+        <v>481</v>
+      </c>
+      <c r="D7" s="162" t="s">
+        <v>303</v>
+      </c>
+      <c r="E7" s="163" t="s">
+        <v>482</v>
+      </c>
+      <c r="F7" s="103"/>
+      <c r="G7" s="104"/>
+    </row>
+    <row r="8" spans="1:7" ht="94.5">
+      <c r="A8" s="161">
+        <v>6</v>
+      </c>
+      <c r="B8" s="158" t="s">
+        <v>483</v>
+      </c>
+      <c r="C8" s="162" t="s">
+        <v>484</v>
+      </c>
+      <c r="D8" s="162" t="s">
+        <v>303</v>
+      </c>
+      <c r="E8" s="163" t="s">
+        <v>485</v>
+      </c>
+      <c r="F8" s="103"/>
+      <c r="G8" s="104"/>
+    </row>
+    <row r="9" spans="1:7" ht="290.25">
+      <c r="A9" s="161">
+        <v>7</v>
+      </c>
+      <c r="B9" s="158" t="s">
+        <v>486</v>
+      </c>
+      <c r="C9" s="162" t="s">
+        <v>487</v>
+      </c>
+      <c r="D9" s="162" t="s">
+        <v>303</v>
+      </c>
+      <c r="E9" s="163" t="s">
+        <v>488</v>
+      </c>
+      <c r="F9" s="103"/>
+      <c r="G9" s="104"/>
+    </row>
+    <row r="10" spans="1:7" ht="290.25">
+      <c r="A10" s="161">
+        <v>8</v>
+      </c>
+      <c r="B10" s="158" t="s">
+        <v>489</v>
+      </c>
+      <c r="C10" s="162" t="s">
+        <v>490</v>
+      </c>
+      <c r="D10" s="162" t="s">
+        <v>303</v>
+      </c>
+      <c r="E10" s="163" t="s">
+        <v>491</v>
+      </c>
+      <c r="F10" s="103"/>
+      <c r="G10" s="104"/>
+    </row>
+    <row r="11" spans="1:7" ht="275.25">
+      <c r="A11" s="161">
+        <v>9</v>
+      </c>
+      <c r="B11" s="158" t="s">
+        <v>492</v>
+      </c>
+      <c r="C11" s="162" t="s">
+        <v>493</v>
+      </c>
+      <c r="D11" s="162" t="s">
+        <v>303</v>
+      </c>
+      <c r="E11" s="163" t="s">
+        <v>494</v>
+      </c>
+      <c r="F11" s="187"/>
+      <c r="G11" s="105"/>
+    </row>
+    <row r="12" spans="1:7" ht="229.5">
+      <c r="A12" s="161">
+        <v>10</v>
+      </c>
+      <c r="B12" s="164" t="s">
+        <v>495</v>
+      </c>
+      <c r="C12" s="162" t="s">
+        <v>496</v>
+      </c>
+      <c r="D12" s="162" t="s">
+        <v>497</v>
+      </c>
+      <c r="E12" s="163" t="s">
+        <v>498</v>
+      </c>
+      <c r="F12" s="187"/>
+      <c r="G12" s="105"/>
+    </row>
+    <row r="13" spans="1:7" ht="15" customHeight="1">
+      <c r="A13" s="271" t="s">
+        <v>229</v>
+      </c>
+      <c r="B13" s="271"/>
+      <c r="C13" s="271"/>
+      <c r="D13" s="271"/>
+      <c r="E13" s="271"/>
+      <c r="F13" s="244"/>
+      <c r="G13" s="140"/>
+    </row>
+    <row r="14" spans="1:7" ht="27">
+      <c r="A14" s="134" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="135" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="135" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="135" t="s">
+        <v>499</v>
+      </c>
+      <c r="E14" s="135" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="139" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" s="138"/>
+    </row>
+    <row r="15" spans="1:7" ht="27">
+      <c r="A15" s="136">
+        <v>1</v>
+      </c>
+      <c r="B15" s="137" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="137" t="s">
+        <v>500</v>
+      </c>
+      <c r="D15" s="142" t="s">
+        <v>321</v>
+      </c>
+      <c r="E15" s="143" t="s">
+        <v>235</v>
+      </c>
+      <c r="F15" s="137" t="s">
+        <v>322</v>
+      </c>
+      <c r="G15" s="105"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="129">
+        <v>2</v>
+      </c>
+      <c r="B16" s="130" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="130" t="s">
+        <v>290</v>
+      </c>
+      <c r="D16" s="144" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="145" t="s">
+        <v>501</v>
+      </c>
+      <c r="F16" s="130" t="s">
+        <v>502</v>
+      </c>
+      <c r="G16" s="105"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="129">
+        <v>3</v>
+      </c>
+      <c r="B17" s="130" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="130" t="s">
+        <v>330</v>
+      </c>
+      <c r="D17" s="146" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="145" t="s">
+        <v>235</v>
+      </c>
+      <c r="F17" s="130" t="s">
+        <v>503</v>
+      </c>
+      <c r="G17" s="105"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="129">
+        <v>4</v>
+      </c>
+      <c r="B18" s="130" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="130" t="s">
+        <v>332</v>
+      </c>
+      <c r="D18" s="146" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="145" t="s">
+        <v>501</v>
+      </c>
+      <c r="F18" s="130" t="s">
+        <v>504</v>
+      </c>
+      <c r="G18" s="105"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="131">
+        <v>5</v>
+      </c>
+      <c r="B19" s="130" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="132" t="s">
+        <v>334</v>
+      </c>
+      <c r="D19" s="147" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="148" t="s">
+        <v>501</v>
+      </c>
+      <c r="F19" s="132" t="s">
+        <v>505</v>
+      </c>
+      <c r="G19" s="106"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="129">
+        <v>6</v>
+      </c>
+      <c r="B20" s="130" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="130" t="s">
+        <v>336</v>
+      </c>
+      <c r="D20" s="146" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="145" t="s">
+        <v>235</v>
+      </c>
+      <c r="F20" s="130" t="s">
+        <v>506</v>
+      </c>
+      <c r="G20" s="104"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="129">
+        <v>7</v>
+      </c>
+      <c r="B21" s="130" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="130" t="s">
+        <v>340</v>
+      </c>
+      <c r="D21" s="146" t="s">
+        <v>341</v>
+      </c>
+      <c r="E21" s="145" t="s">
+        <v>501</v>
+      </c>
+      <c r="F21" s="130" t="s">
+        <v>507</v>
+      </c>
+      <c r="G21" s="105"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="129">
+        <v>8</v>
+      </c>
+      <c r="B22" s="130" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="130" t="s">
+        <v>343</v>
+      </c>
+      <c r="D22" s="146" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" s="145" t="s">
+        <v>501</v>
+      </c>
+      <c r="F22" s="130" t="s">
+        <v>508</v>
+      </c>
+      <c r="G22" s="105"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="129">
+        <v>9</v>
+      </c>
+      <c r="B23" s="130" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="130" t="s">
+        <v>345</v>
+      </c>
+      <c r="D23" s="146" t="s">
+        <v>346</v>
+      </c>
+      <c r="E23" s="145" t="s">
+        <v>235</v>
+      </c>
+      <c r="F23" s="130" t="s">
+        <v>509</v>
+      </c>
+      <c r="G23" s="105"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="129">
+        <v>10</v>
+      </c>
+      <c r="B24" s="130" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="130" t="s">
+        <v>349</v>
+      </c>
+      <c r="D24" s="146" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" s="145" t="s">
+        <v>347</v>
+      </c>
+      <c r="F24" s="130" t="s">
+        <v>510</v>
+      </c>
+      <c r="G24" s="105"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="129">
+        <v>11</v>
+      </c>
+      <c r="B25" s="130" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="130" t="s">
+        <v>351</v>
+      </c>
+      <c r="D25" s="146" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" s="145" t="s">
+        <v>347</v>
+      </c>
+      <c r="F25" s="130" t="s">
+        <v>350</v>
+      </c>
+      <c r="G25" s="105"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="129">
+        <v>12</v>
+      </c>
+      <c r="B26" s="130" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="130" t="s">
+        <v>338</v>
+      </c>
+      <c r="D26" s="146" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" s="145" t="s">
+        <v>501</v>
+      </c>
+      <c r="F26" s="130" t="s">
+        <v>339</v>
+      </c>
+      <c r="G26" s="105"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="129">
+        <v>13</v>
+      </c>
+      <c r="B27" s="130" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="130" t="s">
+        <v>352</v>
+      </c>
+      <c r="D27" s="146" t="s">
+        <v>67</v>
+      </c>
+      <c r="E27" s="145" t="s">
+        <v>501</v>
+      </c>
+      <c r="F27" s="130" t="s">
+        <v>511</v>
+      </c>
+      <c r="G27" s="105"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="129">
+        <v>14</v>
+      </c>
+      <c r="B28" s="130" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="129" t="s">
+        <v>512</v>
+      </c>
+      <c r="D28" s="149" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" s="150" t="s">
+        <v>501</v>
+      </c>
+      <c r="F28" s="129" t="s">
+        <v>513</v>
+      </c>
+      <c r="G28" s="188"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="129">
+        <v>15</v>
+      </c>
+      <c r="B29" s="130" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="129" t="s">
+        <v>514</v>
+      </c>
+      <c r="D29" s="149" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" s="150" t="s">
+        <v>501</v>
+      </c>
+      <c r="F29" s="129" t="s">
+        <v>515</v>
+      </c>
+      <c r="G29" s="188"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A13:F13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9143,7 +9163,7 @@
       <c r="B3" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="172" t="s">
+      <c r="C3" s="169" t="s">
         <v>25</v>
       </c>
       <c r="D3" t="s">
@@ -9157,11 +9177,11 @@
       <c r="B4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="168" t="s">
+      <c r="D4" s="186" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" ht="409.6">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -9194,15 +9214,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="209" t="s">
+      <c r="A1" s="207" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="210"/>
-      <c r="C1" s="210"/>
-      <c r="D1" s="210"/>
-      <c r="E1" s="210"/>
-      <c r="F1" s="210"/>
-      <c r="G1" s="211"/>
+      <c r="B1" s="208"/>
+      <c r="C1" s="208"/>
+      <c r="D1" s="208"/>
+      <c r="E1" s="208"/>
+      <c r="F1" s="208"/>
+      <c r="G1" s="209"/>
       <c r="H1" s="275"/>
     </row>
     <row r="2" spans="1:8">
@@ -9218,11 +9238,11 @@
       <c r="D2" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="210" t="s">
+      <c r="E2" s="208" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="210"/>
-      <c r="G2" s="212"/>
+      <c r="F2" s="208"/>
+      <c r="G2" s="210"/>
       <c r="H2" s="275"/>
     </row>
     <row r="3" spans="1:8">
@@ -9238,9 +9258,9 @@
       <c r="D3" s="91" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="213"/>
-      <c r="F3" s="213"/>
-      <c r="G3" s="214"/>
+      <c r="E3" s="211"/>
+      <c r="F3" s="211"/>
+      <c r="G3" s="212"/>
       <c r="H3" s="275"/>
     </row>
     <row r="4" spans="1:8" ht="64.5" customHeight="1">
@@ -9256,23 +9276,23 @@
       <c r="D4" s="91" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="213" t="s">
+      <c r="E4" s="211" t="s">
         <v>42</v>
       </c>
-      <c r="F4" s="213"/>
-      <c r="G4" s="214"/>
+      <c r="F4" s="211"/>
+      <c r="G4" s="212"/>
       <c r="H4" s="275"/>
     </row>
     <row r="5" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A5" s="215" t="s">
+      <c r="A5" s="213" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="216"/>
-      <c r="C5" s="216"/>
-      <c r="D5" s="216"/>
-      <c r="E5" s="216"/>
-      <c r="F5" s="216"/>
-      <c r="G5" s="217"/>
+      <c r="B5" s="214"/>
+      <c r="C5" s="214"/>
+      <c r="D5" s="214"/>
+      <c r="E5" s="214"/>
+      <c r="F5" s="214"/>
+      <c r="G5" s="215"/>
       <c r="H5" s="275"/>
     </row>
     <row r="6" spans="1:8">
@@ -10703,14 +10723,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="218" t="s">
+      <c r="A1" s="216" t="s">
         <v>173</v>
       </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219"/>
+      <c r="B1" s="217"/>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="217"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7">
@@ -10720,10 +10740,10 @@
       <c r="B2" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="220" t="s">
+      <c r="C2" s="218" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="221"/>
+      <c r="D2" s="219"/>
       <c r="E2" s="40" t="s">
         <v>34</v>
       </c>
@@ -10739,10 +10759,10 @@
       <c r="B3" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="C3" s="222" t="s">
+      <c r="C3" s="220" t="s">
         <v>175</v>
       </c>
-      <c r="D3" s="223"/>
+      <c r="D3" s="221"/>
       <c r="E3" s="41" t="s">
         <v>38</v>
       </c>
@@ -10758,10 +10778,10 @@
       <c r="B4" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="C4" s="222" t="s">
+      <c r="C4" s="220" t="s">
         <v>177</v>
       </c>
-      <c r="D4" s="223"/>
+      <c r="D4" s="221"/>
       <c r="E4" s="41" t="s">
         <v>41</v>
       </c>
@@ -10770,14 +10790,14 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="219" t="s">
+      <c r="A5" s="217" t="s">
         <v>179</v>
       </c>
-      <c r="B5" s="219"/>
-      <c r="C5" s="219"/>
-      <c r="D5" s="219"/>
-      <c r="E5" s="219"/>
-      <c r="F5" s="219"/>
+      <c r="B5" s="217"/>
+      <c r="C5" s="217"/>
+      <c r="D5" s="217"/>
+      <c r="E5" s="217"/>
+      <c r="F5" s="217"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="40" t="s">
@@ -10907,14 +10927,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24.75" customHeight="1">
-      <c r="A1" s="224" t="s">
+      <c r="A1" s="222" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="225"/>
-      <c r="C1" s="225"/>
-      <c r="D1" s="225"/>
-      <c r="E1" s="225"/>
-      <c r="F1" s="225"/>
+      <c r="B1" s="223"/>
+      <c r="C1" s="223"/>
+      <c r="D1" s="223"/>
+      <c r="E1" s="223"/>
+      <c r="F1" s="223"/>
     </row>
     <row r="2" spans="1:6" ht="24.75" customHeight="1">
       <c r="A2" s="46" t="s">
@@ -10923,10 +10943,10 @@
       <c r="B2" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="226" t="s">
+      <c r="C2" s="224" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="227"/>
+      <c r="D2" s="225"/>
       <c r="E2" s="46" t="s">
         <v>34</v>
       </c>
@@ -10941,10 +10961,10 @@
       <c r="B3" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="C3" s="228" t="s">
+      <c r="C3" s="226" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="229"/>
+      <c r="D3" s="227"/>
       <c r="E3" s="47" t="s">
         <v>38</v>
       </c>
@@ -10957,10 +10977,10 @@
       <c r="B4" s="50" t="s">
         <v>198</v>
       </c>
-      <c r="C4" s="230" t="s">
+      <c r="C4" s="228" t="s">
         <v>199</v>
       </c>
-      <c r="D4" s="231"/>
+      <c r="D4" s="229"/>
       <c r="E4" s="49" t="s">
         <v>200</v>
       </c>
@@ -10977,13 +10997,13 @@
       <c r="F5" s="282"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="226" t="s">
+      <c r="A7" s="224" t="s">
         <v>202</v>
       </c>
-      <c r="B7" s="232"/>
-      <c r="C7" s="232"/>
-      <c r="D7" s="232"/>
-      <c r="E7" s="232"/>
+      <c r="B7" s="230"/>
+      <c r="C7" s="230"/>
+      <c r="D7" s="230"/>
+      <c r="E7" s="230"/>
       <c r="F7" s="282"/>
     </row>
     <row r="8" spans="1:6">
@@ -11155,13 +11175,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="235" t="s">
+      <c r="A1" s="233" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="236"/>
-      <c r="C1" s="236"/>
-      <c r="D1" s="236"/>
-      <c r="E1" s="237"/>
+      <c r="B1" s="234"/>
+      <c r="C1" s="234"/>
+      <c r="D1" s="234"/>
+      <c r="E1" s="235"/>
       <c r="F1" s="5"/>
     </row>
     <row r="2" spans="1:6">
@@ -11262,39 +11282,39 @@
       <c r="E7" s="30"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1">
-      <c r="A8" s="235" t="s">
+      <c r="A8" s="233" t="s">
         <v>229</v>
       </c>
-      <c r="B8" s="236"/>
-      <c r="C8" s="236"/>
-      <c r="D8" s="236"/>
-      <c r="E8" s="236"/>
+      <c r="B8" s="234"/>
+      <c r="C8" s="234"/>
+      <c r="D8" s="234"/>
+      <c r="E8" s="234"/>
       <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="238" t="s">
+      <c r="A9" s="236" t="s">
         <v>230</v>
       </c>
-      <c r="B9" s="239" t="s">
+      <c r="B9" s="237" t="s">
         <v>231</v>
       </c>
-      <c r="C9" s="239" t="s">
+      <c r="C9" s="237" t="s">
         <v>182</v>
       </c>
-      <c r="D9" s="240" t="s">
+      <c r="D9" s="238" t="s">
         <v>183</v>
       </c>
-      <c r="E9" s="240" t="s">
+      <c r="E9" s="238" t="s">
         <v>232</v>
       </c>
       <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="238"/>
-      <c r="B10" s="239"/>
-      <c r="C10" s="239"/>
-      <c r="D10" s="241"/>
-      <c r="E10" s="241"/>
+      <c r="A10" s="236"/>
+      <c r="B10" s="237"/>
+      <c r="C10" s="237"/>
+      <c r="D10" s="239"/>
+      <c r="E10" s="239"/>
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6">
@@ -12324,13 +12344,13 @@
       <c r="F67" s="5"/>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="233" t="s">
+      <c r="A68" s="231" t="s">
         <v>249</v>
       </c>
-      <c r="B68" s="234"/>
-      <c r="C68" s="234"/>
-      <c r="D68" s="234"/>
-      <c r="E68" s="234"/>
+      <c r="B68" s="232"/>
+      <c r="C68" s="232"/>
+      <c r="D68" s="232"/>
+      <c r="E68" s="232"/>
       <c r="F68" s="5"/>
     </row>
     <row r="69" spans="1:6">
@@ -13379,13 +13399,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="242" t="s">
+      <c r="A1" s="240" t="s">
         <v>278</v>
       </c>
-      <c r="B1" s="243"/>
-      <c r="C1" s="243"/>
-      <c r="D1" s="243"/>
-      <c r="E1" s="244"/>
+      <c r="B1" s="241"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="241"/>
+      <c r="E1" s="242"/>
       <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:6">
@@ -13432,13 +13452,13 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="245" t="s">
+      <c r="A5" s="243" t="s">
         <v>281</v>
       </c>
-      <c r="B5" s="245"/>
-      <c r="C5" s="245"/>
-      <c r="D5" s="245"/>
-      <c r="E5" s="245"/>
+      <c r="B5" s="243"/>
+      <c r="C5" s="243"/>
+      <c r="D5" s="243"/>
+      <c r="E5" s="243"/>
       <c r="F5" s="112"/>
     </row>
     <row r="6" spans="1:6">
@@ -13621,13 +13641,13 @@
       <c r="E4" s="19"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="190" t="s">
+      <c r="A5" s="244" t="s">
         <v>229</v>
       </c>
-      <c r="B5" s="190"/>
-      <c r="C5" s="190"/>
-      <c r="D5" s="190"/>
-      <c r="E5" s="190"/>
+      <c r="B5" s="244"/>
+      <c r="C5" s="244"/>
+      <c r="D5" s="244"/>
+      <c r="E5" s="244"/>
     </row>
     <row r="6" spans="1:5" ht="24.75">
       <c r="A6" s="21" t="s">
@@ -13741,767 +13761,767 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D674FAF-DFA6-46EE-8CD2-A9D1187C828E}">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="80" customWidth="1"/>
     <col min="3" max="3" width="24.5703125" customWidth="1"/>
     <col min="4" max="4" width="15.28515625" customWidth="1"/>
-    <col min="5" max="5" width="30.140625" style="188" customWidth="1"/>
+    <col min="5" max="5" width="30.140625" style="185" customWidth="1"/>
     <col min="6" max="6" width="70.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1">
-      <c r="A1" s="173" t="s">
+      <c r="A1" s="170" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
+      <c r="B1" s="170"/>
+      <c r="C1" s="170"/>
+      <c r="D1" s="170"/>
+      <c r="E1" s="170"/>
       <c r="F1" s="33"/>
       <c r="G1" s="33"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1">
-      <c r="A2" s="174" t="s">
+      <c r="A2" s="171" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="174" t="s">
+      <c r="B2" s="171" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="174" t="s">
+      <c r="C2" s="171" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="174" t="s">
+      <c r="D2" s="171" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="174" t="s">
+      <c r="E2" s="171" t="s">
         <v>35</v>
       </c>
       <c r="F2" s="33"/>
       <c r="G2" s="33"/>
     </row>
     <row r="3" spans="1:7" ht="409.6">
-      <c r="A3" s="175">
+      <c r="A3" s="172">
         <v>1</v>
       </c>
-      <c r="B3" s="176" t="s">
+      <c r="B3" s="173" t="s">
         <v>301</v>
       </c>
-      <c r="C3" s="177" t="s">
+      <c r="C3" s="174" t="s">
         <v>302</v>
       </c>
-      <c r="D3" s="177" t="s">
+      <c r="D3" s="174" t="s">
         <v>303</v>
       </c>
-      <c r="E3" s="176" t="s">
+      <c r="E3" s="173" t="s">
         <v>304</v>
       </c>
       <c r="F3" s="33"/>
       <c r="G3" s="33"/>
     </row>
     <row r="4" spans="1:7" ht="152.25">
-      <c r="A4" s="175">
+      <c r="A4" s="172">
         <v>2</v>
       </c>
-      <c r="B4" s="176" t="s">
+      <c r="B4" s="173" t="s">
         <v>305</v>
       </c>
-      <c r="C4" s="177" t="s">
+      <c r="C4" s="174" t="s">
         <v>306</v>
       </c>
-      <c r="D4" s="177" t="s">
+      <c r="D4" s="174" t="s">
         <v>303</v>
       </c>
-      <c r="E4" s="176" t="s">
+      <c r="E4" s="173" t="s">
         <v>307</v>
       </c>
       <c r="F4" s="33"/>
       <c r="G4" s="33"/>
     </row>
     <row r="5" spans="1:7" ht="152.25">
-      <c r="A5" s="175">
+      <c r="A5" s="172">
         <v>3</v>
       </c>
-      <c r="B5" s="176" t="s">
+      <c r="B5" s="173" t="s">
         <v>308</v>
       </c>
-      <c r="C5" s="177" t="s">
+      <c r="C5" s="174" t="s">
         <v>309</v>
       </c>
-      <c r="D5" s="177" t="s">
+      <c r="D5" s="174" t="s">
         <v>303</v>
       </c>
-      <c r="E5" s="176" t="s">
+      <c r="E5" s="173" t="s">
         <v>310</v>
       </c>
       <c r="F5" s="33"/>
       <c r="G5" s="33"/>
     </row>
-    <row r="6" spans="1:7" ht="60.75">
-      <c r="A6" s="175">
+    <row r="6" spans="1:7" ht="76.5">
+      <c r="A6" s="172">
         <v>4</v>
       </c>
-      <c r="B6" s="176" t="s">
+      <c r="B6" s="173" t="s">
         <v>311</v>
       </c>
-      <c r="C6" s="177" t="s">
+      <c r="C6" s="174" t="s">
         <v>312</v>
       </c>
-      <c r="D6" s="177" t="s">
+      <c r="D6" s="174" t="s">
         <v>303</v>
       </c>
-      <c r="E6" s="176" t="s">
+      <c r="E6" s="173" t="s">
         <v>313</v>
       </c>
       <c r="F6" s="33"/>
       <c r="G6" s="33"/>
     </row>
-    <row r="7" spans="1:7" ht="366">
-      <c r="A7" s="175">
+    <row r="7" spans="1:7" ht="381.75">
+      <c r="A7" s="172">
         <v>5</v>
       </c>
-      <c r="B7" s="178" t="s">
+      <c r="B7" s="175" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="177" t="s">
+      <c r="C7" s="174" t="s">
         <v>315</v>
       </c>
-      <c r="D7" s="177" t="s">
+      <c r="D7" s="174" t="s">
         <v>316</v>
       </c>
-      <c r="E7" s="176" t="s">
+      <c r="E7" s="173" t="s">
         <v>317</v>
       </c>
       <c r="F7" s="33"/>
       <c r="G7" s="33"/>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1">
-      <c r="A8" s="179"/>
-      <c r="B8" s="180"/>
-      <c r="C8" s="181"/>
-      <c r="D8" s="181"/>
-      <c r="E8" s="181"/>
-      <c r="F8" s="180"/>
+      <c r="A8" s="176"/>
+      <c r="B8" s="177"/>
+      <c r="C8" s="178"/>
+      <c r="D8" s="178"/>
+      <c r="E8" s="178"/>
+      <c r="F8" s="177"/>
       <c r="G8" s="33"/>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1">
-      <c r="A9" s="246" t="s">
+      <c r="A9" s="245" t="s">
         <v>229</v>
       </c>
-      <c r="B9" s="246"/>
-      <c r="C9" s="246"/>
-      <c r="D9" s="246"/>
-      <c r="E9" s="246"/>
-      <c r="F9" s="182"/>
+      <c r="B9" s="245"/>
+      <c r="C9" s="245"/>
+      <c r="D9" s="245"/>
+      <c r="E9" s="245"/>
+      <c r="F9" s="179"/>
       <c r="G9" s="33"/>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1">
-      <c r="A10" s="183" t="s">
+      <c r="A10" s="180" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="183" t="s">
+      <c r="B10" s="180" t="s">
         <v>282</v>
       </c>
-      <c r="C10" s="183" t="s">
+      <c r="C10" s="180" t="s">
         <v>283</v>
       </c>
-      <c r="D10" s="183" t="s">
+      <c r="D10" s="180" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="184" t="s">
+      <c r="E10" s="181" t="s">
         <v>284</v>
       </c>
-      <c r="F10" s="183" t="s">
+      <c r="F10" s="180" t="s">
         <v>48</v>
       </c>
       <c r="G10" s="33"/>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1">
-      <c r="A11" s="247" t="s">
+      <c r="A11" s="246" t="s">
         <v>318</v>
       </c>
-      <c r="B11" s="248"/>
-      <c r="C11" s="248"/>
-      <c r="D11" s="248"/>
-      <c r="E11" s="248"/>
-      <c r="F11" s="248"/>
+      <c r="B11" s="247"/>
+      <c r="C11" s="247"/>
+      <c r="D11" s="247"/>
+      <c r="E11" s="247"/>
+      <c r="F11" s="247"/>
       <c r="G11" s="33"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1">
-      <c r="A12" s="185">
+      <c r="A12" s="182">
         <v>1</v>
       </c>
-      <c r="B12" s="186" t="s">
+      <c r="B12" s="183" t="s">
         <v>319</v>
       </c>
-      <c r="C12" s="186" t="s">
+      <c r="C12" s="183" t="s">
         <v>320</v>
       </c>
-      <c r="D12" s="187" t="s">
+      <c r="D12" s="184" t="s">
         <v>321</v>
       </c>
-      <c r="E12" s="187" t="s">
+      <c r="E12" s="184" t="s">
         <v>235</v>
       </c>
-      <c r="F12" s="186" t="s">
+      <c r="F12" s="183" t="s">
         <v>322</v>
       </c>
       <c r="G12" s="33"/>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1">
-      <c r="A13" s="185">
+      <c r="A13" s="182">
         <v>2</v>
       </c>
-      <c r="B13" s="186" t="s">
+      <c r="B13" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="186" t="s">
+      <c r="C13" s="183" t="s">
         <v>323</v>
       </c>
-      <c r="D13" s="187" t="s">
+      <c r="D13" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="E13" s="187" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" s="186" t="s">
+      <c r="E13" s="184" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="183" t="s">
         <v>324</v>
       </c>
       <c r="G13" s="33"/>
     </row>
     <row r="14" spans="1:7" ht="15" customHeight="1">
-      <c r="A14" s="185">
+      <c r="A14" s="182">
         <v>3</v>
       </c>
-      <c r="B14" s="186" t="s">
+      <c r="B14" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="186" t="s">
+      <c r="C14" s="183" t="s">
         <v>325</v>
       </c>
-      <c r="D14" s="187" t="s">
+      <c r="D14" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="187" t="s">
-        <v>53</v>
-      </c>
-      <c r="F14" s="186" t="s">
+      <c r="E14" s="184" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="183" t="s">
         <v>326</v>
       </c>
       <c r="G14" s="33"/>
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1">
-      <c r="A15" s="185">
+      <c r="A15" s="182">
         <v>4</v>
       </c>
-      <c r="B15" s="186" t="s">
+      <c r="B15" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="186" t="s">
+      <c r="C15" s="183" t="s">
         <v>327</v>
       </c>
-      <c r="D15" s="187" t="s">
+      <c r="D15" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="187" t="s">
-        <v>53</v>
-      </c>
-      <c r="F15" s="186" t="s">
+      <c r="E15" s="184" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="183" t="s">
         <v>328</v>
       </c>
       <c r="G15" s="33"/>
     </row>
     <row r="16" spans="1:7" ht="15" customHeight="1">
-      <c r="A16" s="185">
+      <c r="A16" s="182">
         <v>5</v>
       </c>
-      <c r="B16" s="186" t="s">
+      <c r="B16" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="186" t="s">
+      <c r="C16" s="183" t="s">
         <v>290</v>
       </c>
-      <c r="D16" s="187" t="s">
+      <c r="D16" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="E16" s="187" t="s">
+      <c r="E16" s="184" t="s">
         <v>235</v>
       </c>
-      <c r="F16" s="186" t="s">
+      <c r="F16" s="183" t="s">
         <v>329</v>
       </c>
       <c r="G16" s="33"/>
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1">
-      <c r="A17" s="185">
+      <c r="A17" s="182">
         <v>6</v>
       </c>
-      <c r="B17" s="186" t="s">
+      <c r="B17" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="186" t="s">
+      <c r="C17" s="183" t="s">
         <v>330</v>
       </c>
-      <c r="D17" s="187" t="s">
+      <c r="D17" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="E17" s="187" t="s">
+      <c r="E17" s="184" t="s">
         <v>235</v>
       </c>
-      <c r="F17" s="186" t="s">
+      <c r="F17" s="183" t="s">
         <v>331</v>
       </c>
       <c r="G17" s="33"/>
     </row>
     <row r="18" spans="1:7" ht="15" customHeight="1">
-      <c r="A18" s="185">
+      <c r="A18" s="182">
         <v>7</v>
       </c>
-      <c r="B18" s="186" t="s">
+      <c r="B18" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="186" t="s">
+      <c r="C18" s="183" t="s">
         <v>332</v>
       </c>
-      <c r="D18" s="187" t="s">
+      <c r="D18" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="E18" s="187" t="s">
-        <v>53</v>
-      </c>
-      <c r="F18" s="186" t="s">
+      <c r="E18" s="184" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="183" t="s">
         <v>333</v>
       </c>
       <c r="G18" s="33"/>
     </row>
     <row r="19" spans="1:7" ht="15" customHeight="1">
-      <c r="A19" s="185">
+      <c r="A19" s="182">
         <v>8</v>
       </c>
-      <c r="B19" s="186" t="s">
+      <c r="B19" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="186" t="s">
+      <c r="C19" s="183" t="s">
         <v>334</v>
       </c>
-      <c r="D19" s="187" t="s">
+      <c r="D19" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="187" t="s">
+      <c r="E19" s="184" t="s">
         <v>235</v>
       </c>
-      <c r="F19" s="186" t="s">
+      <c r="F19" s="183" t="s">
         <v>335</v>
       </c>
       <c r="G19" s="33"/>
     </row>
     <row r="20" spans="1:7" ht="15" customHeight="1">
-      <c r="A20" s="185">
+      <c r="A20" s="182">
         <v>9</v>
       </c>
-      <c r="B20" s="186" t="s">
+      <c r="B20" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="186" t="s">
+      <c r="C20" s="183" t="s">
         <v>336</v>
       </c>
-      <c r="D20" s="187" t="s">
+      <c r="D20" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="E20" s="187" t="s">
+      <c r="E20" s="184" t="s">
         <v>235</v>
       </c>
-      <c r="F20" s="186" t="s">
+      <c r="F20" s="183" t="s">
         <v>337</v>
       </c>
       <c r="G20" s="33"/>
     </row>
     <row r="21" spans="1:7" ht="15" customHeight="1">
-      <c r="A21" s="185">
+      <c r="A21" s="182">
         <v>10</v>
       </c>
-      <c r="B21" s="186" t="s">
+      <c r="B21" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="186" t="s">
+      <c r="C21" s="183" t="s">
         <v>338</v>
       </c>
-      <c r="D21" s="187" t="s">
+      <c r="D21" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="E21" s="187" t="s">
-        <v>53</v>
-      </c>
-      <c r="F21" s="186" t="s">
+      <c r="E21" s="184" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" s="183" t="s">
         <v>339</v>
       </c>
       <c r="G21" s="33"/>
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1">
-      <c r="A22" s="185">
+      <c r="A22" s="182">
         <v>11</v>
       </c>
-      <c r="B22" s="186" t="s">
+      <c r="B22" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="186" t="s">
+      <c r="C22" s="183" t="s">
         <v>340</v>
       </c>
-      <c r="D22" s="187" t="s">
+      <c r="D22" s="184" t="s">
         <v>341</v>
       </c>
-      <c r="E22" s="187" t="s">
+      <c r="E22" s="184" t="s">
         <v>235</v>
       </c>
-      <c r="F22" s="186" t="s">
+      <c r="F22" s="183" t="s">
         <v>342</v>
       </c>
       <c r="G22" s="33"/>
     </row>
     <row r="23" spans="1:7" ht="15" customHeight="1">
-      <c r="A23" s="185">
+      <c r="A23" s="182">
         <v>12</v>
       </c>
-      <c r="B23" s="186" t="s">
+      <c r="B23" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="186" t="s">
+      <c r="C23" s="183" t="s">
         <v>343</v>
       </c>
-      <c r="D23" s="187" t="s">
+      <c r="D23" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="E23" s="187" t="s">
+      <c r="E23" s="184" t="s">
         <v>235</v>
       </c>
-      <c r="F23" s="186" t="s">
+      <c r="F23" s="183" t="s">
         <v>344</v>
       </c>
       <c r="G23" s="33"/>
     </row>
     <row r="24" spans="1:7" ht="15" customHeight="1">
-      <c r="A24" s="185">
+      <c r="A24" s="182">
         <v>13</v>
       </c>
-      <c r="B24" s="186" t="s">
+      <c r="B24" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="186" t="s">
+      <c r="C24" s="183" t="s">
         <v>345</v>
       </c>
-      <c r="D24" s="187" t="s">
+      <c r="D24" s="184" t="s">
         <v>346</v>
       </c>
-      <c r="E24" s="187" t="s">
+      <c r="E24" s="184" t="s">
         <v>347</v>
       </c>
-      <c r="F24" s="186" t="s">
+      <c r="F24" s="183" t="s">
         <v>348</v>
       </c>
       <c r="G24" s="33"/>
     </row>
     <row r="25" spans="1:7" ht="15" customHeight="1">
-      <c r="A25" s="185">
+      <c r="A25" s="182">
         <v>14</v>
       </c>
-      <c r="B25" s="186" t="s">
+      <c r="B25" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="186" t="s">
+      <c r="C25" s="183" t="s">
         <v>349</v>
       </c>
-      <c r="D25" s="187" t="s">
+      <c r="D25" s="184" t="s">
         <v>67</v>
       </c>
-      <c r="E25" s="187" t="s">
+      <c r="E25" s="184" t="s">
         <v>347</v>
       </c>
-      <c r="F25" s="186" t="s">
+      <c r="F25" s="183" t="s">
         <v>350</v>
       </c>
       <c r="G25" s="33"/>
     </row>
     <row r="26" spans="1:7" ht="15" customHeight="1">
-      <c r="A26" s="185">
+      <c r="A26" s="182">
         <v>15</v>
       </c>
-      <c r="B26" s="186" t="s">
+      <c r="B26" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="186" t="s">
+      <c r="C26" s="183" t="s">
         <v>351</v>
       </c>
-      <c r="D26" s="187" t="s">
+      <c r="D26" s="184" t="s">
         <v>67</v>
       </c>
-      <c r="E26" s="187" t="s">
+      <c r="E26" s="184" t="s">
         <v>347</v>
       </c>
-      <c r="F26" s="186" t="s">
+      <c r="F26" s="183" t="s">
         <v>350</v>
       </c>
       <c r="G26" s="33"/>
     </row>
     <row r="27" spans="1:7" ht="15" customHeight="1">
-      <c r="A27" s="185">
+      <c r="A27" s="182">
         <v>16</v>
       </c>
-      <c r="B27" s="186" t="s">
+      <c r="B27" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="186" t="s">
+      <c r="C27" s="183" t="s">
         <v>352</v>
       </c>
-      <c r="D27" s="187" t="s">
+      <c r="D27" s="184" t="s">
         <v>67</v>
       </c>
-      <c r="E27" s="187" t="s">
+      <c r="E27" s="184" t="s">
         <v>235</v>
       </c>
-      <c r="F27" s="186" t="s">
+      <c r="F27" s="183" t="s">
         <v>353</v>
       </c>
       <c r="G27" s="33"/>
     </row>
     <row r="28" spans="1:7" ht="15" customHeight="1">
-      <c r="A28" s="247" t="s">
+      <c r="A28" s="246" t="s">
         <v>354</v>
       </c>
-      <c r="B28" s="248"/>
-      <c r="C28" s="248"/>
-      <c r="D28" s="249"/>
-      <c r="E28" s="248"/>
-      <c r="F28" s="248"/>
+      <c r="B28" s="247"/>
+      <c r="C28" s="247"/>
+      <c r="D28" s="248"/>
+      <c r="E28" s="247"/>
+      <c r="F28" s="247"/>
       <c r="G28" s="33"/>
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1">
-      <c r="A29" s="185">
+      <c r="A29" s="182">
         <v>1</v>
       </c>
-      <c r="B29" s="186" t="s">
+      <c r="B29" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="186" t="s">
+      <c r="C29" s="183" t="s">
         <v>323</v>
       </c>
-      <c r="D29" s="187" t="s">
+      <c r="D29" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="E29" s="187" t="s">
-        <v>53</v>
-      </c>
-      <c r="F29" s="186" t="s">
+      <c r="E29" s="184" t="s">
+        <v>53</v>
+      </c>
+      <c r="F29" s="183" t="s">
         <v>355</v>
       </c>
       <c r="G29" s="33"/>
     </row>
     <row r="30" spans="1:7" ht="15" customHeight="1">
-      <c r="A30" s="185">
+      <c r="A30" s="182">
         <v>2</v>
       </c>
-      <c r="B30" s="186" t="s">
+      <c r="B30" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="186" t="s">
+      <c r="C30" s="183" t="s">
         <v>325</v>
       </c>
-      <c r="D30" s="187" t="s">
+      <c r="D30" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="E30" s="187" t="s">
-        <v>53</v>
-      </c>
-      <c r="F30" s="186" t="s">
+      <c r="E30" s="184" t="s">
+        <v>53</v>
+      </c>
+      <c r="F30" s="183" t="s">
         <v>326</v>
       </c>
       <c r="G30" s="33"/>
     </row>
     <row r="31" spans="1:7" ht="15" customHeight="1">
-      <c r="A31" s="185">
+      <c r="A31" s="182">
         <v>3</v>
       </c>
-      <c r="B31" s="186" t="s">
+      <c r="B31" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C31" s="186" t="s">
+      <c r="C31" s="183" t="s">
         <v>327</v>
       </c>
-      <c r="D31" s="187" t="s">
+      <c r="D31" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="E31" s="187" t="s">
-        <v>53</v>
-      </c>
-      <c r="F31" s="186" t="s">
+      <c r="E31" s="184" t="s">
+        <v>53</v>
+      </c>
+      <c r="F31" s="183" t="s">
         <v>328</v>
       </c>
       <c r="G31" s="33"/>
     </row>
     <row r="32" spans="1:7" ht="15" customHeight="1">
-      <c r="A32" s="185">
+      <c r="A32" s="182">
         <v>4</v>
       </c>
-      <c r="B32" s="186" t="s">
+      <c r="B32" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C32" s="186" t="s">
+      <c r="C32" s="183" t="s">
         <v>290</v>
       </c>
-      <c r="D32" s="187" t="s">
+      <c r="D32" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="E32" s="187" t="s">
+      <c r="E32" s="184" t="s">
         <v>235</v>
       </c>
-      <c r="F32" s="186" t="s">
+      <c r="F32" s="183" t="s">
         <v>329</v>
       </c>
       <c r="G32" s="33"/>
     </row>
     <row r="33" spans="1:7" ht="15" customHeight="1">
-      <c r="A33" s="185">
+      <c r="A33" s="182">
         <v>5</v>
       </c>
-      <c r="B33" s="186" t="s">
+      <c r="B33" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C33" s="186" t="s">
+      <c r="C33" s="183" t="s">
         <v>330</v>
       </c>
-      <c r="D33" s="187" t="s">
+      <c r="D33" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="E33" s="187" t="s">
+      <c r="E33" s="184" t="s">
         <v>235</v>
       </c>
-      <c r="F33" s="186" t="s">
+      <c r="F33" s="183" t="s">
         <v>331</v>
       </c>
       <c r="G33" s="33"/>
     </row>
     <row r="34" spans="1:7" ht="15" customHeight="1">
-      <c r="A34" s="185">
+      <c r="A34" s="182">
         <v>6</v>
       </c>
-      <c r="B34" s="186" t="s">
+      <c r="B34" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C34" s="186" t="s">
+      <c r="C34" s="183" t="s">
         <v>332</v>
       </c>
-      <c r="D34" s="187" t="s">
+      <c r="D34" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="E34" s="187" t="s">
-        <v>53</v>
-      </c>
-      <c r="F34" s="186" t="s">
+      <c r="E34" s="184" t="s">
+        <v>53</v>
+      </c>
+      <c r="F34" s="183" t="s">
         <v>333</v>
       </c>
       <c r="G34" s="33"/>
     </row>
     <row r="35" spans="1:7" ht="15" customHeight="1">
-      <c r="A35" s="185">
+      <c r="A35" s="182">
         <v>7</v>
       </c>
-      <c r="B35" s="186" t="s">
+      <c r="B35" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C35" s="186" t="s">
+      <c r="C35" s="183" t="s">
         <v>334</v>
       </c>
-      <c r="D35" s="187" t="s">
+      <c r="D35" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="E35" s="187" t="s">
+      <c r="E35" s="184" t="s">
         <v>235</v>
       </c>
-      <c r="F35" s="186" t="s">
+      <c r="F35" s="183" t="s">
         <v>335</v>
       </c>
       <c r="G35" s="33"/>
     </row>
     <row r="36" spans="1:7" ht="15" customHeight="1">
-      <c r="A36" s="185">
+      <c r="A36" s="182">
         <v>8</v>
       </c>
-      <c r="B36" s="186" t="s">
+      <c r="B36" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="186" t="s">
+      <c r="C36" s="183" t="s">
         <v>336</v>
       </c>
-      <c r="D36" s="187" t="s">
+      <c r="D36" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="E36" s="187" t="s">
+      <c r="E36" s="184" t="s">
         <v>235</v>
       </c>
-      <c r="F36" s="186" t="s">
+      <c r="F36" s="183" t="s">
         <v>337</v>
       </c>
       <c r="G36" s="33"/>
     </row>
     <row r="37" spans="1:7" ht="15" customHeight="1">
-      <c r="A37" s="185">
+      <c r="A37" s="182">
         <v>9</v>
       </c>
-      <c r="B37" s="186" t="s">
+      <c r="B37" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C37" s="186" t="s">
+      <c r="C37" s="183" t="s">
         <v>338</v>
       </c>
-      <c r="D37" s="187" t="s">
+      <c r="D37" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="E37" s="187" t="s">
-        <v>53</v>
-      </c>
-      <c r="F37" s="186" t="s">
+      <c r="E37" s="184" t="s">
+        <v>53</v>
+      </c>
+      <c r="F37" s="183" t="s">
         <v>339</v>
       </c>
       <c r="G37" s="33"/>
     </row>
     <row r="38" spans="1:7" ht="15" customHeight="1">
-      <c r="A38" s="185">
+      <c r="A38" s="182">
         <v>10</v>
       </c>
-      <c r="B38" s="186" t="s">
+      <c r="B38" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="186" t="s">
+      <c r="C38" s="183" t="s">
         <v>340</v>
       </c>
-      <c r="D38" s="187" t="s">
+      <c r="D38" s="184" t="s">
         <v>341</v>
       </c>
-      <c r="E38" s="187" t="s">
+      <c r="E38" s="184" t="s">
         <v>235</v>
       </c>
-      <c r="F38" s="186" t="s">
+      <c r="F38" s="183" t="s">
         <v>342</v>
       </c>
       <c r="G38" s="33"/>
     </row>
     <row r="39" spans="1:7" ht="15" customHeight="1">
-      <c r="A39" s="185">
+      <c r="A39" s="182">
         <v>11</v>
       </c>
-      <c r="B39" s="186" t="s">
+      <c r="B39" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="C39" s="186" t="s">
+      <c r="C39" s="183" t="s">
         <v>343</v>
       </c>
-      <c r="D39" s="187" t="s">
+      <c r="D39" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="E39" s="187" t="s">
+      <c r="E39" s="184" t="s">
         <v>235</v>
       </c>
-      <c r="F39" s="186" t="s">
+      <c r="F39" s="183" t="s">
         <v>344</v>
       </c>
       <c r="G39" s="33"/>
@@ -14545,14 +14565,6 @@
       <c r="D44" s="33"/>
       <c r="F44" s="33"/>
       <c r="G44" s="33"/>
-    </row>
-    <row r="45" spans="1:7" ht="15" customHeight="1">
-      <c r="A45" s="33"/>
-      <c r="B45" s="33"/>
-      <c r="C45" s="33"/>
-      <c r="D45" s="33"/>
-      <c r="F45" s="33"/>
-      <c r="G45" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -14565,16 +14577,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -14746,6 +14748,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -14756,11 +14768,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{338796C8-1E45-4AA1-BD60-A388396432A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AEAC08E-CA6D-43CF-BD5D-30D3E42B8B9C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AEAC08E-CA6D-43CF-BD5D-30D3E42B8B9C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{338796C8-1E45-4AA1-BD60-A388396432A2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/input/mapping/063. OCB_GOLD_TCKH_CB_OFCR_DIM_HOP.xlsx
+++ b/input/mapping/063. OCB_GOLD_TCKH_CB_OFCR_DIM_HOP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1761" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3593D400-E7EE-4688-AA51-2B48CEB6036B}"/>
+  <xr:revisionPtr revIDLastSave="1768" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F63CA0D2-4C4A-4A87-A78F-7AB9DB638DF1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -338,28 +338,9 @@
   <si>
     <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE TABLE IF NOT EXISTS CB_OU_DIM (
-    OU_DIM_ID       BIGINT,
-    OU_ID           STRING,
-    OU_NM           STRING,
-    OU_CODE         STRING,
-    PRN_OU_ID       STRING,
-    PRN_OU_NM       STRING,
-    PRN_OU_CODE     STRING,
-    CB_AREA_ID      INTEGER,
-    CB_AREA_NM      STRING,
-    CRT_TM          TIMESTAMP,
-    EFF_FM_DT       DATE,
-    EFF_TO_DT       DATE,
-    START_WK_DT     DATE,
-    OU_ADR          STRING,
-    OU_PH           STRING
-)
-USING DELTA;
 MERGE INTO CB_OU_DIM tgt
 USING (
     WITH
-    -- STS Hub: khóa có trạng thái mới nhất = 'D' (đã xóa) đến :etl_date
     sts_deleted AS (
         SELECT branch_hashkey
         FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_branch')
@@ -367,15 +348,12 @@
         GROUP BY branch_hashkey
         HAVING MAX_BY(cdc_status, source_event_date) = 'D'
     ),
-    -- Hub đang có hiệu lực (CACHE: dùng lại 2 lần trong source_data)
     hub_active AS (
         SELECT h.branch_hashkey, h.business_key, h.source_event_date
         FROM IDENTIFIER(:cleaned || '.raw_vault.hub_branch') h
         LEFT JOIN sts_deleted d ON h.branch_hashkey = d.branch_hashkey
         WHERE d.branch_hashkey IS NULL
     ),
-    -- Satellite branch_information: bản mới nhất &lt;= :etl_date
-    -- (CACHE: dùng lại 2 lần trong source_data cho branch và parent branch)
     sat_latest AS (
         SELECT
             branch_hashkey,
@@ -384,7 +362,6 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY branch_hashkey
     ),
-    -- Satellite branch_mapping: bản mới nhất &lt;= :etl_date
     bm_latest AS (
         SELECT
             branch_hashkey,
@@ -395,13 +372,11 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY branch_hashkey
     ),
-    -- ou_area_mapping filter trước join (WARN 3.3)
     area_map AS (
         SELECT OU_ID, CB_AREA_ID, CB_AREA_NM
         FROM ou_area_mapping
         WHERE CB_AREA_ID IS NOT NULL
     ),
-    -- Source data tổng hợp (CACHE: dùng lại 3 lần trong changed, new_records, close_records)
     source_data AS (
         SELECT
             h.branch_hashkey                                AS OU_ID,
@@ -429,8 +404,6 @@
         WHERE UPPER(COALESCE(si.t_company_name, '')) &lt;&gt; 'NOT USED'
           AND h.business_key &lt;&gt; 'VN0010001'
     ),
-    -- Tập OU_ID có thay đổi thuộc tính so với bản đang active
-    -- (CACHE: dùng lại 2 lần trong new_records và close_records)
     changed AS (
         SELECT src.OU_ID
         FROM source_data src
@@ -444,8 +417,6 @@
            OR COALESCE(src.OU_ADR,      '') &lt;&gt; COALESCE(tgt.OU_ADR,      '')
            OR COALESCE(src.OU_PH,       '') &lt;&gt; COALESCE(tgt.OU_PH,       '')
     ),
-    -- Bản ghi NEW: insert mới hoặc insert version mới khi thay đổi
-    -- uuid() thay MAX+ROW_NUMBER() (fix 2.5/2.6): idempotent, không trùng khi parallel
     new_records AS (
         SELECT
             'NEW'                                               AS rec_type,
@@ -469,7 +440,6 @@
         WHERE tgt_chk.OU_ID IS NULL
            OR src.OU_ID IN (SELECT OU_ID FROM changed)
     ),
-    -- Bản ghi CLOSE: đóng version hiện tại khi có thay đổi hoặc bị xóa
     close_records AS (
         SELECT
             'CLOSE'                AS rec_type,
@@ -485,7 +455,7 @@
             tgt.START_WK_DT        AS source_event_date,
             tgt.OU_ADR,
             tgt.OU_PH,
-            tgt.OU_DIM_ID          AS NEW_OU_DIM_ID  -- giữ nguyên ID cũ khi close
+            tgt.OU_DIM_ID          AS NEW_OU_DIM_ID 
         FROM CB_OU_DIM tgt
         LEFT JOIN source_data src ON src.OU_ID = tgt.OU_ID
         WHERE tgt.EFF_TO_DT IS NULL
@@ -494,7 +464,6 @@
                 OR src.OU_ID IS NULL
               )
     )
-    -- Liệt kê tường minh (fix 3.1: bỏ SELECT *)
     SELECT
         rec_type, CDC_FLAG,
         OU_ID, OU_NM, OU_CODE,
@@ -547,8 +516,7 @@
 WHEN MATCHED AND src.rec_type = 'CLOSE' THEN
     UPDATE SET
         tgt.EFF_TO_DT = DATE_SUB(TO_DATE(:etl_date, 'yyyyMMdd'), 1),
-        tgt.CRT_TM    = CURRENT_TIMESTAMP()
-;</t>
+        tgt.CRT_TM    = CURRENT_TIMESTAMP()</t>
   </si>
   <si>
     <t>USE CATALOG IDENTIFIER(:curated);
@@ -556,7 +524,6 @@
 MERGE INTO CB_OFCR_DIM tgt
 USING (
     WITH
-    -- STS Hub: tập officer có trạng thái mới nhất = 'D' (đã xóa) đến :etl_date
     sts_deleted AS (
         SELECT dept_acct_officer_hashkey
         FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_acct_officer')
@@ -564,7 +531,6 @@
         GROUP BY dept_acct_officer_hashkey
         HAVING MAX_BY(cdc_status, source_event_date) = 'D'
     ),
-    -- Satellite officer: bản thuộc tính mới nhất đến :etl_date (fix X.6: LEFT JOIN)
     sat_ofcr AS (
         SELECT
             dept_acct_officer_hashkey,
@@ -574,7 +540,6 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY dept_acct_officer_hashkey
     ),
-    -- Hub officer active = Hub LEFT JOIN sat, loại khóa deleted (fix X.6)
     officer_active AS (
         SELECT
             h.dept_acct_officer_hashkey,
@@ -588,7 +553,6 @@
             ON h.dept_acct_officer_hashkey = d.dept_acct_officer_hashkey
         WHERE d.dept_acct_officer_hashkey IS NULL
     ),
-    -- Link officer -&gt; branch (1:N, driving key = dept_acct_officer_hashkey)
     ofcr_branch AS (
         SELECT
             dept_acct_officer_hashkey,
@@ -597,7 +561,6 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY dept_acct_officer_hashkey
     ),
-    -- Parent branch: sat_branch_mapping (single-active), bản mới nhất
     bm_latest AS (
         SELECT
             branch_hashkey,
@@ -606,13 +569,11 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY branch_hashkey
     ),
-    -- ou_area_mapping filter trước join (fix WARN 3.3)
     area_mapping AS (
         SELECT OU_ID, CB_AREA_ID, CB_AREA_NM
         FROM ou_area_mapping
         WHERE CB_AREA_ID IS NOT NULL
     ),
-    -- Build source data với default '999999999' / 'Khong xac dinh'
     src_data AS (
         SELECT
             o.dept_acct_officer_hashkey,
@@ -641,7 +602,6 @@
         LEFT JOIN area_mapping am
             ON am.OU_ID = ou.OU_CODE
     )
-    -- Liệt kê tường minh (fix 3.1: bỏ s.*), surrogate key dùng uuid() (fix 2.5/2.6)
     SELECT
         uuid()                        AS NEW_OU_OFCR_DIM_ID,
         s.dept_acct_officer_hashkey,
@@ -659,7 +619,6 @@
     FROM src_data s
 ) src
 ON tgt.OU_OFCR_ID = src.dept_acct_officer_hashkey
--- CASE INSERT: Officer mới
 WHEN NOT MATCHED THEN
     INSERT (
         OU_OFCR_DIM_ID,
@@ -697,7 +656,6 @@
         NULL,
         src.SRC_DT
     )
--- CASE UPDATE: Officer đã có (SCD Type 1 — overwrite)
 WHEN MATCHED THEN
     UPDATE SET
         tgt.OU_OFCR_NM       = src.OFCR_NM,
@@ -3906,11 +3864,40 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3935,36 +3922,6 @@
     <xf numFmtId="0" fontId="49" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -4160,13 +4117,12 @@
     <xf numFmtId="0" fontId="14" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4552,16 +4508,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="30" customHeight="1">
-      <c r="A1" s="197" t="s">
+      <c r="A1" s="188" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="198"/>
-      <c r="C1" s="198"/>
-      <c r="D1" s="198"/>
-      <c r="E1" s="198"/>
-      <c r="F1" s="198"/>
-      <c r="G1" s="198"/>
-      <c r="H1" s="198"/>
+      <c r="B1" s="189"/>
+      <c r="C1" s="189"/>
+      <c r="D1" s="189"/>
+      <c r="E1" s="189"/>
+      <c r="F1" s="189"/>
+      <c r="G1" s="189"/>
+      <c r="H1" s="189"/>
       <c r="I1" s="141"/>
       <c r="J1" s="39"/>
       <c r="K1" s="39"/>
@@ -4604,44 +4560,44 @@
       <c r="AV1" s="39"/>
     </row>
     <row r="2" spans="1:48">
-      <c r="A2" s="191" t="s">
+      <c r="A2" s="200" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="191"/>
-      <c r="C2" s="194" t="s">
+      <c r="B2" s="200"/>
+      <c r="C2" s="203" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="199" t="s">
+      <c r="D2" s="190" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="199"/>
+      <c r="E2" s="190"/>
       <c r="F2" s="167"/>
       <c r="G2" s="167"/>
       <c r="H2" s="167"/>
     </row>
     <row r="3" spans="1:48">
-      <c r="A3" s="192"/>
-      <c r="B3" s="192"/>
-      <c r="C3" s="195"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="200"/>
+      <c r="A3" s="201"/>
+      <c r="B3" s="201"/>
+      <c r="C3" s="204"/>
+      <c r="D3" s="191"/>
+      <c r="E3" s="191"/>
       <c r="F3" s="167"/>
       <c r="G3" s="167"/>
       <c r="H3" s="167"/>
     </row>
     <row r="4" spans="1:48">
-      <c r="A4" s="192"/>
-      <c r="B4" s="192"/>
-      <c r="C4" s="195"/>
-      <c r="D4" s="200"/>
-      <c r="E4" s="200"/>
+      <c r="A4" s="201"/>
+      <c r="B4" s="201"/>
+      <c r="C4" s="204"/>
+      <c r="D4" s="191"/>
+      <c r="E4" s="191"/>
       <c r="F4" s="167"/>
       <c r="G4" s="167"/>
       <c r="H4" s="167"/>
     </row>
     <row r="5" spans="1:48" ht="18.75" customHeight="1">
-      <c r="A5" s="192"/>
-      <c r="B5" s="192"/>
+      <c r="A5" s="201"/>
+      <c r="B5" s="201"/>
       <c r="C5" s="33"/>
       <c r="D5" s="33"/>
       <c r="E5" s="33"/>
@@ -4650,60 +4606,60 @@
       <c r="H5" s="33"/>
     </row>
     <row r="6" spans="1:48">
-      <c r="A6" s="192"/>
-      <c r="B6" s="192"/>
-      <c r="C6" s="195" t="s">
+      <c r="A6" s="201"/>
+      <c r="B6" s="201"/>
+      <c r="C6" s="204" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="201" t="s">
+      <c r="D6" s="192" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="201"/>
-      <c r="F6" s="204" t="s">
+      <c r="E6" s="192"/>
+      <c r="F6" s="195" t="s">
         <v>2</v>
       </c>
-      <c r="G6" s="205" t="s">
+      <c r="G6" s="196" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="205"/>
+      <c r="H6" s="196"/>
     </row>
     <row r="7" spans="1:48" ht="30.75" customHeight="1">
-      <c r="A7" s="192"/>
-      <c r="B7" s="192"/>
-      <c r="C7" s="195"/>
-      <c r="D7" s="201"/>
-      <c r="E7" s="201"/>
-      <c r="F7" s="204"/>
-      <c r="G7" s="205"/>
-      <c r="H7" s="205"/>
+      <c r="A7" s="201"/>
+      <c r="B7" s="201"/>
+      <c r="C7" s="204"/>
+      <c r="D7" s="192"/>
+      <c r="E7" s="192"/>
+      <c r="F7" s="195"/>
+      <c r="G7" s="196"/>
+      <c r="H7" s="196"/>
     </row>
     <row r="8" spans="1:48" ht="25.5" customHeight="1">
-      <c r="A8" s="192"/>
-      <c r="B8" s="192"/>
-      <c r="C8" s="195"/>
-      <c r="D8" s="201"/>
-      <c r="E8" s="201"/>
+      <c r="A8" s="201"/>
+      <c r="B8" s="201"/>
+      <c r="C8" s="204"/>
+      <c r="D8" s="192"/>
+      <c r="E8" s="192"/>
       <c r="F8"/>
       <c r="G8"/>
       <c r="H8"/>
     </row>
     <row r="9" spans="1:48" ht="71.25" customHeight="1">
-      <c r="A9" s="192"/>
-      <c r="B9" s="192"/>
-      <c r="C9" s="195"/>
-      <c r="D9" s="201"/>
-      <c r="E9" s="201"/>
+      <c r="A9" s="201"/>
+      <c r="B9" s="201"/>
+      <c r="C9" s="204"/>
+      <c r="D9" s="192"/>
+      <c r="E9" s="192"/>
       <c r="F9" s="166" t="s">
         <v>2</v>
       </c>
-      <c r="G9" s="206" t="s">
+      <c r="G9" s="197" t="s">
         <v>6</v>
       </c>
-      <c r="H9" s="206"/>
+      <c r="H9" s="197"/>
     </row>
     <row r="10" spans="1:48" ht="18.75" customHeight="1">
-      <c r="A10" s="192"/>
-      <c r="B10" s="192"/>
+      <c r="A10" s="201"/>
+      <c r="B10" s="201"/>
       <c r="C10" s="33"/>
       <c r="D10" s="33"/>
       <c r="E10" s="33"/>
@@ -4712,44 +4668,44 @@
       <c r="H10" s="33"/>
     </row>
     <row r="11" spans="1:48">
-      <c r="A11" s="192"/>
-      <c r="B11" s="192"/>
-      <c r="C11" s="195" t="s">
+      <c r="A11" s="201"/>
+      <c r="B11" s="201"/>
+      <c r="C11" s="204" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="202" t="s">
+      <c r="D11" s="193" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="202"/>
+      <c r="E11" s="193"/>
       <c r="F11" s="167"/>
       <c r="G11" s="167"/>
       <c r="H11" s="167"/>
     </row>
     <row r="12" spans="1:48">
-      <c r="A12" s="192"/>
-      <c r="B12" s="192"/>
-      <c r="C12" s="195"/>
-      <c r="D12" s="202"/>
-      <c r="E12" s="202"/>
+      <c r="A12" s="201"/>
+      <c r="B12" s="201"/>
+      <c r="C12" s="204"/>
+      <c r="D12" s="193"/>
+      <c r="E12" s="193"/>
       <c r="F12" s="167"/>
       <c r="G12" s="167"/>
       <c r="H12" s="167"/>
     </row>
     <row r="13" spans="1:48">
-      <c r="A13" s="193"/>
-      <c r="B13" s="193"/>
-      <c r="C13" s="196"/>
-      <c r="D13" s="203"/>
-      <c r="E13" s="203"/>
+      <c r="A13" s="202"/>
+      <c r="B13" s="202"/>
+      <c r="C13" s="205"/>
+      <c r="D13" s="194"/>
+      <c r="E13" s="194"/>
       <c r="F13" s="167"/>
       <c r="G13" s="167"/>
       <c r="H13" s="167"/>
     </row>
     <row r="14" spans="1:48">
-      <c r="A14" s="189" t="s">
+      <c r="A14" s="198" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="190"/>
+      <c r="B14" s="199"/>
       <c r="C14" s="272"/>
       <c r="D14" s="272"/>
       <c r="E14" s="272"/>
@@ -4813,6 +4769,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A2:B13"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="C6:C9"/>
+    <mergeCell ref="C11:C13"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="D6:E9"/>
@@ -4820,11 +4781,6 @@
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="G6:H7"/>
     <mergeCell ref="G9:H9"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A2:B13"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="C6:C9"/>
-    <mergeCell ref="C11:C13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4906,8 +4862,8 @@
       </c>
       <c r="B6" s="58"/>
       <c r="C6" s="58"/>
-      <c r="D6" s="251"/>
-      <c r="E6" s="251"/>
+      <c r="D6" s="250"/>
+      <c r="E6" s="250"/>
       <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7" ht="21" customHeight="1">
@@ -4920,10 +4876,10 @@
       <c r="C7" s="59" t="s">
         <v>182</v>
       </c>
-      <c r="D7" s="252" t="s">
+      <c r="D7" s="251" t="s">
         <v>183</v>
       </c>
-      <c r="E7" s="253"/>
+      <c r="E7" s="252"/>
       <c r="G7" s="11"/>
     </row>
     <row r="8" spans="1:7" ht="21" customHeight="1">
@@ -4936,10 +4892,10 @@
       <c r="C8" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="249" t="s">
+      <c r="D8" s="248" t="s">
         <v>362</v>
       </c>
-      <c r="E8" s="250"/>
+      <c r="E8" s="249"/>
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" ht="21" customHeight="1">
@@ -4952,10 +4908,10 @@
       <c r="C9" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="249" t="s">
+      <c r="D9" s="248" t="s">
         <v>119</v>
       </c>
-      <c r="E9" s="250"/>
+      <c r="E9" s="249"/>
       <c r="G9" s="11"/>
     </row>
     <row r="10" spans="1:7" ht="14.45" customHeight="1">
@@ -4968,10 +4924,10 @@
       <c r="C10" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="249" t="s">
+      <c r="D10" s="248" t="s">
         <v>105</v>
       </c>
-      <c r="E10" s="250"/>
+      <c r="E10" s="249"/>
     </row>
     <row r="11" spans="1:7" ht="14.45" customHeight="1">
       <c r="A11" s="8" t="s">
@@ -4983,10 +4939,10 @@
       <c r="C11" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="249" t="s">
+      <c r="D11" s="248" t="s">
         <v>107</v>
       </c>
-      <c r="E11" s="250"/>
+      <c r="E11" s="249"/>
     </row>
     <row r="12" spans="1:7" ht="14.45" customHeight="1">
       <c r="A12" s="8" t="s">
@@ -4998,10 +4954,10 @@
       <c r="C12" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="249" t="s">
+      <c r="D12" s="248" t="s">
         <v>364</v>
       </c>
-      <c r="E12" s="250"/>
+      <c r="E12" s="249"/>
     </row>
     <row r="13" spans="1:7" ht="14.45" customHeight="1">
       <c r="A13" s="8" t="s">
@@ -5013,10 +4969,10 @@
       <c r="C13" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="249" t="s">
+      <c r="D13" s="248" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="250"/>
+      <c r="E13" s="249"/>
     </row>
     <row r="14" spans="1:7" ht="70.5" customHeight="1">
       <c r="A14" s="8" t="s">
@@ -5028,10 +4984,10 @@
       <c r="C14" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="249" t="s">
+      <c r="D14" s="248" t="s">
         <v>366</v>
       </c>
-      <c r="E14" s="250"/>
+      <c r="E14" s="249"/>
     </row>
     <row r="15" spans="1:7" ht="14.45" customHeight="1"/>
   </sheetData>
@@ -5281,13 +5237,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="41.25" customHeight="1">
-      <c r="A1" s="254" t="s">
+      <c r="A1" s="253" t="s">
         <v>372</v>
       </c>
-      <c r="B1" s="255"/>
-      <c r="C1" s="255"/>
-      <c r="D1" s="255"/>
-      <c r="E1" s="255"/>
+      <c r="B1" s="254"/>
+      <c r="C1" s="254"/>
+      <c r="D1" s="254"/>
+      <c r="E1" s="254"/>
     </row>
     <row r="2" spans="1:5" ht="18.75">
       <c r="A2" s="61" t="s">
@@ -5329,13 +5285,13 @@
       <c r="E4" s="63"/>
     </row>
     <row r="5" spans="1:5" ht="18.75">
-      <c r="A5" s="255" t="s">
+      <c r="A5" s="254" t="s">
         <v>375</v>
       </c>
-      <c r="B5" s="255"/>
-      <c r="C5" s="255"/>
-      <c r="D5" s="255"/>
-      <c r="E5" s="255"/>
+      <c r="B5" s="254"/>
+      <c r="C5" s="254"/>
+      <c r="D5" s="254"/>
+      <c r="E5" s="254"/>
     </row>
     <row r="6" spans="1:5" ht="18.75">
       <c r="A6" s="61" t="s">
@@ -5468,14 +5424,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="46.5" customHeight="1">
-      <c r="A1" s="256" t="s">
+      <c r="A1" s="255" t="s">
         <v>382</v>
       </c>
-      <c r="B1" s="257"/>
-      <c r="C1" s="257"/>
-      <c r="D1" s="257"/>
-      <c r="E1" s="257"/>
-      <c r="F1" s="257"/>
+      <c r="B1" s="256"/>
+      <c r="C1" s="256"/>
+      <c r="D1" s="256"/>
+      <c r="E1" s="256"/>
+      <c r="F1" s="256"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="66" t="s">
@@ -5484,10 +5440,10 @@
       <c r="B2" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="258" t="s">
+      <c r="C2" s="257" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="259"/>
+      <c r="D2" s="258"/>
       <c r="E2" s="66" t="s">
         <v>34</v>
       </c>
@@ -5502,8 +5458,8 @@
       <c r="B3" s="68" t="s">
         <v>383</v>
       </c>
-      <c r="C3" s="260"/>
-      <c r="D3" s="261"/>
+      <c r="C3" s="259"/>
+      <c r="D3" s="260"/>
       <c r="E3" s="68" t="s">
         <v>38</v>
       </c>
@@ -5520,13 +5476,13 @@
       <c r="F4" s="69"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="257" t="s">
+      <c r="A5" s="256" t="s">
         <v>385</v>
       </c>
-      <c r="B5" s="257"/>
-      <c r="C5" s="257"/>
-      <c r="D5" s="257"/>
-      <c r="E5" s="257"/>
+      <c r="B5" s="256"/>
+      <c r="C5" s="256"/>
+      <c r="D5" s="256"/>
+      <c r="E5" s="256"/>
       <c r="F5" s="70"/>
     </row>
     <row r="6" spans="1:6">
@@ -6786,14 +6742,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="46.5" customHeight="1">
-      <c r="A1" s="262" t="s">
+      <c r="A1" s="261" t="s">
         <v>450</v>
       </c>
-      <c r="B1" s="263"/>
-      <c r="C1" s="263"/>
-      <c r="D1" s="263"/>
-      <c r="E1" s="263"/>
-      <c r="F1" s="263"/>
+      <c r="B1" s="262"/>
+      <c r="C1" s="262"/>
+      <c r="D1" s="262"/>
+      <c r="E1" s="262"/>
+      <c r="F1" s="262"/>
     </row>
     <row r="2" spans="1:6" ht="18.75">
       <c r="A2" s="60" t="s">
@@ -6802,10 +6758,10 @@
       <c r="B2" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="263" t="s">
+      <c r="C2" s="262" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="263"/>
+      <c r="D2" s="262"/>
       <c r="E2" s="60" t="s">
         <v>34</v>
       </c>
@@ -6822,13 +6778,13 @@
       <c r="F3" s="75"/>
     </row>
     <row r="4" spans="1:6" ht="18.75">
-      <c r="A4" s="263" t="s">
+      <c r="A4" s="262" t="s">
         <v>451</v>
       </c>
-      <c r="B4" s="263"/>
-      <c r="C4" s="263"/>
-      <c r="D4" s="263"/>
-      <c r="E4" s="263"/>
+      <c r="B4" s="262"/>
+      <c r="C4" s="262"/>
+      <c r="D4" s="262"/>
+      <c r="E4" s="262"/>
       <c r="F4" s="76"/>
     </row>
     <row r="5" spans="1:6" ht="18.75">
@@ -8079,13 +8035,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="37.5" customHeight="1">
-      <c r="A1" s="264" t="s">
+      <c r="A1" s="263" t="s">
         <v>453</v>
       </c>
-      <c r="B1" s="265"/>
-      <c r="C1" s="265"/>
-      <c r="D1" s="265"/>
-      <c r="E1" s="265"/>
+      <c r="B1" s="264"/>
+      <c r="C1" s="264"/>
+      <c r="D1" s="264"/>
+      <c r="E1" s="264"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="81" t="s">
@@ -8120,13 +8076,13 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="266" t="s">
+      <c r="A4" s="265" t="s">
         <v>456</v>
       </c>
-      <c r="B4" s="267"/>
-      <c r="C4" s="267"/>
-      <c r="D4" s="267"/>
-      <c r="E4" s="268"/>
+      <c r="B4" s="266"/>
+      <c r="C4" s="266"/>
+      <c r="D4" s="266"/>
+      <c r="E4" s="267"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="81" t="s">
@@ -8242,13 +8198,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="47.25" customHeight="1">
-      <c r="A1" s="269" t="s">
+      <c r="A1" s="268" t="s">
         <v>460</v>
       </c>
-      <c r="B1" s="270"/>
-      <c r="C1" s="270"/>
-      <c r="D1" s="270"/>
-      <c r="E1" s="270"/>
+      <c r="B1" s="269"/>
+      <c r="C1" s="269"/>
+      <c r="D1" s="269"/>
+      <c r="E1" s="269"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="85" t="s">
@@ -8275,13 +8231,13 @@
       <c r="E3" s="86"/>
     </row>
     <row r="5" spans="1:5" ht="18.75">
-      <c r="A5" s="263" t="s">
+      <c r="A5" s="262" t="s">
         <v>461</v>
       </c>
-      <c r="B5" s="263"/>
-      <c r="C5" s="263"/>
-      <c r="D5" s="263"/>
-      <c r="E5" s="263"/>
+      <c r="B5" s="262"/>
+      <c r="C5" s="262"/>
+      <c r="D5" s="262"/>
+      <c r="E5" s="262"/>
     </row>
     <row r="6" spans="1:5" ht="18.75">
       <c r="A6" s="60" t="s">
@@ -8739,7 +8695,7 @@
       <c r="E11" s="163" t="s">
         <v>494</v>
       </c>
-      <c r="F11" s="187"/>
+      <c r="F11" s="186"/>
       <c r="G11" s="105"/>
     </row>
     <row r="12" spans="1:7" ht="229.5">
@@ -8758,18 +8714,18 @@
       <c r="E12" s="163" t="s">
         <v>498</v>
       </c>
-      <c r="F12" s="187"/>
+      <c r="F12" s="186"/>
       <c r="G12" s="105"/>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1">
-      <c r="A13" s="271" t="s">
+      <c r="A13" s="270" t="s">
         <v>229</v>
       </c>
-      <c r="B13" s="271"/>
-      <c r="C13" s="271"/>
-      <c r="D13" s="271"/>
-      <c r="E13" s="271"/>
-      <c r="F13" s="244"/>
+      <c r="B13" s="270"/>
+      <c r="C13" s="270"/>
+      <c r="D13" s="270"/>
+      <c r="E13" s="270"/>
+      <c r="F13" s="243"/>
       <c r="G13" s="140"/>
     </row>
     <row r="14" spans="1:7" ht="27">
@@ -9085,7 +9041,7 @@
       <c r="F28" s="129" t="s">
         <v>513</v>
       </c>
-      <c r="G28" s="188"/>
+      <c r="G28" s="187"/>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="129">
@@ -9106,7 +9062,7 @@
       <c r="F29" s="129" t="s">
         <v>515</v>
       </c>
-      <c r="G29" s="188"/>
+      <c r="G29" s="187"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -9177,11 +9133,11 @@
       <c r="B4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="186" t="s">
+      <c r="D4" s="271" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="409.6">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -9214,15 +9170,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="207" t="s">
+      <c r="A1" s="206" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="208"/>
-      <c r="C1" s="208"/>
-      <c r="D1" s="208"/>
-      <c r="E1" s="208"/>
-      <c r="F1" s="208"/>
-      <c r="G1" s="209"/>
+      <c r="B1" s="207"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="207"/>
+      <c r="G1" s="208"/>
       <c r="H1" s="275"/>
     </row>
     <row r="2" spans="1:8">
@@ -9238,11 +9194,11 @@
       <c r="D2" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="208" t="s">
+      <c r="E2" s="207" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="208"/>
-      <c r="G2" s="210"/>
+      <c r="F2" s="207"/>
+      <c r="G2" s="209"/>
       <c r="H2" s="275"/>
     </row>
     <row r="3" spans="1:8">
@@ -9258,9 +9214,9 @@
       <c r="D3" s="91" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="211"/>
-      <c r="F3" s="211"/>
-      <c r="G3" s="212"/>
+      <c r="E3" s="210"/>
+      <c r="F3" s="210"/>
+      <c r="G3" s="211"/>
       <c r="H3" s="275"/>
     </row>
     <row r="4" spans="1:8" ht="64.5" customHeight="1">
@@ -9276,23 +9232,23 @@
       <c r="D4" s="91" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="211" t="s">
+      <c r="E4" s="210" t="s">
         <v>42</v>
       </c>
-      <c r="F4" s="211"/>
-      <c r="G4" s="212"/>
+      <c r="F4" s="210"/>
+      <c r="G4" s="211"/>
       <c r="H4" s="275"/>
     </row>
     <row r="5" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A5" s="213" t="s">
+      <c r="A5" s="212" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="214"/>
-      <c r="C5" s="214"/>
-      <c r="D5" s="214"/>
-      <c r="E5" s="214"/>
-      <c r="F5" s="214"/>
-      <c r="G5" s="215"/>
+      <c r="B5" s="213"/>
+      <c r="C5" s="213"/>
+      <c r="D5" s="213"/>
+      <c r="E5" s="213"/>
+      <c r="F5" s="213"/>
+      <c r="G5" s="214"/>
       <c r="H5" s="275"/>
     </row>
     <row r="6" spans="1:8">
@@ -10723,14 +10679,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="216" t="s">
+      <c r="A1" s="215" t="s">
         <v>173</v>
       </c>
-      <c r="B1" s="217"/>
-      <c r="C1" s="217"/>
-      <c r="D1" s="217"/>
-      <c r="E1" s="217"/>
-      <c r="F1" s="217"/>
+      <c r="B1" s="216"/>
+      <c r="C1" s="216"/>
+      <c r="D1" s="216"/>
+      <c r="E1" s="216"/>
+      <c r="F1" s="216"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7">
@@ -10740,10 +10696,10 @@
       <c r="B2" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="218" t="s">
+      <c r="C2" s="217" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="219"/>
+      <c r="D2" s="218"/>
       <c r="E2" s="40" t="s">
         <v>34</v>
       </c>
@@ -10759,10 +10715,10 @@
       <c r="B3" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="C3" s="220" t="s">
+      <c r="C3" s="219" t="s">
         <v>175</v>
       </c>
-      <c r="D3" s="221"/>
+      <c r="D3" s="220"/>
       <c r="E3" s="41" t="s">
         <v>38</v>
       </c>
@@ -10778,10 +10734,10 @@
       <c r="B4" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="C4" s="220" t="s">
+      <c r="C4" s="219" t="s">
         <v>177</v>
       </c>
-      <c r="D4" s="221"/>
+      <c r="D4" s="220"/>
       <c r="E4" s="41" t="s">
         <v>41</v>
       </c>
@@ -10790,14 +10746,14 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="217" t="s">
+      <c r="A5" s="216" t="s">
         <v>179</v>
       </c>
-      <c r="B5" s="217"/>
-      <c r="C5" s="217"/>
-      <c r="D5" s="217"/>
-      <c r="E5" s="217"/>
-      <c r="F5" s="217"/>
+      <c r="B5" s="216"/>
+      <c r="C5" s="216"/>
+      <c r="D5" s="216"/>
+      <c r="E5" s="216"/>
+      <c r="F5" s="216"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="40" t="s">
@@ -10927,14 +10883,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24.75" customHeight="1">
-      <c r="A1" s="222" t="s">
+      <c r="A1" s="221" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="223"/>
-      <c r="C1" s="223"/>
-      <c r="D1" s="223"/>
-      <c r="E1" s="223"/>
-      <c r="F1" s="223"/>
+      <c r="B1" s="222"/>
+      <c r="C1" s="222"/>
+      <c r="D1" s="222"/>
+      <c r="E1" s="222"/>
+      <c r="F1" s="222"/>
     </row>
     <row r="2" spans="1:6" ht="24.75" customHeight="1">
       <c r="A2" s="46" t="s">
@@ -10943,10 +10899,10 @@
       <c r="B2" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="224" t="s">
+      <c r="C2" s="223" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="225"/>
+      <c r="D2" s="224"/>
       <c r="E2" s="46" t="s">
         <v>34</v>
       </c>
@@ -10961,10 +10917,10 @@
       <c r="B3" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="C3" s="226" t="s">
+      <c r="C3" s="225" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="227"/>
+      <c r="D3" s="226"/>
       <c r="E3" s="47" t="s">
         <v>38</v>
       </c>
@@ -10977,10 +10933,10 @@
       <c r="B4" s="50" t="s">
         <v>198</v>
       </c>
-      <c r="C4" s="228" t="s">
+      <c r="C4" s="227" t="s">
         <v>199</v>
       </c>
-      <c r="D4" s="229"/>
+      <c r="D4" s="228"/>
       <c r="E4" s="49" t="s">
         <v>200</v>
       </c>
@@ -10997,13 +10953,13 @@
       <c r="F5" s="282"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="224" t="s">
+      <c r="A7" s="223" t="s">
         <v>202</v>
       </c>
-      <c r="B7" s="230"/>
-      <c r="C7" s="230"/>
-      <c r="D7" s="230"/>
-      <c r="E7" s="230"/>
+      <c r="B7" s="229"/>
+      <c r="C7" s="229"/>
+      <c r="D7" s="229"/>
+      <c r="E7" s="229"/>
       <c r="F7" s="282"/>
     </row>
     <row r="8" spans="1:6">
@@ -11175,13 +11131,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="233" t="s">
+      <c r="A1" s="232" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="234"/>
-      <c r="C1" s="234"/>
-      <c r="D1" s="234"/>
-      <c r="E1" s="235"/>
+      <c r="B1" s="233"/>
+      <c r="C1" s="233"/>
+      <c r="D1" s="233"/>
+      <c r="E1" s="234"/>
       <c r="F1" s="5"/>
     </row>
     <row r="2" spans="1:6">
@@ -11282,39 +11238,39 @@
       <c r="E7" s="30"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1">
-      <c r="A8" s="233" t="s">
+      <c r="A8" s="232" t="s">
         <v>229</v>
       </c>
-      <c r="B8" s="234"/>
-      <c r="C8" s="234"/>
-      <c r="D8" s="234"/>
-      <c r="E8" s="234"/>
+      <c r="B8" s="233"/>
+      <c r="C8" s="233"/>
+      <c r="D8" s="233"/>
+      <c r="E8" s="233"/>
       <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="236" t="s">
+      <c r="A9" s="235" t="s">
         <v>230</v>
       </c>
-      <c r="B9" s="237" t="s">
+      <c r="B9" s="236" t="s">
         <v>231</v>
       </c>
-      <c r="C9" s="237" t="s">
+      <c r="C9" s="236" t="s">
         <v>182</v>
       </c>
-      <c r="D9" s="238" t="s">
+      <c r="D9" s="237" t="s">
         <v>183</v>
       </c>
-      <c r="E9" s="238" t="s">
+      <c r="E9" s="237" t="s">
         <v>232</v>
       </c>
       <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="236"/>
-      <c r="B10" s="237"/>
-      <c r="C10" s="237"/>
-      <c r="D10" s="239"/>
-      <c r="E10" s="239"/>
+      <c r="A10" s="235"/>
+      <c r="B10" s="236"/>
+      <c r="C10" s="236"/>
+      <c r="D10" s="238"/>
+      <c r="E10" s="238"/>
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6">
@@ -12344,13 +12300,13 @@
       <c r="F67" s="5"/>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="231" t="s">
+      <c r="A68" s="230" t="s">
         <v>249</v>
       </c>
-      <c r="B68" s="232"/>
-      <c r="C68" s="232"/>
-      <c r="D68" s="232"/>
-      <c r="E68" s="232"/>
+      <c r="B68" s="231"/>
+      <c r="C68" s="231"/>
+      <c r="D68" s="231"/>
+      <c r="E68" s="231"/>
       <c r="F68" s="5"/>
     </row>
     <row r="69" spans="1:6">
@@ -13399,13 +13355,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="240" t="s">
+      <c r="A1" s="239" t="s">
         <v>278</v>
       </c>
-      <c r="B1" s="241"/>
-      <c r="C1" s="241"/>
-      <c r="D1" s="241"/>
-      <c r="E1" s="242"/>
+      <c r="B1" s="240"/>
+      <c r="C1" s="240"/>
+      <c r="D1" s="240"/>
+      <c r="E1" s="241"/>
       <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:6">
@@ -13452,13 +13408,13 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="243" t="s">
+      <c r="A5" s="242" t="s">
         <v>281</v>
       </c>
-      <c r="B5" s="243"/>
-      <c r="C5" s="243"/>
-      <c r="D5" s="243"/>
-      <c r="E5" s="243"/>
+      <c r="B5" s="242"/>
+      <c r="C5" s="242"/>
+      <c r="D5" s="242"/>
+      <c r="E5" s="242"/>
       <c r="F5" s="112"/>
     </row>
     <row r="6" spans="1:6">
@@ -13641,13 +13597,13 @@
       <c r="E4" s="19"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="244" t="s">
+      <c r="A5" s="243" t="s">
         <v>229</v>
       </c>
-      <c r="B5" s="244"/>
-      <c r="C5" s="244"/>
-      <c r="D5" s="244"/>
-      <c r="E5" s="244"/>
+      <c r="B5" s="243"/>
+      <c r="C5" s="243"/>
+      <c r="D5" s="243"/>
+      <c r="E5" s="243"/>
     </row>
     <row r="6" spans="1:5" ht="24.75">
       <c r="A6" s="21" t="s">
@@ -13906,13 +13862,13 @@
       <c r="G8" s="33"/>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1">
-      <c r="A9" s="245" t="s">
+      <c r="A9" s="244" t="s">
         <v>229</v>
       </c>
-      <c r="B9" s="245"/>
-      <c r="C9" s="245"/>
-      <c r="D9" s="245"/>
-      <c r="E9" s="245"/>
+      <c r="B9" s="244"/>
+      <c r="C9" s="244"/>
+      <c r="D9" s="244"/>
+      <c r="E9" s="244"/>
       <c r="F9" s="179"/>
       <c r="G9" s="33"/>
     </row>
@@ -13938,14 +13894,14 @@
       <c r="G10" s="33"/>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1">
-      <c r="A11" s="246" t="s">
+      <c r="A11" s="245" t="s">
         <v>318</v>
       </c>
-      <c r="B11" s="247"/>
-      <c r="C11" s="247"/>
-      <c r="D11" s="247"/>
-      <c r="E11" s="247"/>
-      <c r="F11" s="247"/>
+      <c r="B11" s="246"/>
+      <c r="C11" s="246"/>
+      <c r="D11" s="246"/>
+      <c r="E11" s="246"/>
+      <c r="F11" s="246"/>
       <c r="G11" s="33"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1">
@@ -14285,14 +14241,14 @@
       <c r="G27" s="33"/>
     </row>
     <row r="28" spans="1:7" ht="15" customHeight="1">
-      <c r="A28" s="246" t="s">
+      <c r="A28" s="245" t="s">
         <v>354</v>
       </c>
-      <c r="B28" s="247"/>
-      <c r="C28" s="247"/>
-      <c r="D28" s="248"/>
-      <c r="E28" s="247"/>
-      <c r="F28" s="247"/>
+      <c r="B28" s="246"/>
+      <c r="C28" s="246"/>
+      <c r="D28" s="247"/>
+      <c r="E28" s="246"/>
+      <c r="F28" s="246"/>
       <c r="G28" s="33"/>
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1">
@@ -14749,6 +14705,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
@@ -14758,23 +14723,14 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AEAC08E-CA6D-43CF-BD5D-30D3E42B8B9C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{338796C8-1E45-4AA1-BD60-A388396432A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B1DDD3-2176-4CA0-892E-905566AB1E8D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B1DDD3-2176-4CA0-892E-905566AB1E8D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{338796C8-1E45-4AA1-BD60-A388396432A2}"/>
 </file>